--- a/A+Time-Table New (Course Criculam) - 6th Sem/MasterSheetBCA-Class.xlsx
+++ b/A+Time-Table New (Course Criculam) - 6th Sem/MasterSheetBCA-Class.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop File\BCA 6th 'DS2'\A+Time-Table New (Course Criculam) - 6th Sem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAD7703-B4D1-4872-BDC6-77A0EC3DF424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E450E699-CD47-4F91-9E2B-34B907B8151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BCA-2023-2026" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BCA-2023-2026'!$P$1:$P$641</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BCA-2023-UPDATE'!$P$1:$P$641</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BCA-2023-UPDATE'!$P$1:$P$631</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11549" uniqueCount="2305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11548" uniqueCount="2305">
   <si>
     <t xml:space="preserve">S.No. </t>
   </si>
@@ -6962,7 +6962,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7006,6 +7006,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -7557,7 +7563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7695,6 +7701,69 @@
     <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7711,15 +7780,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7761,63 +7821,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7850,15 +7866,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>3809</xdr:colOff>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>3809</xdr:rowOff>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>605790</xdr:colOff>
+          <xdr:colOff>609600</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>184784</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7890,7 +7906,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="45720" tIns="45720" rIns="45720" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -7920,15 +7936,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>1905</xdr:colOff>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>5715</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>607695</xdr:colOff>
+          <xdr:colOff>609600</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>186690</xdr:rowOff>
+          <xdr:rowOff>190500</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7960,7 +7976,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="45720" tIns="45720" rIns="45720" bIns="45720" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -39154,87 +39170,87 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="79" t="s">
         <v>948</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
-      <c r="J3" s="80" t="s">
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
+      <c r="J3" s="61" t="s">
         <v>2303</v>
       </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="82"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="62"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="29" t="s">
         <v>943</v>
       </c>
-      <c r="C5" s="63" t="str">
+      <c r="C5" s="85" t="str">
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,3,FALSE)</f>
         <v>PRATIPAL KUMAR SINGH</v>
       </c>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65" t="s">
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="87" t="s">
         <v>945</v>
       </c>
-      <c r="H5" s="66"/>
-      <c r="J5" s="86" t="s">
+      <c r="H5" s="88"/>
+      <c r="J5" s="54" t="s">
         <v>2304</v>
       </c>
-      <c r="K5" s="87">
+      <c r="K5" s="67">
         <v>1323607</v>
       </c>
-      <c r="L5" s="88"/>
+      <c r="L5" s="68"/>
     </row>
     <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="29" t="s">
         <v>611</v>
       </c>
-      <c r="C6" s="63" t="str">
+      <c r="C6" s="85" t="str">
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,4,FALSE)</f>
         <v>SAWDHAN SINGH</v>
       </c>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="67">
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="89">
         <v>1323607</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="J6" s="75" t="str">
+      <c r="H6" s="90"/>
+      <c r="J6" s="69" t="str">
         <f>VLOOKUP($K$5,'BCA-2023-2026'!$B$2:$R$631,3,FALSE)</f>
         <v>PRATIPAL KUMAR SINGH</v>
       </c>
-      <c r="K6" s="79"/>
-      <c r="L6" s="76"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>944</v>
       </c>
-      <c r="C7" s="56" t="str">
+      <c r="C7" s="78" t="str">
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,2,FALSE)</f>
         <v>23-MCM-576</v>
       </c>
-      <c r="D7" s="49"/>
+      <c r="D7" s="74"/>
       <c r="E7" s="30" t="s">
         <v>946</v>
       </c>
@@ -39249,11 +39265,11 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,9,FALSE)</f>
         <v>BCA (Data Science)</v>
       </c>
-      <c r="J7" s="77" t="s">
+      <c r="J7" s="52" t="s">
         <v>949</v>
       </c>
-      <c r="K7" s="74"/>
-      <c r="L7" s="78"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="53"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
@@ -39263,16 +39279,16 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,12,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
-      <c r="J8" s="77" t="s">
+      <c r="D8" s="72"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="74"/>
+      <c r="J8" s="52" t="s">
         <v>950</v>
       </c>
-      <c r="K8" s="74"/>
-      <c r="L8" s="78"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="53"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
@@ -39282,16 +39298,16 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,13,FALSE)</f>
         <v>8.0500000000000007</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="52"/>
-      <c r="J9" s="77" t="s">
+      <c r="D9" s="75"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="77"/>
+      <c r="J9" s="52" t="s">
         <v>951</v>
       </c>
-      <c r="K9" s="74"/>
-      <c r="L9" s="78"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="53"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
@@ -39301,16 +39317,16 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,14,FALSE)</f>
         <v>9.0500000000000007</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="52"/>
-      <c r="J10" s="77" t="s">
+      <c r="D10" s="75"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="77"/>
+      <c r="J10" s="52" t="s">
         <v>952</v>
       </c>
-      <c r="K10" s="74"/>
-      <c r="L10" s="78"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="53"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="33" t="s">
@@ -39320,16 +39336,16 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,15,FALSE)</f>
         <v>7.36</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="52"/>
-      <c r="J11" s="77" t="s">
+      <c r="D11" s="75"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77"/>
+      <c r="J11" s="52" t="s">
         <v>2300</v>
       </c>
-      <c r="K11" s="74"/>
-      <c r="L11" s="78"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="33" t="s">
@@ -39339,16 +39355,16 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,16,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="52"/>
-      <c r="J12" s="89" t="s">
+      <c r="D12" s="75"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="77"/>
+      <c r="J12" s="55" t="s">
         <v>2301</v>
       </c>
-      <c r="K12" s="90"/>
-      <c r="L12" s="91"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="57"/>
     </row>
     <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="34" t="s">
@@ -39358,14 +39374,14 @@
         <f>VLOOKUP($G$6,'BCA-2023-2026'!$B$2:$R$631,17,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="52"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="76"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="77"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
     </row>
     <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="35" t="s">
@@ -39375,23 +39391,18 @@
         <f>AVERAGE(C8:H11)</f>
         <v>7.8650000000000002</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="55"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="55"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="60"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="60"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="13">
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J3:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J13:L13"/>
     <mergeCell ref="D8:F14"/>
     <mergeCell ref="G8:H14"/>
     <mergeCell ref="C7:D7"/>
@@ -39400,6 +39411,11 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J3:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J13:L13"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -39474,7 +39490,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075695DB-D9A0-44CD-9351-DFD9650BFBF6}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:T641"/>
+  <dimension ref="A1:S631"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -39494,11 +39510,10 @@
     <col min="15" max="15" width="83.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="64.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="1.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="95" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -39550,14 +39565,14 @@
       <c r="Q1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="69" t="s">
+      <c r="R1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="73" t="s">
+      <c r="S1" s="92" t="s">
         <v>2302</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -39581,13 +39596,13 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="13"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="2" t="e">
+      <c r="R2" s="48"/>
+      <c r="S2" s="93" t="e">
         <f t="shared" ref="S2:S65" si="0">AVERAGE(M2:P2)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -39633,16 +39648,13 @@
         <v>2249</v>
       </c>
       <c r="Q3" s="16"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="2">
+      <c r="R3" s="49"/>
+      <c r="S3" s="93">
         <f t="shared" si="0"/>
         <v>6.2</v>
       </c>
-      <c r="T3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -39668,13 +39680,13 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="16"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="2" t="e">
+      <c r="R4" s="49"/>
+      <c r="S4" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -39720,13 +39732,13 @@
         <v>6.39</v>
       </c>
       <c r="Q5" s="16"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="2">
+      <c r="R5" s="49"/>
+      <c r="S5" s="93">
         <f t="shared" si="0"/>
         <v>6.41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -39758,13 +39770,13 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="16"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="2">
+      <c r="R6" s="49"/>
+      <c r="S6" s="93">
         <f t="shared" si="0"/>
         <v>8.77</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -39810,13 +39822,13 @@
         <v>7.32</v>
       </c>
       <c r="Q7" s="16"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="2">
+      <c r="R7" s="49"/>
+      <c r="S7" s="93">
         <f t="shared" si="0"/>
         <v>8.0449999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -39862,13 +39874,13 @@
         <v>7.55</v>
       </c>
       <c r="Q8" s="16"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="2">
+      <c r="R8" s="49"/>
+      <c r="S8" s="93">
         <f t="shared" si="0"/>
         <v>7.7824999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -39914,13 +39926,13 @@
         <v>6.66</v>
       </c>
       <c r="Q9" s="16"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="2">
+      <c r="R9" s="49"/>
+      <c r="S9" s="93">
         <f t="shared" si="0"/>
         <v>6.66</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -39966,13 +39978,13 @@
         <v>6.25</v>
       </c>
       <c r="Q10" s="16"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="2">
+      <c r="R10" s="49"/>
+      <c r="S10" s="93">
         <f t="shared" si="0"/>
         <v>6.8075000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -40018,13 +40030,13 @@
         <v>7.41</v>
       </c>
       <c r="Q11" s="16"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="2">
+      <c r="R11" s="49"/>
+      <c r="S11" s="93">
         <f t="shared" si="0"/>
         <v>7.9450000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -40070,13 +40082,13 @@
         <v>7.11</v>
       </c>
       <c r="Q12" s="16"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="2">
+      <c r="R12" s="49"/>
+      <c r="S12" s="93">
         <f t="shared" si="0"/>
         <v>7.88</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -40122,13 +40134,13 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="Q13" s="16"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="2">
+      <c r="R13" s="49"/>
+      <c r="S13" s="93">
         <f t="shared" si="0"/>
         <v>9.09</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -40162,13 +40174,13 @@
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="16"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="2">
+      <c r="R14" s="49"/>
+      <c r="S14" s="93">
         <f t="shared" si="0"/>
         <v>8.73</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -40198,13 +40210,13 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="16"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="2" t="e">
+      <c r="R15" s="49"/>
+      <c r="S15" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -40248,8 +40260,8 @@
         <v>8.14</v>
       </c>
       <c r="Q16" s="16"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="2">
+      <c r="R16" s="49"/>
+      <c r="S16" s="93">
         <f t="shared" si="0"/>
         <v>8.1533333333333342</v>
       </c>
@@ -40298,8 +40310,8 @@
         <v>2250</v>
       </c>
       <c r="Q17" s="16"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="2">
+      <c r="R17" s="49"/>
+      <c r="S17" s="93">
         <f t="shared" si="0"/>
         <v>6.8599999999999994</v>
       </c>
@@ -40350,8 +40362,8 @@
         <v>2251</v>
       </c>
       <c r="Q18" s="16"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="2">
+      <c r="R18" s="49"/>
+      <c r="S18" s="93">
         <f t="shared" si="0"/>
         <v>6.07</v>
       </c>
@@ -40402,8 +40414,8 @@
         <v>2252</v>
       </c>
       <c r="Q19" s="16"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="2">
+      <c r="R19" s="49"/>
+      <c r="S19" s="93">
         <f t="shared" si="0"/>
         <v>6.7850000000000001</v>
       </c>
@@ -40454,8 +40466,8 @@
         <v>8.82</v>
       </c>
       <c r="Q20" s="16"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="2">
+      <c r="R20" s="49"/>
+      <c r="S20" s="93">
         <f t="shared" si="0"/>
         <v>8.8425000000000011</v>
       </c>
@@ -40490,8 +40502,8 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="16"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="2" t="e">
+      <c r="R21" s="49"/>
+      <c r="S21" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -40532,8 +40544,8 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="16"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="2" t="e">
+      <c r="R22" s="49"/>
+      <c r="S22" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -40582,8 +40594,8 @@
         <v>2253</v>
       </c>
       <c r="Q23" s="16"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="2">
+      <c r="R23" s="49"/>
+      <c r="S23" s="93">
         <f t="shared" si="0"/>
         <v>6.91</v>
       </c>
@@ -40634,8 +40646,8 @@
         <v>7.95</v>
       </c>
       <c r="Q24" s="16"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="2">
+      <c r="R24" s="49"/>
+      <c r="S24" s="93">
         <f t="shared" si="0"/>
         <v>8.0266666666666655</v>
       </c>
@@ -40664,8 +40676,8 @@
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="16"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="2" t="e">
+      <c r="R25" s="49"/>
+      <c r="S25" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -40716,8 +40728,8 @@
         <v>2254</v>
       </c>
       <c r="Q26" s="16"/>
-      <c r="R26" s="71"/>
-      <c r="S26" s="2">
+      <c r="R26" s="49"/>
+      <c r="S26" s="93">
         <f t="shared" si="0"/>
         <v>6.7149999999999999</v>
       </c>
@@ -40768,8 +40780,8 @@
         <v>6.68</v>
       </c>
       <c r="Q27" s="16"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="2">
+      <c r="R27" s="49"/>
+      <c r="S27" s="93">
         <f t="shared" si="0"/>
         <v>7.4225000000000003</v>
       </c>
@@ -40820,8 +40832,8 @@
         <v>953</v>
       </c>
       <c r="Q28" s="16"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="2">
+      <c r="R28" s="49"/>
+      <c r="S28" s="93">
         <f t="shared" si="0"/>
         <v>7.27</v>
       </c>
@@ -40872,8 +40884,8 @@
         <v>5.8</v>
       </c>
       <c r="Q29" s="16"/>
-      <c r="R29" s="71"/>
-      <c r="S29" s="2">
+      <c r="R29" s="49"/>
+      <c r="S29" s="93">
         <f t="shared" si="0"/>
         <v>6.2750000000000004</v>
       </c>
@@ -40922,8 +40934,8 @@
         <v>2255</v>
       </c>
       <c r="Q30" s="16"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="2" t="e">
+      <c r="R30" s="49"/>
+      <c r="S30" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -40974,8 +40986,8 @@
         <v>7.59</v>
       </c>
       <c r="Q31" s="16"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="2">
+      <c r="R31" s="49"/>
+      <c r="S31" s="93">
         <f t="shared" si="0"/>
         <v>7.59</v>
       </c>
@@ -41026,8 +41038,8 @@
         <v>9.32</v>
       </c>
       <c r="Q32" s="16"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="2">
+      <c r="R32" s="49"/>
+      <c r="S32" s="93">
         <f t="shared" si="0"/>
         <v>9.1349999999999998</v>
       </c>
@@ -41078,8 +41090,8 @@
         <v>954</v>
       </c>
       <c r="Q33" s="16"/>
-      <c r="R33" s="71"/>
-      <c r="S33" s="2">
+      <c r="R33" s="49"/>
+      <c r="S33" s="93">
         <f t="shared" si="0"/>
         <v>7.84</v>
       </c>
@@ -41130,8 +41142,8 @@
         <v>2253</v>
       </c>
       <c r="Q34" s="16"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="2">
+      <c r="R34" s="49"/>
+      <c r="S34" s="93">
         <f t="shared" si="0"/>
         <v>7.32</v>
       </c>
@@ -41182,8 +41194,8 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="Q35" s="16"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="2">
+      <c r="R35" s="49"/>
+      <c r="S35" s="93">
         <f t="shared" si="0"/>
         <v>8.5449999999999999</v>
       </c>
@@ -41214,8 +41226,8 @@
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="16"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="2" t="e">
+      <c r="R36" s="49"/>
+      <c r="S36" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -41266,8 +41278,8 @@
         <v>8</v>
       </c>
       <c r="Q37" s="16"/>
-      <c r="R37" s="71"/>
-      <c r="S37" s="2">
+      <c r="R37" s="49"/>
+      <c r="S37" s="93">
         <f t="shared" si="0"/>
         <v>7.915</v>
       </c>
@@ -41318,8 +41330,8 @@
         <v>7.36</v>
       </c>
       <c r="Q38" s="16"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="2">
+      <c r="R38" s="49"/>
+      <c r="S38" s="93">
         <f t="shared" si="0"/>
         <v>7.36</v>
       </c>
@@ -41370,8 +41382,8 @@
         <v>6.3</v>
       </c>
       <c r="Q39" s="16"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="2">
+      <c r="R39" s="49"/>
+      <c r="S39" s="93">
         <f t="shared" si="0"/>
         <v>6.16</v>
       </c>
@@ -41422,8 +41434,8 @@
         <v>8.23</v>
       </c>
       <c r="Q40" s="16"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="2">
+      <c r="R40" s="49"/>
+      <c r="S40" s="93">
         <f t="shared" si="0"/>
         <v>7.6425000000000001</v>
       </c>
@@ -41474,8 +41486,8 @@
         <v>953</v>
       </c>
       <c r="Q41" s="16"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="2" t="e">
+      <c r="R41" s="49"/>
+      <c r="S41" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -41524,8 +41536,8 @@
         <v>6.27</v>
       </c>
       <c r="Q42" s="16"/>
-      <c r="R42" s="71"/>
-      <c r="S42" s="2">
+      <c r="R42" s="49"/>
+      <c r="S42" s="93">
         <f t="shared" si="0"/>
         <v>6.5366666666666662</v>
       </c>
@@ -41554,8 +41566,8 @@
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="16"/>
-      <c r="R43" s="71"/>
-      <c r="S43" s="2" t="e">
+      <c r="R43" s="49"/>
+      <c r="S43" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -41606,8 +41618,8 @@
         <v>6.64</v>
       </c>
       <c r="Q44" s="16"/>
-      <c r="R44" s="71"/>
-      <c r="S44" s="2">
+      <c r="R44" s="49"/>
+      <c r="S44" s="93">
         <f t="shared" si="0"/>
         <v>6.64</v>
       </c>
@@ -41658,8 +41670,8 @@
         <v>9.73</v>
       </c>
       <c r="Q45" s="16"/>
-      <c r="R45" s="71"/>
-      <c r="S45" s="2">
+      <c r="R45" s="49"/>
+      <c r="S45" s="93">
         <f t="shared" si="0"/>
         <v>9.2175000000000011</v>
       </c>
@@ -41710,8 +41722,8 @@
         <v>7.05</v>
       </c>
       <c r="Q46" s="16"/>
-      <c r="R46" s="71"/>
-      <c r="S46" s="2">
+      <c r="R46" s="49"/>
+      <c r="S46" s="93">
         <f t="shared" si="0"/>
         <v>7.5633333333333335</v>
       </c>
@@ -41762,8 +41774,8 @@
         <v>5.91</v>
       </c>
       <c r="Q47" s="16"/>
-      <c r="R47" s="71"/>
-      <c r="S47" s="2">
+      <c r="R47" s="49"/>
+      <c r="S47" s="93">
         <f t="shared" si="0"/>
         <v>5.96</v>
       </c>
@@ -41812,8 +41824,8 @@
         <v>954</v>
       </c>
       <c r="Q48" s="16"/>
-      <c r="R48" s="71"/>
-      <c r="S48" s="2" t="e">
+      <c r="R48" s="49"/>
+      <c r="S48" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -41864,8 +41876,8 @@
         <v>2256</v>
       </c>
       <c r="Q49" s="16"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="2" t="e">
+      <c r="R49" s="49"/>
+      <c r="S49" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -41916,8 +41928,8 @@
         <v>7.07</v>
       </c>
       <c r="Q50" s="16"/>
-      <c r="R50" s="71"/>
-      <c r="S50" s="2">
+      <c r="R50" s="49"/>
+      <c r="S50" s="93">
         <f t="shared" si="0"/>
         <v>7.08</v>
       </c>
@@ -41968,8 +41980,8 @@
         <v>6.64</v>
       </c>
       <c r="Q51" s="16"/>
-      <c r="R51" s="71"/>
-      <c r="S51" s="2">
+      <c r="R51" s="49"/>
+      <c r="S51" s="93">
         <f t="shared" si="0"/>
         <v>6.64</v>
       </c>
@@ -42020,8 +42032,8 @@
         <v>9</v>
       </c>
       <c r="Q52" s="16"/>
-      <c r="R52" s="71"/>
-      <c r="S52" s="2">
+      <c r="R52" s="49"/>
+      <c r="S52" s="93">
         <f t="shared" si="0"/>
         <v>9.01</v>
       </c>
@@ -42072,8 +42084,8 @@
         <v>9</v>
       </c>
       <c r="Q53" s="16"/>
-      <c r="R53" s="71"/>
-      <c r="S53" s="2">
+      <c r="R53" s="49"/>
+      <c r="S53" s="93">
         <f t="shared" si="0"/>
         <v>8.5549999999999997</v>
       </c>
@@ -42124,8 +42136,8 @@
         <v>954</v>
       </c>
       <c r="Q54" s="16"/>
-      <c r="R54" s="71"/>
-      <c r="S54" s="2" t="e">
+      <c r="R54" s="49"/>
+      <c r="S54" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -42176,8 +42188,8 @@
         <v>2257</v>
       </c>
       <c r="Q55" s="16"/>
-      <c r="R55" s="71"/>
-      <c r="S55" s="2">
+      <c r="R55" s="49"/>
+      <c r="S55" s="93">
         <f t="shared" si="0"/>
         <v>6.6349999999999998</v>
       </c>
@@ -42226,8 +42238,8 @@
         <v>7.18</v>
       </c>
       <c r="Q56" s="16"/>
-      <c r="R56" s="71"/>
-      <c r="S56" s="2">
+      <c r="R56" s="49"/>
+      <c r="S56" s="93">
         <f t="shared" si="0"/>
         <v>7.5225</v>
       </c>
@@ -42256,8 +42268,8 @@
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" s="16"/>
-      <c r="R57" s="71"/>
-      <c r="S57" s="2" t="e">
+      <c r="R57" s="49"/>
+      <c r="S57" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -42308,8 +42320,8 @@
         <v>7.64</v>
       </c>
       <c r="Q58" s="16"/>
-      <c r="R58" s="71"/>
-      <c r="S58" s="2">
+      <c r="R58" s="49"/>
+      <c r="S58" s="93">
         <f t="shared" si="0"/>
         <v>7.2733333333333334</v>
       </c>
@@ -42358,8 +42370,8 @@
         <v>954</v>
       </c>
       <c r="Q59" s="16"/>
-      <c r="R59" s="71"/>
-      <c r="S59" s="2" t="e">
+      <c r="R59" s="49"/>
+      <c r="S59" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -42410,8 +42422,8 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="Q60" s="16"/>
-      <c r="R60" s="71"/>
-      <c r="S60" s="2">
+      <c r="R60" s="49"/>
+      <c r="S60" s="93">
         <f t="shared" si="0"/>
         <v>8.1366666666666667</v>
       </c>
@@ -42462,8 +42474,8 @@
         <v>7.75</v>
       </c>
       <c r="Q61" s="16"/>
-      <c r="R61" s="71"/>
-      <c r="S61" s="2">
+      <c r="R61" s="49"/>
+      <c r="S61" s="93">
         <f t="shared" si="0"/>
         <v>7.5274999999999999</v>
       </c>
@@ -42514,8 +42526,8 @@
         <v>954</v>
       </c>
       <c r="Q62" s="16"/>
-      <c r="R62" s="71"/>
-      <c r="S62" s="2" t="e">
+      <c r="R62" s="49"/>
+      <c r="S62" s="93" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -42566,8 +42578,8 @@
         <v>8.14</v>
       </c>
       <c r="Q63" s="16"/>
-      <c r="R63" s="71"/>
-      <c r="S63" s="2">
+      <c r="R63" s="49"/>
+      <c r="S63" s="93">
         <f t="shared" si="0"/>
         <v>7.7975000000000003</v>
       </c>
@@ -42616,8 +42628,8 @@
         <v>953</v>
       </c>
       <c r="Q64" s="16"/>
-      <c r="R64" s="71"/>
-      <c r="S64" s="2">
+      <c r="R64" s="49"/>
+      <c r="S64" s="93">
         <f t="shared" si="0"/>
         <v>5.98</v>
       </c>
@@ -42666,8 +42678,8 @@
         <v>954</v>
       </c>
       <c r="Q65" s="16"/>
-      <c r="R65" s="71"/>
-      <c r="S65" s="2">
+      <c r="R65" s="49"/>
+      <c r="S65" s="93">
         <f t="shared" si="0"/>
         <v>6.09</v>
       </c>
@@ -42718,8 +42730,8 @@
         <v>9.27</v>
       </c>
       <c r="Q66" s="16"/>
-      <c r="R66" s="71"/>
-      <c r="S66" s="2">
+      <c r="R66" s="49"/>
+      <c r="S66" s="93">
         <f t="shared" ref="S66:S129" si="1">AVERAGE(M66:P66)</f>
         <v>8.76</v>
       </c>
@@ -42770,8 +42782,8 @@
         <v>8.91</v>
       </c>
       <c r="Q67" s="16"/>
-      <c r="R67" s="71"/>
-      <c r="S67" s="2">
+      <c r="R67" s="49"/>
+      <c r="S67" s="93">
         <f t="shared" si="1"/>
         <v>8.625</v>
       </c>
@@ -42822,8 +42834,8 @@
         <v>7.86</v>
       </c>
       <c r="Q68" s="16"/>
-      <c r="R68" s="71"/>
-      <c r="S68" s="2">
+      <c r="R68" s="49"/>
+      <c r="S68" s="93">
         <f t="shared" si="1"/>
         <v>7.7374999999999998</v>
       </c>
@@ -42874,8 +42886,8 @@
         <v>2249</v>
       </c>
       <c r="Q69" s="16"/>
-      <c r="R69" s="71"/>
-      <c r="S69" s="2">
+      <c r="R69" s="49"/>
+      <c r="S69" s="93">
         <f t="shared" si="1"/>
         <v>6.5</v>
       </c>
@@ -42904,8 +42916,8 @@
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="16"/>
-      <c r="R70" s="71"/>
-      <c r="S70" s="2" t="e">
+      <c r="R70" s="49"/>
+      <c r="S70" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -42948,8 +42960,8 @@
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="16"/>
-      <c r="R71" s="71"/>
-      <c r="S71" s="2">
+      <c r="R71" s="49"/>
+      <c r="S71" s="93">
         <f t="shared" si="1"/>
         <v>6.77</v>
       </c>
@@ -42998,8 +43010,8 @@
         <v>954</v>
       </c>
       <c r="Q72" s="16"/>
-      <c r="R72" s="71"/>
-      <c r="S72" s="2">
+      <c r="R72" s="49"/>
+      <c r="S72" s="93">
         <f t="shared" si="1"/>
         <v>6.86</v>
       </c>
@@ -43050,8 +43062,8 @@
         <v>2258</v>
       </c>
       <c r="Q73" s="16"/>
-      <c r="R73" s="71"/>
-      <c r="S73" s="2">
+      <c r="R73" s="49"/>
+      <c r="S73" s="93">
         <f t="shared" si="1"/>
         <v>6.34</v>
       </c>
@@ -43094,8 +43106,8 @@
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="16"/>
-      <c r="R74" s="71"/>
-      <c r="S74" s="2">
+      <c r="R74" s="49"/>
+      <c r="S74" s="93">
         <f t="shared" si="1"/>
         <v>7.5549999999999997</v>
       </c>
@@ -43140,8 +43152,8 @@
         <v>954</v>
       </c>
       <c r="Q75" s="16"/>
-      <c r="R75" s="71"/>
-      <c r="S75" s="2">
+      <c r="R75" s="49"/>
+      <c r="S75" s="93">
         <f t="shared" si="1"/>
         <v>6.66</v>
       </c>
@@ -43178,8 +43190,8 @@
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="16"/>
-      <c r="R76" s="71"/>
-      <c r="S76" s="2">
+      <c r="R76" s="49"/>
+      <c r="S76" s="93">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -43208,8 +43220,8 @@
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
       <c r="Q77" s="16"/>
-      <c r="R77" s="71"/>
-      <c r="S77" s="2" t="e">
+      <c r="R77" s="49"/>
+      <c r="S77" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -43260,8 +43272,8 @@
         <v>9.18</v>
       </c>
       <c r="Q78" s="16"/>
-      <c r="R78" s="71"/>
-      <c r="S78" s="2">
+      <c r="R78" s="49"/>
+      <c r="S78" s="93">
         <f t="shared" si="1"/>
         <v>8.83</v>
       </c>
@@ -43310,8 +43322,8 @@
         <v>6.5</v>
       </c>
       <c r="Q79" s="16"/>
-      <c r="R79" s="71"/>
-      <c r="S79" s="2">
+      <c r="R79" s="49"/>
+      <c r="S79" s="93">
         <f t="shared" si="1"/>
         <v>6.49</v>
       </c>
@@ -43362,8 +43374,8 @@
         <v>8.91</v>
       </c>
       <c r="Q80" s="16"/>
-      <c r="R80" s="71"/>
-      <c r="S80" s="2">
+      <c r="R80" s="49"/>
+      <c r="S80" s="93">
         <f t="shared" si="1"/>
         <v>8.6349999999999998</v>
       </c>
@@ -43414,8 +43426,8 @@
         <v>954</v>
       </c>
       <c r="Q81" s="16"/>
-      <c r="R81" s="71"/>
-      <c r="S81" s="2">
+      <c r="R81" s="49"/>
+      <c r="S81" s="93">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -43454,8 +43466,8 @@
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
       <c r="Q82" s="16"/>
-      <c r="R82" s="71"/>
-      <c r="S82" s="2" t="e">
+      <c r="R82" s="49"/>
+      <c r="S82" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -43506,8 +43518,8 @@
         <v>8.18</v>
       </c>
       <c r="Q83" s="16"/>
-      <c r="R83" s="71"/>
-      <c r="S83" s="2">
+      <c r="R83" s="49"/>
+      <c r="S83" s="93">
         <f t="shared" si="1"/>
         <v>7.5649999999999995</v>
       </c>
@@ -43558,8 +43570,8 @@
         <v>7.73</v>
       </c>
       <c r="Q84" s="16"/>
-      <c r="R84" s="71"/>
-      <c r="S84" s="2">
+      <c r="R84" s="49"/>
+      <c r="S84" s="93">
         <f t="shared" si="1"/>
         <v>7.5333333333333341</v>
       </c>
@@ -43610,8 +43622,8 @@
         <v>8.86</v>
       </c>
       <c r="Q85" s="16"/>
-      <c r="R85" s="71"/>
-      <c r="S85" s="2">
+      <c r="R85" s="49"/>
+      <c r="S85" s="93">
         <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
@@ -43662,8 +43674,8 @@
         <v>7.43</v>
       </c>
       <c r="Q86" s="16"/>
-      <c r="R86" s="71"/>
-      <c r="S86" s="2">
+      <c r="R86" s="49"/>
+      <c r="S86" s="93">
         <f t="shared" si="1"/>
         <v>7.3250000000000002</v>
       </c>
@@ -43714,8 +43726,8 @@
         <v>7</v>
       </c>
       <c r="Q87" s="16"/>
-      <c r="R87" s="71"/>
-      <c r="S87" s="2">
+      <c r="R87" s="49"/>
+      <c r="S87" s="93">
         <f t="shared" si="1"/>
         <v>7.0049999999999999</v>
       </c>
@@ -43766,8 +43778,8 @@
         <v>6.48</v>
       </c>
       <c r="Q88" s="16"/>
-      <c r="R88" s="71"/>
-      <c r="S88" s="2">
+      <c r="R88" s="49"/>
+      <c r="S88" s="93">
         <f t="shared" si="1"/>
         <v>6.7725</v>
       </c>
@@ -43818,8 +43830,8 @@
         <v>2259</v>
       </c>
       <c r="Q89" s="16"/>
-      <c r="R89" s="71"/>
-      <c r="S89" s="2">
+      <c r="R89" s="49"/>
+      <c r="S89" s="93">
         <f t="shared" si="1"/>
         <v>6.09</v>
       </c>
@@ -43858,8 +43870,8 @@
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="Q90" s="16"/>
-      <c r="R90" s="71"/>
-      <c r="S90" s="2">
+      <c r="R90" s="49"/>
+      <c r="S90" s="93">
         <f t="shared" si="1"/>
         <v>6.3</v>
       </c>
@@ -43910,8 +43922,8 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="Q91" s="16"/>
-      <c r="R91" s="71"/>
-      <c r="S91" s="2">
+      <c r="R91" s="49"/>
+      <c r="S91" s="93">
         <f t="shared" si="1"/>
         <v>9.24</v>
       </c>
@@ -43962,8 +43974,8 @@
         <v>8.27</v>
       </c>
       <c r="Q92" s="16"/>
-      <c r="R92" s="71"/>
-      <c r="S92" s="2">
+      <c r="R92" s="49"/>
+      <c r="S92" s="93">
         <f t="shared" si="1"/>
         <v>8.067499999999999</v>
       </c>
@@ -44014,8 +44026,8 @@
         <v>6.45</v>
       </c>
       <c r="Q93" s="16"/>
-      <c r="R93" s="71"/>
-      <c r="S93" s="2">
+      <c r="R93" s="49"/>
+      <c r="S93" s="93">
         <f t="shared" si="1"/>
         <v>6.88</v>
       </c>
@@ -44066,8 +44078,8 @@
         <v>2249</v>
       </c>
       <c r="Q94" s="16"/>
-      <c r="R94" s="71"/>
-      <c r="S94" s="2">
+      <c r="R94" s="49"/>
+      <c r="S94" s="93">
         <f t="shared" si="1"/>
         <v>5.9333333333333336</v>
       </c>
@@ -44118,8 +44130,8 @@
         <v>7.91</v>
       </c>
       <c r="Q95" s="16"/>
-      <c r="R95" s="71"/>
-      <c r="S95" s="2">
+      <c r="R95" s="49"/>
+      <c r="S95" s="93">
         <f t="shared" si="1"/>
         <v>8.2274999999999991</v>
       </c>
@@ -44170,8 +44182,8 @@
         <v>2260</v>
       </c>
       <c r="Q96" s="16"/>
-      <c r="R96" s="71"/>
-      <c r="S96" s="2">
+      <c r="R96" s="49"/>
+      <c r="S96" s="93">
         <f t="shared" si="1"/>
         <v>5.64</v>
       </c>
@@ -44222,8 +44234,8 @@
         <v>6.93</v>
       </c>
       <c r="Q97" s="16"/>
-      <c r="R97" s="71"/>
-      <c r="S97" s="2">
+      <c r="R97" s="49"/>
+      <c r="S97" s="93">
         <f t="shared" si="1"/>
         <v>6.9550000000000001</v>
       </c>
@@ -44274,8 +44286,8 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="Q98" s="16"/>
-      <c r="R98" s="71"/>
-      <c r="S98" s="2">
+      <c r="R98" s="49"/>
+      <c r="S98" s="93">
         <f t="shared" si="1"/>
         <v>8.1875</v>
       </c>
@@ -44310,8 +44322,8 @@
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
       <c r="Q99" s="16"/>
-      <c r="R99" s="71"/>
-      <c r="S99" s="2" t="e">
+      <c r="R99" s="49"/>
+      <c r="S99" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -44348,8 +44360,8 @@
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="16"/>
-      <c r="R100" s="71"/>
-      <c r="S100" s="2" t="e">
+      <c r="R100" s="49"/>
+      <c r="S100" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -44400,8 +44412,8 @@
         <v>7.55</v>
       </c>
       <c r="Q101" s="16"/>
-      <c r="R101" s="71"/>
-      <c r="S101" s="2">
+      <c r="R101" s="49"/>
+      <c r="S101" s="93">
         <f t="shared" si="1"/>
         <v>7.2225000000000001</v>
       </c>
@@ -44452,8 +44464,8 @@
         <v>8.86</v>
       </c>
       <c r="Q102" s="16"/>
-      <c r="R102" s="71"/>
-      <c r="S102" s="2">
+      <c r="R102" s="49"/>
+      <c r="S102" s="93">
         <f t="shared" si="1"/>
         <v>8.26</v>
       </c>
@@ -44492,8 +44504,8 @@
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
       <c r="Q103" s="16"/>
-      <c r="R103" s="71"/>
-      <c r="S103" s="2">
+      <c r="R103" s="49"/>
+      <c r="S103" s="93">
         <f t="shared" si="1"/>
         <v>6.36</v>
       </c>
@@ -44544,8 +44556,8 @@
         <v>2253</v>
       </c>
       <c r="Q104" s="16"/>
-      <c r="R104" s="71"/>
-      <c r="S104" s="2">
+      <c r="R104" s="49"/>
+      <c r="S104" s="93">
         <f t="shared" si="1"/>
         <v>6.2666666666666666</v>
       </c>
@@ -44596,8 +44608,8 @@
         <v>8.18</v>
       </c>
       <c r="Q105" s="16"/>
-      <c r="R105" s="71"/>
-      <c r="S105" s="2">
+      <c r="R105" s="49"/>
+      <c r="S105" s="93">
         <f t="shared" si="1"/>
         <v>7.4775</v>
       </c>
@@ -44648,8 +44660,8 @@
         <v>6.8</v>
       </c>
       <c r="Q106" s="16"/>
-      <c r="R106" s="71"/>
-      <c r="S106" s="2">
+      <c r="R106" s="49"/>
+      <c r="S106" s="93">
         <f t="shared" si="1"/>
         <v>6.8025000000000002</v>
       </c>
@@ -44698,8 +44710,8 @@
         <v>5.89</v>
       </c>
       <c r="Q107" s="16"/>
-      <c r="R107" s="71"/>
-      <c r="S107" s="2">
+      <c r="R107" s="49"/>
+      <c r="S107" s="93">
         <f t="shared" si="1"/>
         <v>5.82</v>
       </c>
@@ -44750,8 +44762,8 @@
         <v>8</v>
       </c>
       <c r="Q108" s="16"/>
-      <c r="R108" s="71"/>
-      <c r="S108" s="2">
+      <c r="R108" s="49"/>
+      <c r="S108" s="93">
         <f t="shared" si="1"/>
         <v>7.7725</v>
       </c>
@@ -44802,8 +44814,8 @@
         <v>953</v>
       </c>
       <c r="Q109" s="16"/>
-      <c r="R109" s="71"/>
-      <c r="S109" s="2">
+      <c r="R109" s="49"/>
+      <c r="S109" s="93">
         <f t="shared" si="1"/>
         <v>5.9649999999999999</v>
       </c>
@@ -44854,8 +44866,8 @@
         <v>2261</v>
       </c>
       <c r="Q110" s="16"/>
-      <c r="R110" s="71"/>
-      <c r="S110" s="2" t="e">
+      <c r="R110" s="49"/>
+      <c r="S110" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -44906,8 +44918,8 @@
         <v>7.91</v>
       </c>
       <c r="Q111" s="16"/>
-      <c r="R111" s="71"/>
-      <c r="S111" s="2">
+      <c r="R111" s="49"/>
+      <c r="S111" s="93">
         <f t="shared" si="1"/>
         <v>7.57</v>
       </c>
@@ -44958,8 +44970,8 @@
         <v>6</v>
       </c>
       <c r="Q112" s="16"/>
-      <c r="R112" s="71"/>
-      <c r="S112" s="2">
+      <c r="R112" s="49"/>
+      <c r="S112" s="93">
         <f t="shared" si="1"/>
         <v>5.9866666666666672</v>
       </c>
@@ -45010,8 +45022,8 @@
         <v>6.25</v>
       </c>
       <c r="Q113" s="16"/>
-      <c r="R113" s="71"/>
-      <c r="S113" s="2">
+      <c r="R113" s="49"/>
+      <c r="S113" s="93">
         <f t="shared" si="1"/>
         <v>5.96</v>
       </c>
@@ -45062,8 +45074,8 @@
         <v>9</v>
       </c>
       <c r="Q114" s="16"/>
-      <c r="R114" s="71"/>
-      <c r="S114" s="2">
+      <c r="R114" s="49"/>
+      <c r="S114" s="93">
         <f t="shared" si="1"/>
         <v>9.1125000000000007</v>
       </c>
@@ -45114,8 +45126,8 @@
         <v>8.91</v>
       </c>
       <c r="Q115" s="16"/>
-      <c r="R115" s="71"/>
-      <c r="S115" s="2">
+      <c r="R115" s="49"/>
+      <c r="S115" s="93">
         <f t="shared" si="1"/>
         <v>8.9774999999999991</v>
       </c>
@@ -45166,8 +45178,8 @@
         <v>7.25</v>
       </c>
       <c r="Q116" s="16"/>
-      <c r="R116" s="71"/>
-      <c r="S116" s="2">
+      <c r="R116" s="49"/>
+      <c r="S116" s="93">
         <f t="shared" si="1"/>
         <v>7.4950000000000001</v>
       </c>
@@ -45218,8 +45230,8 @@
         <v>8.91</v>
       </c>
       <c r="Q117" s="16"/>
-      <c r="R117" s="71"/>
-      <c r="S117" s="2">
+      <c r="R117" s="49"/>
+      <c r="S117" s="93">
         <f t="shared" si="1"/>
         <v>8.375</v>
       </c>
@@ -45270,8 +45282,8 @@
         <v>6.27</v>
       </c>
       <c r="Q118" s="16"/>
-      <c r="R118" s="71"/>
-      <c r="S118" s="2">
+      <c r="R118" s="49"/>
+      <c r="S118" s="93">
         <f t="shared" si="1"/>
         <v>6.5733333333333333</v>
       </c>
@@ -45322,8 +45334,8 @@
         <v>8</v>
       </c>
       <c r="Q119" s="16"/>
-      <c r="R119" s="71"/>
-      <c r="S119" s="2">
+      <c r="R119" s="49"/>
+      <c r="S119" s="93">
         <f t="shared" si="1"/>
         <v>7.85</v>
       </c>
@@ -45358,8 +45370,8 @@
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
       <c r="Q120" s="16"/>
-      <c r="R120" s="71"/>
-      <c r="S120" s="2" t="e">
+      <c r="R120" s="49"/>
+      <c r="S120" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -45396,8 +45408,8 @@
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" s="16"/>
-      <c r="R121" s="71"/>
-      <c r="S121" s="2" t="e">
+      <c r="R121" s="49"/>
+      <c r="S121" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -45434,8 +45446,8 @@
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
       <c r="Q122" s="16"/>
-      <c r="R122" s="71"/>
-      <c r="S122" s="2">
+      <c r="R122" s="49"/>
+      <c r="S122" s="93">
         <f t="shared" si="1"/>
         <v>8.09</v>
       </c>
@@ -45474,8 +45486,8 @@
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
       <c r="Q123" s="16"/>
-      <c r="R123" s="71"/>
-      <c r="S123" s="2">
+      <c r="R123" s="49"/>
+      <c r="S123" s="93">
         <f t="shared" si="1"/>
         <v>5.84</v>
       </c>
@@ -45526,8 +45538,8 @@
         <v>8.18</v>
       </c>
       <c r="Q124" s="16"/>
-      <c r="R124" s="71"/>
-      <c r="S124" s="2">
+      <c r="R124" s="49"/>
+      <c r="S124" s="93">
         <f t="shared" si="1"/>
         <v>8.2050000000000001</v>
       </c>
@@ -45578,8 +45590,8 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="Q125" s="16"/>
-      <c r="R125" s="71"/>
-      <c r="S125" s="2">
+      <c r="R125" s="49"/>
+      <c r="S125" s="93">
         <f t="shared" si="1"/>
         <v>8.4074999999999989</v>
       </c>
@@ -45630,8 +45642,8 @@
         <v>958</v>
       </c>
       <c r="Q126" s="16"/>
-      <c r="R126" s="71"/>
-      <c r="S126" s="2" t="e">
+      <c r="R126" s="49"/>
+      <c r="S126" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -45682,8 +45694,8 @@
         <v>954</v>
       </c>
       <c r="Q127" s="16"/>
-      <c r="R127" s="71"/>
-      <c r="S127" s="2" t="e">
+      <c r="R127" s="49"/>
+      <c r="S127" s="93" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
@@ -45734,8 +45746,8 @@
         <v>5.68</v>
       </c>
       <c r="Q128" s="16"/>
-      <c r="R128" s="71"/>
-      <c r="S128" s="2">
+      <c r="R128" s="49"/>
+      <c r="S128" s="93">
         <f t="shared" si="1"/>
         <v>5.875</v>
       </c>
@@ -45786,8 +45798,8 @@
         <v>5.98</v>
       </c>
       <c r="Q129" s="16"/>
-      <c r="R129" s="71"/>
-      <c r="S129" s="2">
+      <c r="R129" s="49"/>
+      <c r="S129" s="93">
         <f t="shared" si="1"/>
         <v>6.23</v>
       </c>
@@ -45822,8 +45834,8 @@
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
       <c r="Q130" s="16"/>
-      <c r="R130" s="71"/>
-      <c r="S130" s="2" t="e">
+      <c r="R130" s="49"/>
+      <c r="S130" s="93" t="e">
         <f t="shared" ref="S130:S193" si="2">AVERAGE(M130:P130)</f>
         <v>#DIV/0!</v>
       </c>
@@ -45874,8 +45886,8 @@
         <v>9</v>
       </c>
       <c r="Q131" s="16"/>
-      <c r="R131" s="71"/>
-      <c r="S131" s="2">
+      <c r="R131" s="49"/>
+      <c r="S131" s="93">
         <f t="shared" si="2"/>
         <v>9.1024999999999991</v>
       </c>
@@ -45926,8 +45938,8 @@
         <v>2262</v>
       </c>
       <c r="Q132" s="16"/>
-      <c r="R132" s="71"/>
-      <c r="S132" s="2">
+      <c r="R132" s="49"/>
+      <c r="S132" s="93">
         <f t="shared" si="2"/>
         <v>6.34</v>
       </c>
@@ -45978,8 +45990,8 @@
         <v>9.09</v>
       </c>
       <c r="Q133" s="16"/>
-      <c r="R133" s="71"/>
-      <c r="S133" s="2">
+      <c r="R133" s="49"/>
+      <c r="S133" s="93">
         <f t="shared" si="2"/>
         <v>9.5225000000000009</v>
       </c>
@@ -46030,8 +46042,8 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="Q134" s="16"/>
-      <c r="R134" s="71"/>
-      <c r="S134" s="2">
+      <c r="R134" s="49"/>
+      <c r="S134" s="93">
         <f t="shared" si="2"/>
         <v>8.4074999999999989</v>
       </c>
@@ -46082,8 +46094,8 @@
         <v>6.43</v>
       </c>
       <c r="Q135" s="16"/>
-      <c r="R135" s="71"/>
-      <c r="S135" s="2">
+      <c r="R135" s="49"/>
+      <c r="S135" s="93">
         <f t="shared" si="2"/>
         <v>6.5625</v>
       </c>
@@ -46134,8 +46146,8 @@
         <v>6.5</v>
       </c>
       <c r="Q136" s="16"/>
-      <c r="R136" s="71"/>
-      <c r="S136" s="2">
+      <c r="R136" s="49"/>
+      <c r="S136" s="93">
         <f t="shared" si="2"/>
         <v>6.7750000000000004</v>
       </c>
@@ -46186,8 +46198,8 @@
         <v>2250</v>
       </c>
       <c r="Q137" s="16"/>
-      <c r="R137" s="71"/>
-      <c r="S137" s="2">
+      <c r="R137" s="49"/>
+      <c r="S137" s="93">
         <f t="shared" si="2"/>
         <v>7.1850000000000005</v>
       </c>
@@ -46236,8 +46248,8 @@
         <v>6.09</v>
       </c>
       <c r="Q138" s="16"/>
-      <c r="R138" s="71"/>
-      <c r="S138" s="2">
+      <c r="R138" s="49"/>
+      <c r="S138" s="93">
         <f t="shared" si="2"/>
         <v>6.09</v>
       </c>
@@ -46288,8 +46300,8 @@
         <v>7.86</v>
       </c>
       <c r="Q139" s="16"/>
-      <c r="R139" s="71"/>
-      <c r="S139" s="2">
+      <c r="R139" s="49"/>
+      <c r="S139" s="93">
         <f t="shared" si="2"/>
         <v>7.666666666666667</v>
       </c>
@@ -46326,8 +46338,8 @@
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
       <c r="Q140" s="16"/>
-      <c r="R140" s="71"/>
-      <c r="S140" s="2" t="e">
+      <c r="R140" s="49"/>
+      <c r="S140" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -46378,8 +46390,8 @@
         <v>7.02</v>
       </c>
       <c r="Q141" s="16"/>
-      <c r="R141" s="71"/>
-      <c r="S141" s="2">
+      <c r="R141" s="49"/>
+      <c r="S141" s="93">
         <f t="shared" si="2"/>
         <v>6.9624999999999995</v>
       </c>
@@ -46430,8 +46442,8 @@
         <v>2250</v>
       </c>
       <c r="Q142" s="16"/>
-      <c r="R142" s="71"/>
-      <c r="S142" s="2">
+      <c r="R142" s="49"/>
+      <c r="S142" s="93">
         <f t="shared" si="2"/>
         <v>6.0150000000000006</v>
       </c>
@@ -46482,8 +46494,8 @@
         <v>8.73</v>
       </c>
       <c r="Q143" s="16"/>
-      <c r="R143" s="71"/>
-      <c r="S143" s="2">
+      <c r="R143" s="49"/>
+      <c r="S143" s="93">
         <f t="shared" si="2"/>
         <v>8.9</v>
       </c>
@@ -46534,8 +46546,8 @@
         <v>9.09</v>
       </c>
       <c r="Q144" s="16"/>
-      <c r="R144" s="71"/>
-      <c r="S144" s="2">
+      <c r="R144" s="49"/>
+      <c r="S144" s="93">
         <f t="shared" si="2"/>
         <v>8.817499999999999</v>
       </c>
@@ -46586,8 +46598,8 @@
         <v>8.09</v>
       </c>
       <c r="Q145" s="16"/>
-      <c r="R145" s="71"/>
-      <c r="S145" s="2">
+      <c r="R145" s="49"/>
+      <c r="S145" s="93">
         <f t="shared" si="2"/>
         <v>7.6574999999999998</v>
       </c>
@@ -46638,8 +46650,8 @@
         <v>7.91</v>
       </c>
       <c r="Q146" s="16"/>
-      <c r="R146" s="71"/>
-      <c r="S146" s="2">
+      <c r="R146" s="49"/>
+      <c r="S146" s="93">
         <f t="shared" si="2"/>
         <v>7.4124999999999996</v>
       </c>
@@ -46690,8 +46702,8 @@
         <v>7.18</v>
       </c>
       <c r="Q147" s="16"/>
-      <c r="R147" s="71"/>
-      <c r="S147" s="2">
+      <c r="R147" s="49"/>
+      <c r="S147" s="93">
         <f t="shared" si="2"/>
         <v>7.19</v>
       </c>
@@ -46742,8 +46754,8 @@
         <v>8.59</v>
       </c>
       <c r="Q148" s="16"/>
-      <c r="R148" s="71"/>
-      <c r="S148" s="2">
+      <c r="R148" s="49"/>
+      <c r="S148" s="93">
         <f t="shared" si="2"/>
         <v>8.6275000000000013</v>
       </c>
@@ -46794,8 +46806,8 @@
         <v>2263</v>
       </c>
       <c r="Q149" s="16"/>
-      <c r="R149" s="71"/>
-      <c r="S149" s="2">
+      <c r="R149" s="49"/>
+      <c r="S149" s="93">
         <f t="shared" si="2"/>
         <v>6.6466666666666674</v>
       </c>
@@ -46846,8 +46858,8 @@
         <v>6.02</v>
       </c>
       <c r="Q150" s="16"/>
-      <c r="R150" s="71"/>
-      <c r="S150" s="2">
+      <c r="R150" s="49"/>
+      <c r="S150" s="93">
         <f t="shared" si="2"/>
         <v>6.2349999999999994</v>
       </c>
@@ -46896,8 +46908,8 @@
         <v>954</v>
       </c>
       <c r="Q151" s="16"/>
-      <c r="R151" s="71"/>
-      <c r="S151" s="2" t="e">
+      <c r="R151" s="49"/>
+      <c r="S151" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -46948,8 +46960,8 @@
         <v>6.7</v>
       </c>
       <c r="Q152" s="16"/>
-      <c r="R152" s="71"/>
-      <c r="S152" s="2">
+      <c r="R152" s="49"/>
+      <c r="S152" s="93">
         <f t="shared" si="2"/>
         <v>6.7524999999999995</v>
       </c>
@@ -47000,8 +47012,8 @@
         <v>8.82</v>
       </c>
       <c r="Q153" s="16"/>
-      <c r="R153" s="71"/>
-      <c r="S153" s="2">
+      <c r="R153" s="49"/>
+      <c r="S153" s="93">
         <f t="shared" si="2"/>
         <v>8.5449999999999999</v>
       </c>
@@ -47038,8 +47050,8 @@
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
       <c r="Q154" s="16"/>
-      <c r="R154" s="71"/>
-      <c r="S154" s="2">
+      <c r="R154" s="49"/>
+      <c r="S154" s="93">
         <f t="shared" si="2"/>
         <v>9.14</v>
       </c>
@@ -47090,8 +47102,8 @@
         <v>6.23</v>
       </c>
       <c r="Q155" s="16"/>
-      <c r="R155" s="71"/>
-      <c r="S155" s="2">
+      <c r="R155" s="49"/>
+      <c r="S155" s="93">
         <f t="shared" si="2"/>
         <v>6.6375000000000002</v>
       </c>
@@ -47142,8 +47154,8 @@
         <v>2250</v>
       </c>
       <c r="Q156" s="16"/>
-      <c r="R156" s="71"/>
-      <c r="S156" s="2">
+      <c r="R156" s="49"/>
+      <c r="S156" s="93">
         <f t="shared" si="2"/>
         <v>7.0750000000000002</v>
       </c>
@@ -47194,8 +47206,8 @@
         <v>2264</v>
       </c>
       <c r="Q157" s="16"/>
-      <c r="R157" s="71"/>
-      <c r="S157" s="2">
+      <c r="R157" s="49"/>
+      <c r="S157" s="93">
         <f t="shared" si="2"/>
         <v>6.33</v>
       </c>
@@ -47246,8 +47258,8 @@
         <v>8.68</v>
       </c>
       <c r="Q158" s="16"/>
-      <c r="R158" s="71"/>
-      <c r="S158" s="2">
+      <c r="R158" s="49"/>
+      <c r="S158" s="93">
         <f t="shared" si="2"/>
         <v>8.84</v>
       </c>
@@ -47298,8 +47310,8 @@
         <v>8.5</v>
       </c>
       <c r="Q159" s="16"/>
-      <c r="R159" s="71"/>
-      <c r="S159" s="2">
+      <c r="R159" s="49"/>
+      <c r="S159" s="93">
         <f t="shared" si="2"/>
         <v>8.0225000000000009</v>
       </c>
@@ -47350,8 +47362,8 @@
         <v>2265</v>
       </c>
       <c r="Q160" s="16"/>
-      <c r="R160" s="71"/>
-      <c r="S160" s="2">
+      <c r="R160" s="49"/>
+      <c r="S160" s="93">
         <f t="shared" si="2"/>
         <v>6.1850000000000005</v>
       </c>
@@ -47402,8 +47414,8 @@
         <v>6.91</v>
       </c>
       <c r="Q161" s="16"/>
-      <c r="R161" s="71"/>
-      <c r="S161" s="2">
+      <c r="R161" s="49"/>
+      <c r="S161" s="93">
         <f t="shared" si="2"/>
         <v>6.7975000000000003</v>
       </c>
@@ -47454,8 +47466,8 @@
         <v>8.36</v>
       </c>
       <c r="Q162" s="16"/>
-      <c r="R162" s="71"/>
-      <c r="S162" s="2">
+      <c r="R162" s="49"/>
+      <c r="S162" s="93">
         <f t="shared" si="2"/>
         <v>7.7675000000000001</v>
       </c>
@@ -47504,8 +47516,8 @@
         <v>6.41</v>
       </c>
       <c r="Q163" s="16"/>
-      <c r="R163" s="71"/>
-      <c r="S163" s="2">
+      <c r="R163" s="49"/>
+      <c r="S163" s="93">
         <f t="shared" si="2"/>
         <v>6.1950000000000003</v>
       </c>
@@ -47556,8 +47568,8 @@
         <v>9</v>
       </c>
       <c r="Q164" s="16"/>
-      <c r="R164" s="71"/>
-      <c r="S164" s="2">
+      <c r="R164" s="49"/>
+      <c r="S164" s="93">
         <f t="shared" si="2"/>
         <v>8.4533333333333331</v>
       </c>
@@ -47608,8 +47620,8 @@
         <v>7.86</v>
       </c>
       <c r="Q165" s="16"/>
-      <c r="R165" s="71"/>
-      <c r="S165" s="2">
+      <c r="R165" s="49"/>
+      <c r="S165" s="93">
         <f t="shared" si="2"/>
         <v>7.7275</v>
       </c>
@@ -47660,8 +47672,8 @@
         <v>7.45</v>
       </c>
       <c r="Q166" s="16"/>
-      <c r="R166" s="71"/>
-      <c r="S166" s="2">
+      <c r="R166" s="49"/>
+      <c r="S166" s="93">
         <f t="shared" si="2"/>
         <v>7.0724999999999998</v>
       </c>
@@ -47712,8 +47724,8 @@
         <v>8.77</v>
       </c>
       <c r="Q167" s="16"/>
-      <c r="R167" s="71"/>
-      <c r="S167" s="2">
+      <c r="R167" s="49"/>
+      <c r="S167" s="93">
         <f t="shared" si="2"/>
         <v>8.4550000000000001</v>
       </c>
@@ -47764,8 +47776,8 @@
         <v>6.32</v>
       </c>
       <c r="Q168" s="16"/>
-      <c r="R168" s="71"/>
-      <c r="S168" s="2">
+      <c r="R168" s="49"/>
+      <c r="S168" s="93">
         <f t="shared" si="2"/>
         <v>6.3825000000000003</v>
       </c>
@@ -47800,8 +47812,8 @@
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="16"/>
-      <c r="R169" s="71"/>
-      <c r="S169" s="2" t="e">
+      <c r="R169" s="49"/>
+      <c r="S169" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -47836,8 +47848,8 @@
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
       <c r="Q170" s="16"/>
-      <c r="R170" s="71"/>
-      <c r="S170" s="2" t="e">
+      <c r="R170" s="49"/>
+      <c r="S170" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -47888,8 +47900,8 @@
         <v>7.77</v>
       </c>
       <c r="Q171" s="16"/>
-      <c r="R171" s="71"/>
-      <c r="S171" s="2">
+      <c r="R171" s="49"/>
+      <c r="S171" s="93">
         <f t="shared" si="2"/>
         <v>7.5774999999999997</v>
       </c>
@@ -47918,8 +47930,8 @@
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
       <c r="Q172" s="16"/>
-      <c r="R172" s="71"/>
-      <c r="S172" s="2" t="e">
+      <c r="R172" s="49"/>
+      <c r="S172" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -47970,8 +47982,8 @@
         <v>8.59</v>
       </c>
       <c r="Q173" s="16"/>
-      <c r="R173" s="71"/>
-      <c r="S173" s="2">
+      <c r="R173" s="49"/>
+      <c r="S173" s="93">
         <f t="shared" si="2"/>
         <v>9.08</v>
       </c>
@@ -48010,8 +48022,8 @@
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
       <c r="Q174" s="16"/>
-      <c r="R174" s="71"/>
-      <c r="S174" s="2" t="e">
+      <c r="R174" s="49"/>
+      <c r="S174" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -48058,8 +48070,8 @@
         <v>2249</v>
       </c>
       <c r="Q175" s="16"/>
-      <c r="R175" s="71"/>
-      <c r="S175" s="2">
+      <c r="R175" s="49"/>
+      <c r="S175" s="93">
         <f t="shared" si="2"/>
         <v>7.1500000000000012</v>
       </c>
@@ -48110,8 +48122,8 @@
         <v>2266</v>
       </c>
       <c r="Q176" s="16"/>
-      <c r="R176" s="71"/>
-      <c r="S176" s="2">
+      <c r="R176" s="49"/>
+      <c r="S176" s="93">
         <f t="shared" si="2"/>
         <v>6.27</v>
       </c>
@@ -48162,8 +48174,8 @@
         <v>2249</v>
       </c>
       <c r="Q177" s="16"/>
-      <c r="R177" s="71"/>
-      <c r="S177" s="2">
+      <c r="R177" s="49"/>
+      <c r="S177" s="93">
         <f t="shared" si="2"/>
         <v>6.94</v>
       </c>
@@ -48214,8 +48226,8 @@
         <v>7.52</v>
       </c>
       <c r="Q178" s="16"/>
-      <c r="R178" s="71"/>
-      <c r="S178" s="2">
+      <c r="R178" s="49"/>
+      <c r="S178" s="93">
         <f t="shared" si="2"/>
         <v>7.2</v>
       </c>
@@ -48266,8 +48278,8 @@
         <v>8.82</v>
       </c>
       <c r="Q179" s="16"/>
-      <c r="R179" s="71"/>
-      <c r="S179" s="2">
+      <c r="R179" s="49"/>
+      <c r="S179" s="93">
         <f t="shared" si="2"/>
         <v>8.8524999999999991</v>
       </c>
@@ -48318,8 +48330,8 @@
         <v>2267</v>
       </c>
       <c r="Q180" s="16"/>
-      <c r="R180" s="71"/>
-      <c r="S180" s="2">
+      <c r="R180" s="49"/>
+      <c r="S180" s="93">
         <f t="shared" si="2"/>
         <v>6.64</v>
       </c>
@@ -48370,8 +48382,8 @@
         <v>7.68</v>
       </c>
       <c r="Q181" s="16"/>
-      <c r="R181" s="71"/>
-      <c r="S181" s="2">
+      <c r="R181" s="49"/>
+      <c r="S181" s="93">
         <f t="shared" si="2"/>
         <v>7.8975</v>
       </c>
@@ -48408,8 +48420,8 @@
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
       <c r="Q182" s="16"/>
-      <c r="R182" s="71"/>
-      <c r="S182" s="2">
+      <c r="R182" s="49"/>
+      <c r="S182" s="93">
         <f t="shared" si="2"/>
         <v>6.58</v>
       </c>
@@ -48460,8 +48472,8 @@
         <v>9.36</v>
       </c>
       <c r="Q183" s="16"/>
-      <c r="R183" s="71"/>
-      <c r="S183" s="2">
+      <c r="R183" s="49"/>
+      <c r="S183" s="93">
         <f t="shared" si="2"/>
         <v>8.6366666666666667</v>
       </c>
@@ -48512,8 +48524,8 @@
         <v>9.27</v>
       </c>
       <c r="Q184" s="16"/>
-      <c r="R184" s="71"/>
-      <c r="S184" s="2">
+      <c r="R184" s="49"/>
+      <c r="S184" s="93">
         <f t="shared" si="2"/>
         <v>8.7375000000000007</v>
       </c>
@@ -48548,8 +48560,8 @@
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
       <c r="Q185" s="16"/>
-      <c r="R185" s="71"/>
-      <c r="S185" s="2" t="e">
+      <c r="R185" s="49"/>
+      <c r="S185" s="93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -48600,8 +48612,8 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="Q186" s="16"/>
-      <c r="R186" s="71"/>
-      <c r="S186" s="2">
+      <c r="R186" s="49"/>
+      <c r="S186" s="93">
         <f t="shared" si="2"/>
         <v>9.4550000000000001</v>
       </c>
@@ -48652,8 +48664,8 @@
         <v>7.02</v>
       </c>
       <c r="Q187" s="16"/>
-      <c r="R187" s="71"/>
-      <c r="S187" s="2">
+      <c r="R187" s="49"/>
+      <c r="S187" s="93">
         <f t="shared" si="2"/>
         <v>6.4666666666666659</v>
       </c>
@@ -48704,8 +48716,8 @@
         <v>8.86</v>
       </c>
       <c r="Q188" s="16"/>
-      <c r="R188" s="71"/>
-      <c r="S188" s="2">
+      <c r="R188" s="49"/>
+      <c r="S188" s="93">
         <f t="shared" si="2"/>
         <v>8.58</v>
       </c>
@@ -48756,8 +48768,8 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="Q189" s="16"/>
-      <c r="R189" s="71"/>
-      <c r="S189" s="2">
+      <c r="R189" s="49"/>
+      <c r="S189" s="93">
         <f t="shared" si="2"/>
         <v>8.7025000000000006</v>
       </c>
@@ -48808,8 +48820,8 @@
         <v>8.23</v>
       </c>
       <c r="Q190" s="16"/>
-      <c r="R190" s="71"/>
-      <c r="S190" s="2">
+      <c r="R190" s="49"/>
+      <c r="S190" s="93">
         <f t="shared" si="2"/>
         <v>8.1024999999999991</v>
       </c>
@@ -48860,8 +48872,8 @@
         <v>2268</v>
       </c>
       <c r="Q191" s="16"/>
-      <c r="R191" s="71"/>
-      <c r="S191" s="2">
+      <c r="R191" s="49"/>
+      <c r="S191" s="93">
         <f t="shared" si="2"/>
         <v>5.82</v>
       </c>
@@ -48912,8 +48924,8 @@
         <v>7.64</v>
       </c>
       <c r="Q192" s="16"/>
-      <c r="R192" s="71"/>
-      <c r="S192" s="2">
+      <c r="R192" s="49"/>
+      <c r="S192" s="93">
         <f t="shared" si="2"/>
         <v>7.2475000000000005</v>
       </c>
@@ -48964,8 +48976,8 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="Q193" s="16"/>
-      <c r="R193" s="71"/>
-      <c r="S193" s="2">
+      <c r="R193" s="49"/>
+      <c r="S193" s="93">
         <f t="shared" si="2"/>
         <v>9.09</v>
       </c>
@@ -49016,8 +49028,8 @@
         <v>8.91</v>
       </c>
       <c r="Q194" s="16"/>
-      <c r="R194" s="71"/>
-      <c r="S194" s="2">
+      <c r="R194" s="49"/>
+      <c r="S194" s="93">
         <f t="shared" ref="S194:S257" si="3">AVERAGE(M194:P194)</f>
         <v>9.1275000000000013</v>
       </c>
@@ -49068,8 +49080,8 @@
         <v>2250</v>
       </c>
       <c r="Q195" s="16"/>
-      <c r="R195" s="71"/>
-      <c r="S195" s="2">
+      <c r="R195" s="49"/>
+      <c r="S195" s="93">
         <f t="shared" si="3"/>
         <v>6.4533333333333331</v>
       </c>
@@ -49120,8 +49132,8 @@
         <v>8.59</v>
       </c>
       <c r="Q196" s="16"/>
-      <c r="R196" s="71"/>
-      <c r="S196" s="2">
+      <c r="R196" s="49"/>
+      <c r="S196" s="93">
         <f t="shared" si="3"/>
         <v>8.74</v>
       </c>
@@ -49172,8 +49184,8 @@
         <v>7.18</v>
       </c>
       <c r="Q197" s="16"/>
-      <c r="R197" s="71"/>
-      <c r="S197" s="2">
+      <c r="R197" s="49"/>
+      <c r="S197" s="93">
         <f t="shared" si="3"/>
         <v>6.9633333333333338</v>
       </c>
@@ -49224,8 +49236,8 @@
         <v>5.61</v>
       </c>
       <c r="Q198" s="16"/>
-      <c r="R198" s="71"/>
-      <c r="S198" s="2">
+      <c r="R198" s="49"/>
+      <c r="S198" s="93">
         <f t="shared" si="3"/>
         <v>5.9050000000000002</v>
       </c>
@@ -49276,8 +49288,8 @@
         <v>2249</v>
       </c>
       <c r="Q199" s="16"/>
-      <c r="R199" s="71"/>
-      <c r="S199" s="2" t="e">
+      <c r="R199" s="49"/>
+      <c r="S199" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -49328,8 +49340,8 @@
         <v>7.73</v>
       </c>
       <c r="Q200" s="16"/>
-      <c r="R200" s="71"/>
-      <c r="S200" s="2">
+      <c r="R200" s="49"/>
+      <c r="S200" s="93">
         <f t="shared" si="3"/>
         <v>6.956666666666667</v>
       </c>
@@ -49380,8 +49392,8 @@
         <v>7.86</v>
       </c>
       <c r="Q201" s="16"/>
-      <c r="R201" s="71"/>
-      <c r="S201" s="2">
+      <c r="R201" s="49"/>
+      <c r="S201" s="93">
         <f t="shared" si="3"/>
         <v>7.3025000000000002</v>
       </c>
@@ -49432,8 +49444,8 @@
         <v>8.41</v>
       </c>
       <c r="Q202" s="16"/>
-      <c r="R202" s="71"/>
-      <c r="S202" s="2">
+      <c r="R202" s="49"/>
+      <c r="S202" s="93">
         <f t="shared" si="3"/>
         <v>8.2974999999999994</v>
       </c>
@@ -49482,8 +49494,8 @@
         <v>7.3</v>
       </c>
       <c r="Q203" s="16"/>
-      <c r="R203" s="71"/>
-      <c r="S203" s="2">
+      <c r="R203" s="49"/>
+      <c r="S203" s="93">
         <f t="shared" si="3"/>
         <v>7.1775000000000002</v>
       </c>
@@ -49534,8 +49546,8 @@
         <v>7.68</v>
       </c>
       <c r="Q204" s="16"/>
-      <c r="R204" s="71"/>
-      <c r="S204" s="2">
+      <c r="R204" s="49"/>
+      <c r="S204" s="93">
         <f t="shared" si="3"/>
         <v>7.5466666666666669</v>
       </c>
@@ -49586,8 +49598,8 @@
         <v>7.55</v>
       </c>
       <c r="Q205" s="16"/>
-      <c r="R205" s="71"/>
-      <c r="S205" s="2">
+      <c r="R205" s="49"/>
+      <c r="S205" s="93">
         <f t="shared" si="3"/>
         <v>7.625</v>
       </c>
@@ -49638,8 +49650,8 @@
         <v>8.18</v>
       </c>
       <c r="Q206" s="16"/>
-      <c r="R206" s="71"/>
-      <c r="S206" s="2">
+      <c r="R206" s="49"/>
+      <c r="S206" s="93">
         <f t="shared" si="3"/>
         <v>8.17</v>
       </c>
@@ -49690,8 +49702,8 @@
         <v>8.82</v>
       </c>
       <c r="Q207" s="16"/>
-      <c r="R207" s="71"/>
-      <c r="S207" s="2">
+      <c r="R207" s="49"/>
+      <c r="S207" s="93">
         <f t="shared" si="3"/>
         <v>8.6199999999999992</v>
       </c>
@@ -49742,8 +49754,8 @@
         <v>2269</v>
       </c>
       <c r="Q208" s="16"/>
-      <c r="R208" s="71"/>
-      <c r="S208" s="2">
+      <c r="R208" s="49"/>
+      <c r="S208" s="93">
         <f t="shared" si="3"/>
         <v>6.25</v>
       </c>
@@ -49794,8 +49806,8 @@
         <v>2270</v>
       </c>
       <c r="Q209" s="16"/>
-      <c r="R209" s="71"/>
-      <c r="S209" s="2">
+      <c r="R209" s="49"/>
+      <c r="S209" s="93">
         <f t="shared" si="3"/>
         <v>6.09</v>
       </c>
@@ -49846,8 +49858,8 @@
         <v>8.23</v>
       </c>
       <c r="Q210" s="16"/>
-      <c r="R210" s="71"/>
-      <c r="S210" s="2">
+      <c r="R210" s="49"/>
+      <c r="S210" s="93">
         <f t="shared" si="3"/>
         <v>8.1950000000000003</v>
       </c>
@@ -49898,8 +49910,8 @@
         <v>8.14</v>
       </c>
       <c r="Q211" s="16"/>
-      <c r="R211" s="71"/>
-      <c r="S211" s="2">
+      <c r="R211" s="49"/>
+      <c r="S211" s="93">
         <f t="shared" si="3"/>
         <v>8.15</v>
       </c>
@@ -49950,8 +49962,8 @@
         <v>2250</v>
       </c>
       <c r="Q212" s="16"/>
-      <c r="R212" s="71"/>
-      <c r="S212" s="2">
+      <c r="R212" s="49"/>
+      <c r="S212" s="93">
         <f t="shared" si="3"/>
         <v>5.97</v>
       </c>
@@ -49988,8 +50000,8 @@
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
       <c r="Q213" s="16"/>
-      <c r="R213" s="71"/>
-      <c r="S213" s="2">
+      <c r="R213" s="49"/>
+      <c r="S213" s="93">
         <f t="shared" si="3"/>
         <v>6.23</v>
       </c>
@@ -50040,8 +50052,8 @@
         <v>9.14</v>
       </c>
       <c r="Q214" s="16"/>
-      <c r="R214" s="71"/>
-      <c r="S214" s="2">
+      <c r="R214" s="49"/>
+      <c r="S214" s="93">
         <f t="shared" si="3"/>
         <v>9.1150000000000002</v>
       </c>
@@ -50092,8 +50104,8 @@
         <v>6.34</v>
       </c>
       <c r="Q215" s="16"/>
-      <c r="R215" s="71"/>
-      <c r="S215" s="2">
+      <c r="R215" s="49"/>
+      <c r="S215" s="93">
         <f t="shared" si="3"/>
         <v>7.0100000000000007</v>
       </c>
@@ -50144,8 +50156,8 @@
         <v>6.57</v>
       </c>
       <c r="Q216" s="16"/>
-      <c r="R216" s="71"/>
-      <c r="S216" s="2">
+      <c r="R216" s="49"/>
+      <c r="S216" s="93">
         <f t="shared" si="3"/>
         <v>6.9950000000000001</v>
       </c>
@@ -50194,8 +50206,8 @@
         <v>954</v>
       </c>
       <c r="Q217" s="16"/>
-      <c r="R217" s="71"/>
-      <c r="S217" s="2" t="e">
+      <c r="R217" s="49"/>
+      <c r="S217" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -50230,8 +50242,8 @@
       <c r="O218" s="2"/>
       <c r="P218" s="2"/>
       <c r="Q218" s="16"/>
-      <c r="R218" s="71"/>
-      <c r="S218" s="2" t="e">
+      <c r="R218" s="49"/>
+      <c r="S218" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -50282,8 +50294,8 @@
         <v>2249</v>
       </c>
       <c r="Q219" s="16"/>
-      <c r="R219" s="71"/>
-      <c r="S219" s="2">
+      <c r="R219" s="49"/>
+      <c r="S219" s="93">
         <f t="shared" si="3"/>
         <v>6.1499999999999995</v>
       </c>
@@ -50334,8 +50346,8 @@
         <v>5.91</v>
       </c>
       <c r="Q220" s="16"/>
-      <c r="R220" s="71"/>
-      <c r="S220" s="2">
+      <c r="R220" s="49"/>
+      <c r="S220" s="93">
         <f t="shared" si="3"/>
         <v>6.1766666666666667</v>
       </c>
@@ -50386,8 +50398,8 @@
         <v>2249</v>
       </c>
       <c r="Q221" s="16"/>
-      <c r="R221" s="71"/>
-      <c r="S221" s="2">
+      <c r="R221" s="49"/>
+      <c r="S221" s="93">
         <f t="shared" si="3"/>
         <v>7.4899999999999993</v>
       </c>
@@ -50438,8 +50450,8 @@
         <v>7.68</v>
       </c>
       <c r="Q222" s="16"/>
-      <c r="R222" s="71"/>
-      <c r="S222" s="2">
+      <c r="R222" s="49"/>
+      <c r="S222" s="93">
         <f t="shared" si="3"/>
         <v>8.18</v>
       </c>
@@ -50490,8 +50502,8 @@
         <v>7.91</v>
       </c>
       <c r="Q223" s="16"/>
-      <c r="R223" s="71"/>
-      <c r="S223" s="2">
+      <c r="R223" s="49"/>
+      <c r="S223" s="93">
         <f t="shared" si="3"/>
         <v>7.8525</v>
       </c>
@@ -50542,8 +50554,8 @@
         <v>7.86</v>
       </c>
       <c r="Q224" s="16"/>
-      <c r="R224" s="71"/>
-      <c r="S224" s="2">
+      <c r="R224" s="49"/>
+      <c r="S224" s="93">
         <f t="shared" si="3"/>
         <v>7.42</v>
       </c>
@@ -50594,8 +50606,8 @@
         <v>6.52</v>
       </c>
       <c r="Q225" s="16"/>
-      <c r="R225" s="71"/>
-      <c r="S225" s="2">
+      <c r="R225" s="49"/>
+      <c r="S225" s="93">
         <f t="shared" si="3"/>
         <v>6.8975</v>
       </c>
@@ -50646,8 +50658,8 @@
         <v>6.82</v>
       </c>
       <c r="Q226" s="16"/>
-      <c r="R226" s="71"/>
-      <c r="S226" s="2">
+      <c r="R226" s="49"/>
+      <c r="S226" s="93">
         <f t="shared" si="3"/>
         <v>6.7566666666666668</v>
       </c>
@@ -50698,8 +50710,8 @@
         <v>7.5</v>
       </c>
       <c r="Q227" s="16"/>
-      <c r="R227" s="71"/>
-      <c r="S227" s="2">
+      <c r="R227" s="49"/>
+      <c r="S227" s="93">
         <f t="shared" si="3"/>
         <v>7.66</v>
       </c>
@@ -50750,8 +50762,8 @@
         <v>7.95</v>
       </c>
       <c r="Q228" s="16"/>
-      <c r="R228" s="71"/>
-      <c r="S228" s="2">
+      <c r="R228" s="49"/>
+      <c r="S228" s="93">
         <f t="shared" si="3"/>
         <v>7.8274999999999997</v>
       </c>
@@ -50802,8 +50814,8 @@
         <v>2271</v>
       </c>
       <c r="Q229" s="16"/>
-      <c r="R229" s="71"/>
-      <c r="S229" s="2">
+      <c r="R229" s="49"/>
+      <c r="S229" s="93">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -50854,8 +50866,8 @@
         <v>2272</v>
       </c>
       <c r="Q230" s="16"/>
-      <c r="R230" s="71"/>
-      <c r="S230" s="2" t="e">
+      <c r="R230" s="49"/>
+      <c r="S230" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -50892,8 +50904,8 @@
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
       <c r="Q231" s="16"/>
-      <c r="R231" s="71"/>
-      <c r="S231" s="2" t="e">
+      <c r="R231" s="49"/>
+      <c r="S231" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -50928,8 +50940,8 @@
       <c r="O232" s="2"/>
       <c r="P232" s="2"/>
       <c r="Q232" s="16"/>
-      <c r="R232" s="71"/>
-      <c r="S232" s="2" t="e">
+      <c r="R232" s="49"/>
+      <c r="S232" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -50980,8 +50992,8 @@
         <v>7.32</v>
       </c>
       <c r="Q233" s="16"/>
-      <c r="R233" s="71"/>
-      <c r="S233" s="2">
+      <c r="R233" s="49"/>
+      <c r="S233" s="93">
         <f t="shared" si="3"/>
         <v>7.83</v>
       </c>
@@ -51032,8 +51044,8 @@
         <v>7.14</v>
       </c>
       <c r="Q234" s="16"/>
-      <c r="R234" s="71"/>
-      <c r="S234" s="2">
+      <c r="R234" s="49"/>
+      <c r="S234" s="93">
         <f t="shared" si="3"/>
         <v>7.2433333333333332</v>
       </c>
@@ -51084,8 +51096,8 @@
         <v>6.86</v>
       </c>
       <c r="Q235" s="16"/>
-      <c r="R235" s="71"/>
-      <c r="S235" s="2">
+      <c r="R235" s="49"/>
+      <c r="S235" s="93">
         <f t="shared" si="3"/>
         <v>7.166666666666667</v>
       </c>
@@ -51122,8 +51134,8 @@
       <c r="O236" s="2"/>
       <c r="P236" s="2"/>
       <c r="Q236" s="16"/>
-      <c r="R236" s="71"/>
-      <c r="S236" s="2">
+      <c r="R236" s="49"/>
+      <c r="S236" s="93">
         <f t="shared" si="3"/>
         <v>7.18</v>
       </c>
@@ -51174,8 +51186,8 @@
         <v>7.32</v>
       </c>
       <c r="Q237" s="16"/>
-      <c r="R237" s="71"/>
-      <c r="S237" s="2">
+      <c r="R237" s="49"/>
+      <c r="S237" s="93">
         <f t="shared" si="3"/>
         <v>7.3425000000000002</v>
       </c>
@@ -51226,8 +51238,8 @@
         <v>7.77</v>
       </c>
       <c r="Q238" s="16"/>
-      <c r="R238" s="71"/>
-      <c r="S238" s="2">
+      <c r="R238" s="49"/>
+      <c r="S238" s="93">
         <f t="shared" si="3"/>
         <v>7.7924999999999995</v>
       </c>
@@ -51278,8 +51290,8 @@
         <v>6.86</v>
       </c>
       <c r="Q239" s="16"/>
-      <c r="R239" s="71"/>
-      <c r="S239" s="2">
+      <c r="R239" s="49"/>
+      <c r="S239" s="93">
         <f t="shared" si="3"/>
         <v>6.8025000000000002</v>
       </c>
@@ -51316,8 +51328,8 @@
       <c r="O240" s="2"/>
       <c r="P240" s="2"/>
       <c r="Q240" s="16"/>
-      <c r="R240" s="71"/>
-      <c r="S240" s="2">
+      <c r="R240" s="49"/>
+      <c r="S240" s="93">
         <f t="shared" si="3"/>
         <v>6.95</v>
       </c>
@@ -51368,8 +51380,8 @@
         <v>6.2</v>
       </c>
       <c r="Q241" s="16"/>
-      <c r="R241" s="71"/>
-      <c r="S241" s="2">
+      <c r="R241" s="49"/>
+      <c r="S241" s="93">
         <f t="shared" si="3"/>
         <v>6.1333333333333329</v>
       </c>
@@ -51420,8 +51432,8 @@
         <v>7.41</v>
       </c>
       <c r="Q242" s="16"/>
-      <c r="R242" s="71"/>
-      <c r="S242" s="2">
+      <c r="R242" s="49"/>
+      <c r="S242" s="93">
         <f t="shared" si="3"/>
         <v>6.8875000000000002</v>
       </c>
@@ -51472,8 +51484,8 @@
         <v>8.91</v>
       </c>
       <c r="Q243" s="16"/>
-      <c r="R243" s="71"/>
-      <c r="S243" s="2">
+      <c r="R243" s="49"/>
+      <c r="S243" s="93">
         <f t="shared" si="3"/>
         <v>8.2274999999999991</v>
       </c>
@@ -51524,8 +51536,8 @@
         <v>8.14</v>
       </c>
       <c r="Q244" s="16"/>
-      <c r="R244" s="71"/>
-      <c r="S244" s="2">
+      <c r="R244" s="49"/>
+      <c r="S244" s="93">
         <f t="shared" si="3"/>
         <v>8.0166666666666675</v>
       </c>
@@ -51576,8 +51588,8 @@
         <v>2273</v>
       </c>
       <c r="Q245" s="16"/>
-      <c r="R245" s="71"/>
-      <c r="S245" s="2">
+      <c r="R245" s="49"/>
+      <c r="S245" s="93">
         <f t="shared" si="3"/>
         <v>7.66</v>
       </c>
@@ -51628,8 +51640,8 @@
         <v>6.48</v>
       </c>
       <c r="Q246" s="16"/>
-      <c r="R246" s="71"/>
-      <c r="S246" s="2">
+      <c r="R246" s="49"/>
+      <c r="S246" s="93">
         <f t="shared" si="3"/>
         <v>6.8025000000000002</v>
       </c>
@@ -51680,8 +51692,8 @@
         <v>8.14</v>
       </c>
       <c r="Q247" s="16"/>
-      <c r="R247" s="71"/>
-      <c r="S247" s="2">
+      <c r="R247" s="49"/>
+      <c r="S247" s="93">
         <f t="shared" si="3"/>
         <v>7.7050000000000001</v>
       </c>
@@ -51732,8 +51744,8 @@
         <v>6.23</v>
       </c>
       <c r="Q248" s="16"/>
-      <c r="R248" s="71"/>
-      <c r="S248" s="2">
+      <c r="R248" s="49"/>
+      <c r="S248" s="93">
         <f t="shared" si="3"/>
         <v>6.72</v>
       </c>
@@ -51784,8 +51796,8 @@
         <v>2274</v>
       </c>
       <c r="Q249" s="16"/>
-      <c r="R249" s="71"/>
-      <c r="S249" s="2" t="e">
+      <c r="R249" s="49"/>
+      <c r="S249" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -51814,8 +51826,8 @@
       <c r="O250" s="2"/>
       <c r="P250" s="2"/>
       <c r="Q250" s="16"/>
-      <c r="R250" s="71"/>
-      <c r="S250" s="2" t="e">
+      <c r="R250" s="49"/>
+      <c r="S250" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -51850,8 +51862,8 @@
       <c r="O251" s="2"/>
       <c r="P251" s="2"/>
       <c r="Q251" s="16"/>
-      <c r="R251" s="71"/>
-      <c r="S251" s="2" t="e">
+      <c r="R251" s="49"/>
+      <c r="S251" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -51902,8 +51914,8 @@
         <v>7.32</v>
       </c>
       <c r="Q252" s="16"/>
-      <c r="R252" s="71"/>
-      <c r="S252" s="2">
+      <c r="R252" s="49"/>
+      <c r="S252" s="93">
         <f t="shared" si="3"/>
         <v>7.3825000000000003</v>
       </c>
@@ -51954,8 +51966,8 @@
         <v>8.27</v>
       </c>
       <c r="Q253" s="16"/>
-      <c r="R253" s="71"/>
-      <c r="S253" s="2">
+      <c r="R253" s="49"/>
+      <c r="S253" s="93">
         <f t="shared" si="3"/>
         <v>8.5449999999999999</v>
       </c>
@@ -52006,8 +52018,8 @@
         <v>2275</v>
       </c>
       <c r="Q254" s="16"/>
-      <c r="R254" s="71"/>
-      <c r="S254" s="2" t="e">
+      <c r="R254" s="49"/>
+      <c r="S254" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -52058,8 +52070,8 @@
         <v>7.18</v>
       </c>
       <c r="Q255" s="16"/>
-      <c r="R255" s="71"/>
-      <c r="S255" s="2">
+      <c r="R255" s="49"/>
+      <c r="S255" s="93">
         <f t="shared" si="3"/>
         <v>7.085</v>
       </c>
@@ -52110,8 +52122,8 @@
         <v>2249</v>
       </c>
       <c r="Q256" s="16"/>
-      <c r="R256" s="71"/>
-      <c r="S256" s="2" t="e">
+      <c r="R256" s="49"/>
+      <c r="S256" s="93" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -52162,8 +52174,8 @@
         <v>8.36</v>
       </c>
       <c r="Q257" s="16"/>
-      <c r="R257" s="71"/>
-      <c r="S257" s="2">
+      <c r="R257" s="49"/>
+      <c r="S257" s="93">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
@@ -52214,8 +52226,8 @@
         <v>8.5</v>
       </c>
       <c r="Q258" s="16"/>
-      <c r="R258" s="71"/>
-      <c r="S258" s="2">
+      <c r="R258" s="49"/>
+      <c r="S258" s="93">
         <f t="shared" ref="S258:S321" si="4">AVERAGE(M258:P258)</f>
         <v>8.0933333333333337</v>
       </c>
@@ -52266,8 +52278,8 @@
         <v>8.27</v>
       </c>
       <c r="Q259" s="16"/>
-      <c r="R259" s="71"/>
-      <c r="S259" s="2">
+      <c r="R259" s="49"/>
+      <c r="S259" s="93">
         <f t="shared" si="4"/>
         <v>7.9424999999999999</v>
       </c>
@@ -52318,8 +52330,8 @@
         <v>8.86</v>
       </c>
       <c r="Q260" s="16"/>
-      <c r="R260" s="71"/>
-      <c r="S260" s="2">
+      <c r="R260" s="49"/>
+      <c r="S260" s="93">
         <f t="shared" si="4"/>
         <v>8.9875000000000007</v>
       </c>
@@ -52370,8 +52382,8 @@
         <v>8.18</v>
       </c>
       <c r="Q261" s="16"/>
-      <c r="R261" s="71"/>
-      <c r="S261" s="2">
+      <c r="R261" s="49"/>
+      <c r="S261" s="93">
         <f t="shared" si="4"/>
         <v>8.1224999999999987</v>
       </c>
@@ -52422,8 +52434,8 @@
         <v>8.73</v>
       </c>
       <c r="Q262" s="16"/>
-      <c r="R262" s="71"/>
-      <c r="S262" s="2">
+      <c r="R262" s="49"/>
+      <c r="S262" s="93">
         <f t="shared" si="4"/>
         <v>8.41</v>
       </c>
@@ -52474,8 +52486,8 @@
         <v>9.27</v>
       </c>
       <c r="Q263" s="16"/>
-      <c r="R263" s="71"/>
-      <c r="S263" s="2">
+      <c r="R263" s="49"/>
+      <c r="S263" s="93">
         <f t="shared" si="4"/>
         <v>9.192499999999999</v>
       </c>
@@ -52526,8 +52538,8 @@
         <v>7.95</v>
       </c>
       <c r="Q264" s="16"/>
-      <c r="R264" s="71"/>
-      <c r="S264" s="2">
+      <c r="R264" s="49"/>
+      <c r="S264" s="93">
         <f t="shared" si="4"/>
         <v>7.7233333333333336</v>
       </c>
@@ -52578,8 +52590,8 @@
         <v>7.86</v>
       </c>
       <c r="Q265" s="16"/>
-      <c r="R265" s="71"/>
-      <c r="S265" s="2">
+      <c r="R265" s="49"/>
+      <c r="S265" s="93">
         <f t="shared" si="4"/>
         <v>8.2625000000000011</v>
       </c>
@@ -52630,8 +52642,8 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="Q266" s="16"/>
-      <c r="R266" s="71"/>
-      <c r="S266" s="2">
+      <c r="R266" s="49"/>
+      <c r="S266" s="93">
         <f t="shared" si="4"/>
         <v>8.2624999999999993</v>
       </c>
@@ -52674,8 +52686,8 @@
       </c>
       <c r="P267" s="2"/>
       <c r="Q267" s="16"/>
-      <c r="R267" s="71"/>
-      <c r="S267" s="2">
+      <c r="R267" s="49"/>
+      <c r="S267" s="93">
         <f t="shared" si="4"/>
         <v>6.95</v>
       </c>
@@ -52726,8 +52738,8 @@
         <v>8.36</v>
       </c>
       <c r="Q268" s="16"/>
-      <c r="R268" s="71"/>
-      <c r="S268" s="2">
+      <c r="R268" s="49"/>
+      <c r="S268" s="93">
         <f t="shared" si="4"/>
         <v>8.09</v>
       </c>
@@ -52778,8 +52790,8 @@
         <v>8.32</v>
       </c>
       <c r="Q269" s="16"/>
-      <c r="R269" s="71"/>
-      <c r="S269" s="2">
+      <c r="R269" s="49"/>
+      <c r="S269" s="93">
         <f t="shared" si="4"/>
         <v>8.3975000000000009</v>
       </c>
@@ -52830,8 +52842,8 @@
         <v>6.5</v>
       </c>
       <c r="Q270" s="16"/>
-      <c r="R270" s="71"/>
-      <c r="S270" s="2">
+      <c r="R270" s="49"/>
+      <c r="S270" s="93">
         <f t="shared" si="4"/>
         <v>6.4933333333333332</v>
       </c>
@@ -52882,8 +52894,8 @@
         <v>7.86</v>
       </c>
       <c r="Q271" s="16"/>
-      <c r="R271" s="71"/>
-      <c r="S271" s="2">
+      <c r="R271" s="49"/>
+      <c r="S271" s="93">
         <f t="shared" si="4"/>
         <v>7.9775</v>
       </c>
@@ -52934,8 +52946,8 @@
         <v>954</v>
       </c>
       <c r="Q272" s="16"/>
-      <c r="R272" s="71"/>
-      <c r="S272" s="2">
+      <c r="R272" s="49"/>
+      <c r="S272" s="93">
         <f t="shared" si="4"/>
         <v>6.0949999999999998</v>
       </c>
@@ -52986,8 +52998,8 @@
         <v>9.18</v>
       </c>
       <c r="Q273" s="16"/>
-      <c r="R273" s="71"/>
-      <c r="S273" s="2">
+      <c r="R273" s="49"/>
+      <c r="S273" s="93">
         <f t="shared" si="4"/>
         <v>9.3975000000000009</v>
       </c>
@@ -53022,8 +53034,8 @@
       <c r="O274" s="2"/>
       <c r="P274" s="2"/>
       <c r="Q274" s="16"/>
-      <c r="R274" s="71"/>
-      <c r="S274" s="2">
+      <c r="R274" s="49"/>
+      <c r="S274" s="93">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
@@ -53068,8 +53080,8 @@
         <v>7.25</v>
       </c>
       <c r="Q275" s="16"/>
-      <c r="R275" s="71"/>
-      <c r="S275" s="2">
+      <c r="R275" s="49"/>
+      <c r="S275" s="93">
         <f t="shared" si="4"/>
         <v>7.3049999999999997</v>
       </c>
@@ -53120,8 +53132,8 @@
         <v>2276</v>
       </c>
       <c r="Q276" s="16"/>
-      <c r="R276" s="71"/>
-      <c r="S276" s="2">
+      <c r="R276" s="49"/>
+      <c r="S276" s="93">
         <f t="shared" si="4"/>
         <v>7.77</v>
       </c>
@@ -53172,8 +53184,8 @@
         <v>954</v>
       </c>
       <c r="Q277" s="16"/>
-      <c r="R277" s="71"/>
-      <c r="S277" s="2">
+      <c r="R277" s="49"/>
+      <c r="S277" s="93">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
@@ -53224,8 +53236,8 @@
         <v>954</v>
       </c>
       <c r="Q278" s="16"/>
-      <c r="R278" s="71"/>
-      <c r="S278" s="2" t="e">
+      <c r="R278" s="49"/>
+      <c r="S278" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -53276,8 +53288,8 @@
         <v>7.23</v>
       </c>
       <c r="Q279" s="16"/>
-      <c r="R279" s="71"/>
-      <c r="S279" s="2">
+      <c r="R279" s="49"/>
+      <c r="S279" s="93">
         <f t="shared" si="4"/>
         <v>7.6533333333333333</v>
       </c>
@@ -53328,8 +53340,8 @@
         <v>7.16</v>
       </c>
       <c r="Q280" s="16"/>
-      <c r="R280" s="71"/>
-      <c r="S280" s="2">
+      <c r="R280" s="49"/>
+      <c r="S280" s="93">
         <f t="shared" si="4"/>
         <v>7.66</v>
       </c>
@@ -53380,8 +53392,8 @@
         <v>2268</v>
       </c>
       <c r="Q281" s="16"/>
-      <c r="R281" s="71"/>
-      <c r="S281" s="2">
+      <c r="R281" s="49"/>
+      <c r="S281" s="93">
         <f t="shared" si="4"/>
         <v>7.82</v>
       </c>
@@ -53432,8 +53444,8 @@
         <v>8.23</v>
       </c>
       <c r="Q282" s="16"/>
-      <c r="R282" s="71"/>
-      <c r="S282" s="2">
+      <c r="R282" s="49"/>
+      <c r="S282" s="93">
         <f t="shared" si="4"/>
         <v>8.57</v>
       </c>
@@ -53484,8 +53496,8 @@
         <v>2277</v>
       </c>
       <c r="Q283" s="16"/>
-      <c r="R283" s="71"/>
-      <c r="S283" s="2">
+      <c r="R283" s="49"/>
+      <c r="S283" s="93">
         <f t="shared" si="4"/>
         <v>7.18</v>
       </c>
@@ -53536,8 +53548,8 @@
         <v>6.45</v>
       </c>
       <c r="Q284" s="16"/>
-      <c r="R284" s="71"/>
-      <c r="S284" s="2">
+      <c r="R284" s="49"/>
+      <c r="S284" s="93">
         <f t="shared" si="4"/>
         <v>6.7949999999999999</v>
       </c>
@@ -53588,8 +53600,8 @@
         <v>7.05</v>
       </c>
       <c r="Q285" s="16"/>
-      <c r="R285" s="71"/>
-      <c r="S285" s="2">
+      <c r="R285" s="49"/>
+      <c r="S285" s="93">
         <f t="shared" si="4"/>
         <v>7.2133333333333338</v>
       </c>
@@ -53640,8 +53652,8 @@
         <v>7.2</v>
       </c>
       <c r="Q286" s="16"/>
-      <c r="R286" s="71"/>
-      <c r="S286" s="2">
+      <c r="R286" s="49"/>
+      <c r="S286" s="93">
         <f t="shared" si="4"/>
         <v>7.4024999999999999</v>
       </c>
@@ -53692,8 +53704,8 @@
         <v>6.07</v>
       </c>
       <c r="Q287" s="16"/>
-      <c r="R287" s="71"/>
-      <c r="S287" s="2">
+      <c r="R287" s="49"/>
+      <c r="S287" s="93">
         <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
@@ -53744,8 +53756,8 @@
         <v>6.2</v>
       </c>
       <c r="Q288" s="16"/>
-      <c r="R288" s="71"/>
-      <c r="S288" s="2">
+      <c r="R288" s="49"/>
+      <c r="S288" s="93">
         <f t="shared" si="4"/>
         <v>6.2225000000000001</v>
       </c>
@@ -53796,8 +53808,8 @@
         <v>6.75</v>
       </c>
       <c r="Q289" s="16"/>
-      <c r="R289" s="71"/>
-      <c r="S289" s="2">
+      <c r="R289" s="49"/>
+      <c r="S289" s="93">
         <f t="shared" si="4"/>
         <v>7.1433333333333335</v>
       </c>
@@ -53846,8 +53858,8 @@
         <v>6.84</v>
       </c>
       <c r="Q290" s="16"/>
-      <c r="R290" s="71"/>
-      <c r="S290" s="2">
+      <c r="R290" s="49"/>
+      <c r="S290" s="93">
         <f t="shared" si="4"/>
         <v>7.165</v>
       </c>
@@ -53898,8 +53910,8 @@
         <v>2278</v>
       </c>
       <c r="Q291" s="16"/>
-      <c r="R291" s="71"/>
-      <c r="S291" s="2">
+      <c r="R291" s="49"/>
+      <c r="S291" s="93">
         <f t="shared" si="4"/>
         <v>6.2050000000000001</v>
       </c>
@@ -53950,8 +53962,8 @@
         <v>6.5</v>
       </c>
       <c r="Q292" s="16"/>
-      <c r="R292" s="71"/>
-      <c r="S292" s="2">
+      <c r="R292" s="49"/>
+      <c r="S292" s="93">
         <f t="shared" si="4"/>
         <v>6.66</v>
       </c>
@@ -54002,8 +54014,8 @@
         <v>7.3</v>
       </c>
       <c r="Q293" s="16"/>
-      <c r="R293" s="71"/>
-      <c r="S293" s="2">
+      <c r="R293" s="49"/>
+      <c r="S293" s="93">
         <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
@@ -54054,8 +54066,8 @@
         <v>7.64</v>
       </c>
       <c r="Q294" s="16"/>
-      <c r="R294" s="71"/>
-      <c r="S294" s="2">
+      <c r="R294" s="49"/>
+      <c r="S294" s="93">
         <f t="shared" si="4"/>
         <v>7.7733333333333334</v>
       </c>
@@ -54106,8 +54118,8 @@
         <v>7.18</v>
       </c>
       <c r="Q295" s="16"/>
-      <c r="R295" s="71"/>
-      <c r="S295" s="2">
+      <c r="R295" s="49"/>
+      <c r="S295" s="93">
         <f t="shared" si="4"/>
         <v>7.4074999999999998</v>
       </c>
@@ -54144,8 +54156,8 @@
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
       <c r="Q296" s="16"/>
-      <c r="R296" s="71"/>
-      <c r="S296" s="2" t="e">
+      <c r="R296" s="49"/>
+      <c r="S296" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -54196,8 +54208,8 @@
         <v>6.43</v>
       </c>
       <c r="Q297" s="16"/>
-      <c r="R297" s="71"/>
-      <c r="S297" s="2">
+      <c r="R297" s="49"/>
+      <c r="S297" s="93">
         <f t="shared" si="4"/>
         <v>6.9375</v>
       </c>
@@ -54234,8 +54246,8 @@
       <c r="O298" s="2"/>
       <c r="P298" s="2"/>
       <c r="Q298" s="16"/>
-      <c r="R298" s="71"/>
-      <c r="S298" s="2">
+      <c r="R298" s="49"/>
+      <c r="S298" s="93">
         <f t="shared" si="4"/>
         <v>6.55</v>
       </c>
@@ -54266,8 +54278,8 @@
       <c r="O299" s="2"/>
       <c r="P299" s="2"/>
       <c r="Q299" s="16"/>
-      <c r="R299" s="71"/>
-      <c r="S299" s="2" t="e">
+      <c r="R299" s="49"/>
+      <c r="S299" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -54316,8 +54328,8 @@
         <v>2256</v>
       </c>
       <c r="Q300" s="16"/>
-      <c r="R300" s="71"/>
-      <c r="S300" s="2">
+      <c r="R300" s="49"/>
+      <c r="S300" s="93">
         <f t="shared" si="4"/>
         <v>6.68</v>
       </c>
@@ -54368,8 +54380,8 @@
         <v>7.18</v>
       </c>
       <c r="Q301" s="16"/>
-      <c r="R301" s="71"/>
-      <c r="S301" s="2">
+      <c r="R301" s="49"/>
+      <c r="S301" s="93">
         <f t="shared" si="4"/>
         <v>6.8624999999999998</v>
       </c>
@@ -54420,8 +54432,8 @@
         <v>6.2</v>
       </c>
       <c r="Q302" s="16"/>
-      <c r="R302" s="71"/>
-      <c r="S302" s="2">
+      <c r="R302" s="49"/>
+      <c r="S302" s="93">
         <f t="shared" si="4"/>
         <v>6.17</v>
       </c>
@@ -54470,8 +54482,8 @@
         <v>7.59</v>
       </c>
       <c r="Q303" s="16"/>
-      <c r="R303" s="71"/>
-      <c r="S303" s="2">
+      <c r="R303" s="49"/>
+      <c r="S303" s="93">
         <f t="shared" si="4"/>
         <v>7.37</v>
       </c>
@@ -54510,8 +54522,8 @@
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
       <c r="Q304" s="16"/>
-      <c r="R304" s="71"/>
-      <c r="S304" s="2">
+      <c r="R304" s="49"/>
+      <c r="S304" s="93">
         <f t="shared" si="4"/>
         <v>8.09</v>
       </c>
@@ -54562,8 +54574,8 @@
         <v>7.64</v>
       </c>
       <c r="Q305" s="16"/>
-      <c r="R305" s="71"/>
-      <c r="S305" s="2">
+      <c r="R305" s="49"/>
+      <c r="S305" s="93">
         <f t="shared" si="4"/>
         <v>7.6150000000000002</v>
       </c>
@@ -54614,8 +54626,8 @@
         <v>2250</v>
       </c>
       <c r="Q306" s="16"/>
-      <c r="R306" s="71"/>
-      <c r="S306" s="2">
+      <c r="R306" s="49"/>
+      <c r="S306" s="93">
         <f t="shared" si="4"/>
         <v>6.7750000000000004</v>
       </c>
@@ -54666,8 +54678,8 @@
         <v>7.55</v>
       </c>
       <c r="Q307" s="16"/>
-      <c r="R307" s="71"/>
-      <c r="S307" s="2">
+      <c r="R307" s="49"/>
+      <c r="S307" s="93">
         <f t="shared" si="4"/>
         <v>6.9866666666666672</v>
       </c>
@@ -54718,8 +54730,8 @@
         <v>7.91</v>
       </c>
       <c r="Q308" s="16"/>
-      <c r="R308" s="71"/>
-      <c r="S308" s="2">
+      <c r="R308" s="49"/>
+      <c r="S308" s="93">
         <f t="shared" si="4"/>
         <v>7.2</v>
       </c>
@@ -54770,8 +54782,8 @@
         <v>7.68</v>
       </c>
       <c r="Q309" s="16"/>
-      <c r="R309" s="71"/>
-      <c r="S309" s="2">
+      <c r="R309" s="49"/>
+      <c r="S309" s="93">
         <f t="shared" si="4"/>
         <v>6.8</v>
       </c>
@@ -54822,8 +54834,8 @@
         <v>7.45</v>
       </c>
       <c r="Q310" s="16"/>
-      <c r="R310" s="71"/>
-      <c r="S310" s="2">
+      <c r="R310" s="49"/>
+      <c r="S310" s="93">
         <f t="shared" si="4"/>
         <v>6.8599999999999994</v>
       </c>
@@ -54874,8 +54886,8 @@
         <v>7.55</v>
       </c>
       <c r="Q311" s="16"/>
-      <c r="R311" s="71"/>
-      <c r="S311" s="2">
+      <c r="R311" s="49"/>
+      <c r="S311" s="93">
         <f t="shared" si="4"/>
         <v>7.8775000000000004</v>
       </c>
@@ -54926,8 +54938,8 @@
         <v>7.59</v>
       </c>
       <c r="Q312" s="16"/>
-      <c r="R312" s="71"/>
-      <c r="S312" s="2">
+      <c r="R312" s="49"/>
+      <c r="S312" s="93">
         <f t="shared" si="4"/>
         <v>7.53</v>
       </c>
@@ -54978,8 +54990,8 @@
         <v>7.91</v>
       </c>
       <c r="Q313" s="16"/>
-      <c r="R313" s="71"/>
-      <c r="S313" s="2">
+      <c r="R313" s="49"/>
+      <c r="S313" s="93">
         <f t="shared" si="4"/>
         <v>7.7266666666666666</v>
       </c>
@@ -55030,8 +55042,8 @@
         <v>6.32</v>
       </c>
       <c r="Q314" s="16"/>
-      <c r="R314" s="71"/>
-      <c r="S314" s="2">
+      <c r="R314" s="49"/>
+      <c r="S314" s="93">
         <f t="shared" si="4"/>
         <v>7.0925000000000002</v>
       </c>
@@ -55082,8 +55094,8 @@
         <v>954</v>
       </c>
       <c r="Q315" s="16"/>
-      <c r="R315" s="71"/>
-      <c r="S315" s="2">
+      <c r="R315" s="49"/>
+      <c r="S315" s="93">
         <f t="shared" si="4"/>
         <v>6.24</v>
       </c>
@@ -55122,8 +55134,8 @@
       <c r="O316" s="2"/>
       <c r="P316" s="2"/>
       <c r="Q316" s="16"/>
-      <c r="R316" s="71"/>
-      <c r="S316" s="2" t="e">
+      <c r="R316" s="49"/>
+      <c r="S316" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -55174,8 +55186,8 @@
         <v>2250</v>
       </c>
       <c r="Q317" s="16"/>
-      <c r="R317" s="71"/>
-      <c r="S317" s="2">
+      <c r="R317" s="49"/>
+      <c r="S317" s="93">
         <f t="shared" si="4"/>
         <v>6.1</v>
       </c>
@@ -55216,8 +55228,8 @@
       <c r="O318" s="2"/>
       <c r="P318" s="2"/>
       <c r="Q318" s="16"/>
-      <c r="R318" s="71"/>
-      <c r="S318" s="2" t="e">
+      <c r="R318" s="49"/>
+      <c r="S318" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -55268,8 +55280,8 @@
         <v>2279</v>
       </c>
       <c r="Q319" s="16"/>
-      <c r="R319" s="71"/>
-      <c r="S319" s="2">
+      <c r="R319" s="49"/>
+      <c r="S319" s="93">
         <f t="shared" si="4"/>
         <v>6.64</v>
       </c>
@@ -55320,8 +55332,8 @@
         <v>2280</v>
       </c>
       <c r="Q320" s="16"/>
-      <c r="R320" s="71"/>
-      <c r="S320" s="2" t="e">
+      <c r="R320" s="49"/>
+      <c r="S320" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -55356,8 +55368,8 @@
       <c r="O321" s="2"/>
       <c r="P321" s="2"/>
       <c r="Q321" s="16"/>
-      <c r="R321" s="71"/>
-      <c r="S321" s="2" t="e">
+      <c r="R321" s="49"/>
+      <c r="S321" s="93" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -55408,8 +55420,8 @@
         <v>7.77</v>
       </c>
       <c r="Q322" s="16"/>
-      <c r="R322" s="71"/>
-      <c r="S322" s="2">
+      <c r="R322" s="49"/>
+      <c r="S322" s="93">
         <f t="shared" ref="S322:S385" si="5">AVERAGE(M322:P322)</f>
         <v>7.5</v>
       </c>
@@ -55460,8 +55472,8 @@
         <v>7.95</v>
       </c>
       <c r="Q323" s="16"/>
-      <c r="R323" s="71"/>
-      <c r="S323" s="2">
+      <c r="R323" s="49"/>
+      <c r="S323" s="93">
         <f t="shared" si="5"/>
         <v>8.1549999999999994</v>
       </c>
@@ -55512,8 +55524,8 @@
         <v>7.77</v>
       </c>
       <c r="Q324" s="16"/>
-      <c r="R324" s="71"/>
-      <c r="S324" s="2">
+      <c r="R324" s="49"/>
+      <c r="S324" s="93">
         <f t="shared" si="5"/>
         <v>7.8624999999999998</v>
       </c>
@@ -55564,8 +55576,8 @@
         <v>2249</v>
       </c>
       <c r="Q325" s="16"/>
-      <c r="R325" s="71"/>
-      <c r="S325" s="2">
+      <c r="R325" s="49"/>
+      <c r="S325" s="93">
         <f t="shared" si="5"/>
         <v>5.8049999999999997</v>
       </c>
@@ -55602,8 +55614,8 @@
       <c r="O326" s="2"/>
       <c r="P326" s="2"/>
       <c r="Q326" s="16"/>
-      <c r="R326" s="71"/>
-      <c r="S326" s="2" t="e">
+      <c r="R326" s="49"/>
+      <c r="S326" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -55640,8 +55652,8 @@
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
       <c r="Q327" s="16"/>
-      <c r="R327" s="71"/>
-      <c r="S327" s="2">
+      <c r="R327" s="49"/>
+      <c r="S327" s="93">
         <f t="shared" si="5"/>
         <v>6.05</v>
       </c>
@@ -55692,8 +55704,8 @@
         <v>5.82</v>
       </c>
       <c r="Q328" s="16"/>
-      <c r="R328" s="71"/>
-      <c r="S328" s="2">
+      <c r="R328" s="49"/>
+      <c r="S328" s="93">
         <f t="shared" si="5"/>
         <v>6.3425000000000002</v>
       </c>
@@ -55744,8 +55756,8 @@
         <v>7.86</v>
       </c>
       <c r="Q329" s="16"/>
-      <c r="R329" s="71"/>
-      <c r="S329" s="2">
+      <c r="R329" s="49"/>
+      <c r="S329" s="93">
         <f t="shared" si="5"/>
         <v>7.7024999999999997</v>
       </c>
@@ -55794,8 +55806,8 @@
         <v>6.93</v>
       </c>
       <c r="Q330" s="16"/>
-      <c r="R330" s="71"/>
-      <c r="S330" s="2">
+      <c r="R330" s="49"/>
+      <c r="S330" s="93">
         <f t="shared" si="5"/>
         <v>7.52</v>
       </c>
@@ -55824,8 +55836,8 @@
       <c r="O331" s="2"/>
       <c r="P331" s="2"/>
       <c r="Q331" s="16"/>
-      <c r="R331" s="71"/>
-      <c r="S331" s="2" t="e">
+      <c r="R331" s="49"/>
+      <c r="S331" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -55868,8 +55880,8 @@
       </c>
       <c r="P332" s="2"/>
       <c r="Q332" s="16"/>
-      <c r="R332" s="71"/>
-      <c r="S332" s="2">
+      <c r="R332" s="49"/>
+      <c r="S332" s="93">
         <f t="shared" si="5"/>
         <v>7.45</v>
       </c>
@@ -55908,8 +55920,8 @@
       <c r="O333" s="2"/>
       <c r="P333" s="2"/>
       <c r="Q333" s="16"/>
-      <c r="R333" s="71"/>
-      <c r="S333" s="2" t="e">
+      <c r="R333" s="49"/>
+      <c r="S333" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -55946,8 +55958,8 @@
       <c r="O334" s="2"/>
       <c r="P334" s="2"/>
       <c r="Q334" s="16"/>
-      <c r="R334" s="71"/>
-      <c r="S334" s="2">
+      <c r="R334" s="49"/>
+      <c r="S334" s="93">
         <f t="shared" si="5"/>
         <v>8.59</v>
       </c>
@@ -55992,8 +56004,8 @@
         <v>8.14</v>
       </c>
       <c r="Q335" s="16"/>
-      <c r="R335" s="71"/>
-      <c r="S335" s="2">
+      <c r="R335" s="49"/>
+      <c r="S335" s="93">
         <f t="shared" si="5"/>
         <v>7.8366666666666669</v>
       </c>
@@ -56044,8 +56056,8 @@
         <v>6.73</v>
       </c>
       <c r="Q336" s="16"/>
-      <c r="R336" s="71"/>
-      <c r="S336" s="2">
+      <c r="R336" s="49"/>
+      <c r="S336" s="93">
         <f t="shared" si="5"/>
         <v>7.15</v>
       </c>
@@ -56096,8 +56108,8 @@
         <v>2281</v>
       </c>
       <c r="Q337" s="16"/>
-      <c r="R337" s="71"/>
-      <c r="S337" s="2">
+      <c r="R337" s="49"/>
+      <c r="S337" s="93">
         <f t="shared" si="5"/>
         <v>7.376666666666666</v>
       </c>
@@ -56148,8 +56160,8 @@
         <v>6.43</v>
       </c>
       <c r="Q338" s="16"/>
-      <c r="R338" s="71"/>
-      <c r="S338" s="2">
+      <c r="R338" s="49"/>
+      <c r="S338" s="93">
         <f t="shared" si="5"/>
         <v>6.6133333333333333</v>
       </c>
@@ -56200,8 +56212,8 @@
         <v>6.77</v>
       </c>
       <c r="Q339" s="16"/>
-      <c r="R339" s="71"/>
-      <c r="S339" s="2">
+      <c r="R339" s="49"/>
+      <c r="S339" s="93">
         <f t="shared" si="5"/>
         <v>7.4233333333333329</v>
       </c>
@@ -56242,8 +56254,8 @@
       </c>
       <c r="P340" s="2"/>
       <c r="Q340" s="16"/>
-      <c r="R340" s="71"/>
-      <c r="S340" s="2">
+      <c r="R340" s="49"/>
+      <c r="S340" s="93">
         <f t="shared" si="5"/>
         <v>8.32</v>
       </c>
@@ -56294,8 +56306,8 @@
         <v>2282</v>
       </c>
       <c r="Q341" s="16"/>
-      <c r="R341" s="71"/>
-      <c r="S341" s="2">
+      <c r="R341" s="49"/>
+      <c r="S341" s="93">
         <f t="shared" si="5"/>
         <v>6.7050000000000001</v>
       </c>
@@ -56346,8 +56358,8 @@
         <v>6.36</v>
       </c>
       <c r="Q342" s="16"/>
-      <c r="R342" s="71"/>
-      <c r="S342" s="2">
+      <c r="R342" s="49"/>
+      <c r="S342" s="93">
         <f t="shared" si="5"/>
         <v>7.01</v>
       </c>
@@ -56398,8 +56410,8 @@
         <v>8.41</v>
       </c>
       <c r="Q343" s="16"/>
-      <c r="R343" s="71"/>
-      <c r="S343" s="2">
+      <c r="R343" s="49"/>
+      <c r="S343" s="93">
         <f t="shared" si="5"/>
         <v>8.2866666666666671</v>
       </c>
@@ -56450,8 +56462,8 @@
         <v>8.14</v>
       </c>
       <c r="Q344" s="16"/>
-      <c r="R344" s="71"/>
-      <c r="S344" s="2">
+      <c r="R344" s="49"/>
+      <c r="S344" s="93">
         <f t="shared" si="5"/>
         <v>8.16</v>
       </c>
@@ -56502,8 +56514,8 @@
         <v>2281</v>
       </c>
       <c r="Q345" s="16"/>
-      <c r="R345" s="71"/>
-      <c r="S345" s="2">
+      <c r="R345" s="49"/>
+      <c r="S345" s="93">
         <f t="shared" si="5"/>
         <v>7.4550000000000001</v>
       </c>
@@ -56542,8 +56554,8 @@
       <c r="O346" s="2"/>
       <c r="P346" s="2"/>
       <c r="Q346" s="16"/>
-      <c r="R346" s="71"/>
-      <c r="S346" s="2">
+      <c r="R346" s="49"/>
+      <c r="S346" s="93">
         <f t="shared" si="5"/>
         <v>6.5350000000000001</v>
       </c>
@@ -56592,8 +56604,8 @@
         <v>7.05</v>
       </c>
       <c r="Q347" s="16"/>
-      <c r="R347" s="71"/>
-      <c r="S347" s="2">
+      <c r="R347" s="49"/>
+      <c r="S347" s="93">
         <f t="shared" si="5"/>
         <v>7.0466666666666669</v>
       </c>
@@ -56628,8 +56640,8 @@
       <c r="O348" s="2"/>
       <c r="P348" s="2"/>
       <c r="Q348" s="16"/>
-      <c r="R348" s="71"/>
-      <c r="S348" s="2" t="e">
+      <c r="R348" s="49"/>
+      <c r="S348" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -56666,8 +56678,8 @@
       <c r="O349" s="2"/>
       <c r="P349" s="2"/>
       <c r="Q349" s="16"/>
-      <c r="R349" s="71"/>
-      <c r="S349" s="2" t="e">
+      <c r="R349" s="49"/>
+      <c r="S349" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -56718,8 +56730,8 @@
         <v>7.68</v>
       </c>
       <c r="Q350" s="16"/>
-      <c r="R350" s="71"/>
-      <c r="S350" s="2">
+      <c r="R350" s="49"/>
+      <c r="S350" s="93">
         <f t="shared" si="5"/>
         <v>8.01</v>
       </c>
@@ -56770,8 +56782,8 @@
         <v>5.89</v>
       </c>
       <c r="Q351" s="16"/>
-      <c r="R351" s="71"/>
-      <c r="S351" s="2">
+      <c r="R351" s="49"/>
+      <c r="S351" s="93">
         <f t="shared" si="5"/>
         <v>6.2725</v>
       </c>
@@ -56822,8 +56834,8 @@
         <v>7.3</v>
       </c>
       <c r="Q352" s="16"/>
-      <c r="R352" s="71"/>
-      <c r="S352" s="2">
+      <c r="R352" s="49"/>
+      <c r="S352" s="93">
         <f t="shared" si="5"/>
         <v>7.5724999999999998</v>
       </c>
@@ -56872,8 +56884,8 @@
         <v>6.32</v>
       </c>
       <c r="Q353" s="16"/>
-      <c r="R353" s="71"/>
-      <c r="S353" s="2">
+      <c r="R353" s="49"/>
+      <c r="S353" s="93">
         <f t="shared" si="5"/>
         <v>6.88</v>
       </c>
@@ -56924,8 +56936,8 @@
         <v>7.64</v>
       </c>
       <c r="Q354" s="16"/>
-      <c r="R354" s="71"/>
-      <c r="S354" s="2">
+      <c r="R354" s="49"/>
+      <c r="S354" s="93">
         <f t="shared" si="5"/>
         <v>7.39</v>
       </c>
@@ -56976,8 +56988,8 @@
         <v>2273</v>
       </c>
       <c r="Q355" s="16"/>
-      <c r="R355" s="71"/>
-      <c r="S355" s="2" t="e">
+      <c r="R355" s="49"/>
+      <c r="S355" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -57006,8 +57018,8 @@
       <c r="O356" s="2"/>
       <c r="P356" s="2"/>
       <c r="Q356" s="16"/>
-      <c r="R356" s="71"/>
-      <c r="S356" s="2" t="e">
+      <c r="R356" s="49"/>
+      <c r="S356" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -57046,8 +57058,8 @@
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
       <c r="Q357" s="16"/>
-      <c r="R357" s="71"/>
-      <c r="S357" s="2" t="e">
+      <c r="R357" s="49"/>
+      <c r="S357" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -57098,8 +57110,8 @@
         <v>6.73</v>
       </c>
       <c r="Q358" s="16"/>
-      <c r="R358" s="71"/>
-      <c r="S358" s="2">
+      <c r="R358" s="49"/>
+      <c r="S358" s="93">
         <f t="shared" si="5"/>
         <v>6.5366666666666662</v>
       </c>
@@ -57128,8 +57140,8 @@
       <c r="O359" s="2"/>
       <c r="P359" s="2"/>
       <c r="Q359" s="16"/>
-      <c r="R359" s="71"/>
-      <c r="S359" s="2" t="e">
+      <c r="R359" s="49"/>
+      <c r="S359" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -57180,8 +57192,8 @@
         <v>2283</v>
       </c>
       <c r="Q360" s="16"/>
-      <c r="R360" s="71"/>
-      <c r="S360" s="2">
+      <c r="R360" s="49"/>
+      <c r="S360" s="93">
         <f t="shared" si="5"/>
         <v>6.05</v>
       </c>
@@ -57232,8 +57244,8 @@
         <v>8.59</v>
       </c>
       <c r="Q361" s="16"/>
-      <c r="R361" s="71"/>
-      <c r="S361" s="2">
+      <c r="R361" s="49"/>
+      <c r="S361" s="93">
         <f t="shared" si="5"/>
         <v>8.2175000000000011</v>
       </c>
@@ -57284,8 +57296,8 @@
         <v>7.84</v>
       </c>
       <c r="Q362" s="16"/>
-      <c r="R362" s="71"/>
-      <c r="S362" s="2">
+      <c r="R362" s="49"/>
+      <c r="S362" s="93">
         <f t="shared" si="5"/>
         <v>7.6449999999999996</v>
       </c>
@@ -57336,8 +57348,8 @@
         <v>2284</v>
       </c>
       <c r="Q363" s="16"/>
-      <c r="R363" s="71"/>
-      <c r="S363" s="2">
+      <c r="R363" s="49"/>
+      <c r="S363" s="93">
         <f t="shared" si="5"/>
         <v>7.67</v>
       </c>
@@ -57388,8 +57400,8 @@
         <v>7.2</v>
       </c>
       <c r="Q364" s="16"/>
-      <c r="R364" s="71"/>
-      <c r="S364" s="2">
+      <c r="R364" s="49"/>
+      <c r="S364" s="93">
         <f t="shared" si="5"/>
         <v>7.7074999999999996</v>
       </c>
@@ -57440,8 +57452,8 @@
         <v>8.09</v>
       </c>
       <c r="Q365" s="16"/>
-      <c r="R365" s="71"/>
-      <c r="S365" s="2">
+      <c r="R365" s="49"/>
+      <c r="S365" s="93">
         <f t="shared" si="5"/>
         <v>8.1574999999999989</v>
       </c>
@@ -57492,8 +57504,8 @@
         <v>6.45</v>
       </c>
       <c r="Q366" s="16"/>
-      <c r="R366" s="71"/>
-      <c r="S366" s="2">
+      <c r="R366" s="49"/>
+      <c r="S366" s="93">
         <f t="shared" si="5"/>
         <v>7.4950000000000001</v>
       </c>
@@ -57544,8 +57556,8 @@
         <v>953</v>
       </c>
       <c r="Q367" s="16"/>
-      <c r="R367" s="71"/>
-      <c r="S367" s="2">
+      <c r="R367" s="49"/>
+      <c r="S367" s="93">
         <f t="shared" si="5"/>
         <v>6.2</v>
       </c>
@@ -57596,8 +57608,8 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="Q368" s="16"/>
-      <c r="R368" s="71"/>
-      <c r="S368" s="2">
+      <c r="R368" s="49"/>
+      <c r="S368" s="93">
         <f t="shared" si="5"/>
         <v>8.5449999999999999</v>
       </c>
@@ -57648,8 +57660,8 @@
         <v>2285</v>
       </c>
       <c r="Q369" s="16"/>
-      <c r="R369" s="71"/>
-      <c r="S369" s="2">
+      <c r="R369" s="49"/>
+      <c r="S369" s="93">
         <f t="shared" si="5"/>
         <v>5.95</v>
       </c>
@@ -57700,8 +57712,8 @@
         <v>2250</v>
       </c>
       <c r="Q370" s="16"/>
-      <c r="R370" s="71"/>
-      <c r="S370" s="2">
+      <c r="R370" s="49"/>
+      <c r="S370" s="93">
         <f t="shared" si="5"/>
         <v>6.8849999999999998</v>
       </c>
@@ -57752,8 +57764,8 @@
         <v>2250</v>
       </c>
       <c r="Q371" s="16"/>
-      <c r="R371" s="71"/>
-      <c r="S371" s="2">
+      <c r="R371" s="49"/>
+      <c r="S371" s="93">
         <f t="shared" si="5"/>
         <v>6.2133333333333338</v>
       </c>
@@ -57804,8 +57816,8 @@
         <v>2272</v>
       </c>
       <c r="Q372" s="16"/>
-      <c r="R372" s="71"/>
-      <c r="S372" s="2">
+      <c r="R372" s="49"/>
+      <c r="S372" s="93">
         <f t="shared" si="5"/>
         <v>5.59</v>
       </c>
@@ -57834,8 +57846,8 @@
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
       <c r="Q373" s="16"/>
-      <c r="R373" s="71"/>
-      <c r="S373" s="2" t="e">
+      <c r="R373" s="49"/>
+      <c r="S373" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -57886,8 +57898,8 @@
         <v>5.59</v>
       </c>
       <c r="Q374" s="16"/>
-      <c r="R374" s="71"/>
-      <c r="S374" s="2">
+      <c r="R374" s="49"/>
+      <c r="S374" s="93">
         <f t="shared" si="5"/>
         <v>5.7949999999999999</v>
       </c>
@@ -57938,8 +57950,8 @@
         <v>6.34</v>
       </c>
       <c r="Q375" s="16"/>
-      <c r="R375" s="71"/>
-      <c r="S375" s="2">
+      <c r="R375" s="49"/>
+      <c r="S375" s="93">
         <f t="shared" si="5"/>
         <v>6.8633333333333333</v>
       </c>
@@ -57990,8 +58002,8 @@
         <v>8.52</v>
       </c>
       <c r="Q376" s="16"/>
-      <c r="R376" s="71"/>
-      <c r="S376" s="2">
+      <c r="R376" s="49"/>
+      <c r="S376" s="93">
         <f t="shared" si="5"/>
         <v>8.34</v>
       </c>
@@ -58030,8 +58042,8 @@
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
       <c r="Q377" s="16"/>
-      <c r="R377" s="71"/>
-      <c r="S377" s="2" t="e">
+      <c r="R377" s="49"/>
+      <c r="S377" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -58082,8 +58094,8 @@
         <v>9</v>
       </c>
       <c r="Q378" s="16"/>
-      <c r="R378" s="71"/>
-      <c r="S378" s="2">
+      <c r="R378" s="49"/>
+      <c r="S378" s="93">
         <f t="shared" si="5"/>
         <v>8.6966666666666672</v>
       </c>
@@ -58134,8 +58146,8 @@
         <v>2250</v>
       </c>
       <c r="Q379" s="16"/>
-      <c r="R379" s="71"/>
-      <c r="S379" s="2">
+      <c r="R379" s="49"/>
+      <c r="S379" s="93">
         <f t="shared" si="5"/>
         <v>6.33</v>
       </c>
@@ -58186,8 +58198,8 @@
         <v>7.14</v>
       </c>
       <c r="Q380" s="16"/>
-      <c r="R380" s="71"/>
-      <c r="S380" s="2">
+      <c r="R380" s="49"/>
+      <c r="S380" s="93">
         <f t="shared" si="5"/>
         <v>7.2549999999999999</v>
       </c>
@@ -58238,8 +58250,8 @@
         <v>5.86</v>
       </c>
       <c r="Q381" s="16"/>
-      <c r="R381" s="71"/>
-      <c r="S381" s="2">
+      <c r="R381" s="49"/>
+      <c r="S381" s="93">
         <f t="shared" si="5"/>
         <v>5.86</v>
       </c>
@@ -58290,8 +58302,8 @@
         <v>954</v>
       </c>
       <c r="Q382" s="16"/>
-      <c r="R382" s="71"/>
-      <c r="S382" s="2">
+      <c r="R382" s="49"/>
+      <c r="S382" s="93">
         <f t="shared" si="5"/>
         <v>6.3</v>
       </c>
@@ -58342,8 +58354,8 @@
         <v>6.82</v>
       </c>
       <c r="Q383" s="16"/>
-      <c r="R383" s="71"/>
-      <c r="S383" s="2">
+      <c r="R383" s="49"/>
+      <c r="S383" s="93">
         <f t="shared" si="5"/>
         <v>6.75</v>
       </c>
@@ -58394,8 +58406,8 @@
         <v>2250</v>
       </c>
       <c r="Q384" s="16"/>
-      <c r="R384" s="71"/>
-      <c r="S384" s="2" t="e">
+      <c r="R384" s="49"/>
+      <c r="S384" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -58430,8 +58442,8 @@
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
       <c r="Q385" s="16"/>
-      <c r="R385" s="71"/>
-      <c r="S385" s="2" t="e">
+      <c r="R385" s="49"/>
+      <c r="S385" s="93" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -58460,8 +58472,8 @@
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
       <c r="Q386" s="16"/>
-      <c r="R386" s="71"/>
-      <c r="S386" s="2" t="e">
+      <c r="R386" s="49"/>
+      <c r="S386" s="93" t="e">
         <f t="shared" ref="S386:S449" si="6">AVERAGE(M386:P386)</f>
         <v>#DIV/0!</v>
       </c>
@@ -58498,8 +58510,8 @@
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
       <c r="Q387" s="16"/>
-      <c r="R387" s="71"/>
-      <c r="S387" s="2" t="e">
+      <c r="R387" s="49"/>
+      <c r="S387" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -58550,8 +58562,8 @@
         <v>8.09</v>
       </c>
       <c r="Q388" s="16"/>
-      <c r="R388" s="71"/>
-      <c r="S388" s="2">
+      <c r="R388" s="49"/>
+      <c r="S388" s="93">
         <f t="shared" si="6"/>
         <v>8.2149999999999999</v>
       </c>
@@ -58602,8 +58614,8 @@
         <v>8.09</v>
       </c>
       <c r="Q389" s="16"/>
-      <c r="R389" s="71"/>
-      <c r="S389" s="2">
+      <c r="R389" s="49"/>
+      <c r="S389" s="93">
         <f t="shared" si="6"/>
         <v>8.33</v>
       </c>
@@ -58654,8 +58666,8 @@
         <v>7.23</v>
       </c>
       <c r="Q390" s="16"/>
-      <c r="R390" s="71"/>
-      <c r="S390" s="2">
+      <c r="R390" s="49"/>
+      <c r="S390" s="93">
         <f t="shared" si="6"/>
         <v>7.23</v>
       </c>
@@ -58702,8 +58714,8 @@
         <v>954</v>
       </c>
       <c r="Q391" s="16"/>
-      <c r="R391" s="71"/>
-      <c r="S391" s="2" t="e">
+      <c r="R391" s="49"/>
+      <c r="S391" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -58732,8 +58744,8 @@
       <c r="O392" s="2"/>
       <c r="P392" s="2"/>
       <c r="Q392" s="16"/>
-      <c r="R392" s="71"/>
-      <c r="S392" s="2" t="e">
+      <c r="R392" s="49"/>
+      <c r="S392" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -58784,8 +58796,8 @@
         <v>5.8</v>
       </c>
       <c r="Q393" s="16"/>
-      <c r="R393" s="71"/>
-      <c r="S393" s="2">
+      <c r="R393" s="49"/>
+      <c r="S393" s="93">
         <f t="shared" si="6"/>
         <v>6.1700000000000008</v>
       </c>
@@ -58836,8 +58848,8 @@
         <v>7.91</v>
       </c>
       <c r="Q394" s="16"/>
-      <c r="R394" s="71"/>
-      <c r="S394" s="2">
+      <c r="R394" s="49"/>
+      <c r="S394" s="93">
         <f t="shared" si="6"/>
         <v>7.92</v>
       </c>
@@ -58888,8 +58900,8 @@
         <v>5.84</v>
       </c>
       <c r="Q395" s="16"/>
-      <c r="R395" s="71"/>
-      <c r="S395" s="2">
+      <c r="R395" s="49"/>
+      <c r="S395" s="93">
         <f t="shared" si="6"/>
         <v>6.5075000000000003</v>
       </c>
@@ -58924,8 +58936,8 @@
       <c r="O396" s="2"/>
       <c r="P396" s="2"/>
       <c r="Q396" s="16"/>
-      <c r="R396" s="71"/>
-      <c r="S396" s="2" t="e">
+      <c r="R396" s="49"/>
+      <c r="S396" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -58954,8 +58966,8 @@
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
       <c r="Q397" s="16"/>
-      <c r="R397" s="71"/>
-      <c r="S397" s="2" t="e">
+      <c r="R397" s="49"/>
+      <c r="S397" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -58984,8 +58996,8 @@
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
       <c r="Q398" s="16"/>
-      <c r="R398" s="71"/>
-      <c r="S398" s="2" t="e">
+      <c r="R398" s="49"/>
+      <c r="S398" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -59036,8 +59048,8 @@
         <v>2286</v>
       </c>
       <c r="Q399" s="16"/>
-      <c r="R399" s="71"/>
-      <c r="S399" s="2">
+      <c r="R399" s="49"/>
+      <c r="S399" s="93">
         <f t="shared" si="6"/>
         <v>6.6099999999999994</v>
       </c>
@@ -59076,8 +59088,8 @@
       <c r="O400" s="2"/>
       <c r="P400" s="2"/>
       <c r="Q400" s="16"/>
-      <c r="R400" s="71"/>
-      <c r="S400" s="2" t="e">
+      <c r="R400" s="49"/>
+      <c r="S400" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -59128,8 +59140,8 @@
         <v>7.84</v>
       </c>
       <c r="Q401" s="16"/>
-      <c r="R401" s="71"/>
-      <c r="S401" s="2">
+      <c r="R401" s="49"/>
+      <c r="S401" s="93">
         <f t="shared" si="6"/>
         <v>7.9924999999999997</v>
       </c>
@@ -59180,8 +59192,8 @@
         <v>7.57</v>
       </c>
       <c r="Q402" s="16"/>
-      <c r="R402" s="71"/>
-      <c r="S402" s="2">
+      <c r="R402" s="49"/>
+      <c r="S402" s="93">
         <f t="shared" si="6"/>
         <v>7.96</v>
       </c>
@@ -59232,8 +59244,8 @@
         <v>2286</v>
       </c>
       <c r="Q403" s="16"/>
-      <c r="R403" s="71"/>
-      <c r="S403" s="2">
+      <c r="R403" s="49"/>
+      <c r="S403" s="93">
         <f t="shared" si="6"/>
         <v>6.52</v>
       </c>
@@ -59284,8 +59296,8 @@
         <v>8.11</v>
       </c>
       <c r="Q404" s="16"/>
-      <c r="R404" s="71"/>
-      <c r="S404" s="2">
+      <c r="R404" s="49"/>
+      <c r="S404" s="93">
         <f t="shared" si="6"/>
         <v>8.0625</v>
       </c>
@@ -59336,8 +59348,8 @@
         <v>2250</v>
       </c>
       <c r="Q405" s="16"/>
-      <c r="R405" s="71"/>
-      <c r="S405" s="2">
+      <c r="R405" s="49"/>
+      <c r="S405" s="93">
         <f t="shared" si="6"/>
         <v>6.5949999999999998</v>
       </c>
@@ -59388,8 +59400,8 @@
         <v>6.93</v>
       </c>
       <c r="Q406" s="16"/>
-      <c r="R406" s="71"/>
-      <c r="S406" s="2">
+      <c r="R406" s="49"/>
+      <c r="S406" s="93">
         <f t="shared" si="6"/>
         <v>7.5175000000000001</v>
       </c>
@@ -59440,8 +59452,8 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="Q407" s="16"/>
-      <c r="R407" s="71"/>
-      <c r="S407" s="2">
+      <c r="R407" s="49"/>
+      <c r="S407" s="93">
         <f t="shared" si="6"/>
         <v>8.3425000000000011</v>
       </c>
@@ -59492,8 +59504,8 @@
         <v>7.34</v>
       </c>
       <c r="Q408" s="16"/>
-      <c r="R408" s="71"/>
-      <c r="S408" s="2">
+      <c r="R408" s="49"/>
+      <c r="S408" s="93">
         <f t="shared" si="6"/>
         <v>7.79</v>
       </c>
@@ -59544,8 +59556,8 @@
         <v>7.09</v>
       </c>
       <c r="Q409" s="16"/>
-      <c r="R409" s="71"/>
-      <c r="S409" s="2">
+      <c r="R409" s="49"/>
+      <c r="S409" s="93">
         <f t="shared" si="6"/>
         <v>7.4066666666666663</v>
       </c>
@@ -59596,8 +59608,8 @@
         <v>8.82</v>
       </c>
       <c r="Q410" s="16"/>
-      <c r="R410" s="71"/>
-      <c r="S410" s="2">
+      <c r="R410" s="49"/>
+      <c r="S410" s="93">
         <f t="shared" si="6"/>
         <v>8.932500000000001</v>
       </c>
@@ -59648,8 +59660,8 @@
         <v>7.05</v>
       </c>
       <c r="Q411" s="16"/>
-      <c r="R411" s="71"/>
-      <c r="S411" s="2">
+      <c r="R411" s="49"/>
+      <c r="S411" s="93">
         <f t="shared" si="6"/>
         <v>7.6124999999999998</v>
       </c>
@@ -59700,8 +59712,8 @@
         <v>8.32</v>
       </c>
       <c r="Q412" s="16"/>
-      <c r="R412" s="71"/>
-      <c r="S412" s="2">
+      <c r="R412" s="49"/>
+      <c r="S412" s="93">
         <f t="shared" si="6"/>
         <v>8.41</v>
       </c>
@@ -59752,8 +59764,8 @@
         <v>2249</v>
       </c>
       <c r="Q413" s="16"/>
-      <c r="R413" s="71"/>
-      <c r="S413" s="2">
+      <c r="R413" s="49"/>
+      <c r="S413" s="93">
         <f t="shared" si="6"/>
         <v>6.4749999999999996</v>
       </c>
@@ -59804,8 +59816,8 @@
         <v>6.89</v>
       </c>
       <c r="Q414" s="16"/>
-      <c r="R414" s="71"/>
-      <c r="S414" s="2">
+      <c r="R414" s="49"/>
+      <c r="S414" s="93">
         <f t="shared" si="6"/>
         <v>7.4024999999999999</v>
       </c>
@@ -59856,8 +59868,8 @@
         <v>7.77</v>
       </c>
       <c r="Q415" s="16"/>
-      <c r="R415" s="71"/>
-      <c r="S415" s="2">
+      <c r="R415" s="49"/>
+      <c r="S415" s="93">
         <f t="shared" si="6"/>
         <v>7.6950000000000003</v>
       </c>
@@ -59886,8 +59898,8 @@
       <c r="O416" s="2"/>
       <c r="P416" s="2"/>
       <c r="Q416" s="16"/>
-      <c r="R416" s="71"/>
-      <c r="S416" s="2" t="e">
+      <c r="R416" s="49"/>
+      <c r="S416" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -59938,8 +59950,8 @@
         <v>2287</v>
       </c>
       <c r="Q417" s="16"/>
-      <c r="R417" s="71"/>
-      <c r="S417" s="2" t="e">
+      <c r="R417" s="49"/>
+      <c r="S417" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -59974,8 +59986,8 @@
       <c r="O418" s="2"/>
       <c r="P418" s="2"/>
       <c r="Q418" s="16"/>
-      <c r="R418" s="71"/>
-      <c r="S418" s="2" t="e">
+      <c r="R418" s="49"/>
+      <c r="S418" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60026,8 +60038,8 @@
         <v>7.91</v>
       </c>
       <c r="Q419" s="16"/>
-      <c r="R419" s="71"/>
-      <c r="S419" s="2">
+      <c r="R419" s="49"/>
+      <c r="S419" s="93">
         <f t="shared" si="6"/>
         <v>8.182500000000001</v>
       </c>
@@ -60078,8 +60090,8 @@
         <v>6.91</v>
       </c>
       <c r="Q420" s="16"/>
-      <c r="R420" s="71"/>
-      <c r="S420" s="2">
+      <c r="R420" s="49"/>
+      <c r="S420" s="93">
         <f t="shared" si="6"/>
         <v>6.58</v>
       </c>
@@ -60130,8 +60142,8 @@
         <v>2250</v>
       </c>
       <c r="Q421" s="16"/>
-      <c r="R421" s="71"/>
-      <c r="S421" s="2">
+      <c r="R421" s="49"/>
+      <c r="S421" s="93">
         <f t="shared" si="6"/>
         <v>5.9466666666666663</v>
       </c>
@@ -60182,8 +60194,8 @@
         <v>6.57</v>
       </c>
       <c r="Q422" s="16"/>
-      <c r="R422" s="71"/>
-      <c r="S422" s="2">
+      <c r="R422" s="49"/>
+      <c r="S422" s="93">
         <f t="shared" si="6"/>
         <v>6.3624999999999998</v>
       </c>
@@ -60234,8 +60246,8 @@
         <v>7.59</v>
       </c>
       <c r="Q423" s="16"/>
-      <c r="R423" s="71"/>
-      <c r="S423" s="2">
+      <c r="R423" s="49"/>
+      <c r="S423" s="93">
         <f t="shared" si="6"/>
         <v>7.7149999999999999</v>
       </c>
@@ -60286,8 +60298,8 @@
         <v>2250</v>
       </c>
       <c r="Q424" s="16"/>
-      <c r="R424" s="71"/>
-      <c r="S424" s="2">
+      <c r="R424" s="49"/>
+      <c r="S424" s="93">
         <f t="shared" si="6"/>
         <v>7.3033333333333337</v>
       </c>
@@ -60338,8 +60350,8 @@
         <v>7.16</v>
       </c>
       <c r="Q425" s="16"/>
-      <c r="R425" s="71"/>
-      <c r="S425" s="2">
+      <c r="R425" s="49"/>
+      <c r="S425" s="93">
         <f t="shared" si="6"/>
         <v>7.4375</v>
       </c>
@@ -60390,8 +60402,8 @@
         <v>2250</v>
       </c>
       <c r="Q426" s="16"/>
-      <c r="R426" s="71"/>
-      <c r="S426" s="2">
+      <c r="R426" s="49"/>
+      <c r="S426" s="93">
         <f t="shared" si="6"/>
         <v>6.8033333333333337</v>
       </c>
@@ -60442,8 +60454,8 @@
         <v>7.45</v>
       </c>
       <c r="Q427" s="16"/>
-      <c r="R427" s="71"/>
-      <c r="S427" s="2">
+      <c r="R427" s="49"/>
+      <c r="S427" s="93">
         <f t="shared" si="6"/>
         <v>8.0549999999999997</v>
       </c>
@@ -60494,8 +60506,8 @@
         <v>7.41</v>
       </c>
       <c r="Q428" s="16"/>
-      <c r="R428" s="71"/>
-      <c r="S428" s="2">
+      <c r="R428" s="49"/>
+      <c r="S428" s="93">
         <f t="shared" si="6"/>
         <v>8.2050000000000001</v>
       </c>
@@ -60524,8 +60536,8 @@
       <c r="O429" s="2"/>
       <c r="P429" s="2"/>
       <c r="Q429" s="16"/>
-      <c r="R429" s="71"/>
-      <c r="S429" s="2" t="e">
+      <c r="R429" s="49"/>
+      <c r="S429" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60554,8 +60566,8 @@
       <c r="O430" s="2"/>
       <c r="P430" s="2"/>
       <c r="Q430" s="16"/>
-      <c r="R430" s="71"/>
-      <c r="S430" s="2" t="e">
+      <c r="R430" s="49"/>
+      <c r="S430" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60584,8 +60596,8 @@
       <c r="O431" s="2"/>
       <c r="P431" s="2"/>
       <c r="Q431" s="16"/>
-      <c r="R431" s="71"/>
-      <c r="S431" s="2" t="e">
+      <c r="R431" s="49"/>
+      <c r="S431" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60636,8 +60648,8 @@
         <v>8</v>
       </c>
       <c r="Q432" s="16"/>
-      <c r="R432" s="71"/>
-      <c r="S432" s="2">
+      <c r="R432" s="49"/>
+      <c r="S432" s="93">
         <f t="shared" si="6"/>
         <v>8.6349999999999998</v>
       </c>
@@ -60688,8 +60700,8 @@
         <v>6.27</v>
       </c>
       <c r="Q433" s="16"/>
-      <c r="R433" s="71"/>
-      <c r="S433" s="2">
+      <c r="R433" s="49"/>
+      <c r="S433" s="93">
         <f t="shared" si="6"/>
         <v>6.7566666666666668</v>
       </c>
@@ -60726,8 +60738,8 @@
       <c r="O434" s="2"/>
       <c r="P434" s="2"/>
       <c r="Q434" s="16"/>
-      <c r="R434" s="71"/>
-      <c r="S434" s="2" t="e">
+      <c r="R434" s="49"/>
+      <c r="S434" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60774,8 +60786,8 @@
         <v>954</v>
       </c>
       <c r="Q435" s="16"/>
-      <c r="R435" s="71"/>
-      <c r="S435" s="2">
+      <c r="R435" s="49"/>
+      <c r="S435" s="93">
         <f t="shared" si="6"/>
         <v>6.4</v>
       </c>
@@ -60826,8 +60838,8 @@
         <v>7.23</v>
       </c>
       <c r="Q436" s="16"/>
-      <c r="R436" s="71"/>
-      <c r="S436" s="2">
+      <c r="R436" s="49"/>
+      <c r="S436" s="93">
         <f t="shared" si="6"/>
         <v>7.8650000000000002</v>
       </c>
@@ -60856,8 +60868,8 @@
       <c r="O437" s="2"/>
       <c r="P437" s="2"/>
       <c r="Q437" s="16"/>
-      <c r="R437" s="71"/>
-      <c r="S437" s="2" t="e">
+      <c r="R437" s="49"/>
+      <c r="S437" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60908,8 +60920,8 @@
         <v>7.48</v>
       </c>
       <c r="Q438" s="16"/>
-      <c r="R438" s="71"/>
-      <c r="S438" s="2">
+      <c r="R438" s="49"/>
+      <c r="S438" s="93">
         <f t="shared" si="6"/>
         <v>7.78</v>
       </c>
@@ -60938,8 +60950,8 @@
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
       <c r="Q439" s="16"/>
-      <c r="R439" s="71"/>
-      <c r="S439" s="2" t="e">
+      <c r="R439" s="49"/>
+      <c r="S439" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -60968,8 +60980,8 @@
       <c r="O440" s="2"/>
       <c r="P440" s="2"/>
       <c r="Q440" s="16"/>
-      <c r="R440" s="71"/>
-      <c r="S440" s="2" t="e">
+      <c r="R440" s="49"/>
+      <c r="S440" s="93" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
@@ -61020,8 +61032,8 @@
         <v>6.7</v>
       </c>
       <c r="Q441" s="16"/>
-      <c r="R441" s="71"/>
-      <c r="S441" s="2">
+      <c r="R441" s="49"/>
+      <c r="S441" s="93">
         <f t="shared" si="6"/>
         <v>6.6</v>
       </c>
@@ -61072,8 +61084,8 @@
         <v>7.7</v>
       </c>
       <c r="Q442" s="16"/>
-      <c r="R442" s="71"/>
-      <c r="S442" s="2">
+      <c r="R442" s="49"/>
+      <c r="S442" s="93">
         <f t="shared" si="6"/>
         <v>8.1624999999999996</v>
       </c>
@@ -61124,8 +61136,8 @@
         <v>2277</v>
       </c>
       <c r="Q443" s="16"/>
-      <c r="R443" s="71"/>
-      <c r="S443" s="2">
+      <c r="R443" s="49"/>
+      <c r="S443" s="93">
         <f t="shared" si="6"/>
         <v>7.6766666666666667</v>
       </c>
@@ -61176,8 +61188,8 @@
         <v>7.91</v>
       </c>
       <c r="Q444" s="16"/>
-      <c r="R444" s="71"/>
-      <c r="S444" s="2">
+      <c r="R444" s="49"/>
+      <c r="S444" s="93">
         <f t="shared" si="6"/>
         <v>8.067499999999999</v>
       </c>
@@ -61228,8 +61240,8 @@
         <v>6.36</v>
       </c>
       <c r="Q445" s="16"/>
-      <c r="R445" s="71"/>
-      <c r="S445" s="2">
+      <c r="R445" s="49"/>
+      <c r="S445" s="93">
         <f t="shared" si="6"/>
         <v>6.5175000000000001</v>
       </c>
@@ -61280,8 +61292,8 @@
         <v>7.39</v>
       </c>
       <c r="Q446" s="16"/>
-      <c r="R446" s="71"/>
-      <c r="S446" s="2">
+      <c r="R446" s="49"/>
+      <c r="S446" s="93">
         <f t="shared" si="6"/>
         <v>7.6875</v>
       </c>
@@ -61332,8 +61344,8 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="Q447" s="16"/>
-      <c r="R447" s="71"/>
-      <c r="S447" s="2">
+      <c r="R447" s="49"/>
+      <c r="S447" s="93">
         <f t="shared" si="6"/>
         <v>9.0633333333333344</v>
       </c>
@@ -61384,8 +61396,8 @@
         <v>7.8</v>
       </c>
       <c r="Q448" s="16"/>
-      <c r="R448" s="71"/>
-      <c r="S448" s="2">
+      <c r="R448" s="49"/>
+      <c r="S448" s="93">
         <f t="shared" si="6"/>
         <v>8.2774999999999999</v>
       </c>
@@ -61436,8 +61448,8 @@
         <v>8</v>
       </c>
       <c r="Q449" s="16"/>
-      <c r="R449" s="71"/>
-      <c r="S449" s="2">
+      <c r="R449" s="49"/>
+      <c r="S449" s="93">
         <f t="shared" si="6"/>
         <v>8.42</v>
       </c>
@@ -61488,8 +61500,8 @@
         <v>7.55</v>
       </c>
       <c r="Q450" s="16"/>
-      <c r="R450" s="71"/>
-      <c r="S450" s="2">
+      <c r="R450" s="49"/>
+      <c r="S450" s="93">
         <f t="shared" ref="S450:S513" si="7">AVERAGE(M450:P450)</f>
         <v>7.6025</v>
       </c>
@@ -61540,8 +61552,8 @@
         <v>7.98</v>
       </c>
       <c r="Q451" s="16"/>
-      <c r="R451" s="71"/>
-      <c r="S451" s="2">
+      <c r="R451" s="49"/>
+      <c r="S451" s="93">
         <f t="shared" si="7"/>
         <v>8.2800000000000011</v>
       </c>
@@ -61592,8 +61604,8 @@
         <v>7.36</v>
       </c>
       <c r="Q452" s="16"/>
-      <c r="R452" s="71"/>
-      <c r="S452" s="2">
+      <c r="R452" s="49"/>
+      <c r="S452" s="93">
         <f t="shared" si="7"/>
         <v>7.9233333333333329</v>
       </c>
@@ -61630,8 +61642,8 @@
       <c r="O453" s="2"/>
       <c r="P453" s="2"/>
       <c r="Q453" s="16"/>
-      <c r="R453" s="71"/>
-      <c r="S453" s="2" t="e">
+      <c r="R453" s="49"/>
+      <c r="S453" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -61670,8 +61682,8 @@
       <c r="O454" s="2"/>
       <c r="P454" s="2"/>
       <c r="Q454" s="16"/>
-      <c r="R454" s="71"/>
-      <c r="S454" s="2">
+      <c r="R454" s="49"/>
+      <c r="S454" s="93">
         <f t="shared" si="7"/>
         <v>7.18</v>
       </c>
@@ -61722,8 +61734,8 @@
         <v>7.43</v>
       </c>
       <c r="Q455" s="16"/>
-      <c r="R455" s="71"/>
-      <c r="S455" s="2">
+      <c r="R455" s="49"/>
+      <c r="S455" s="93">
         <f t="shared" si="7"/>
         <v>7.79</v>
       </c>
@@ -61774,8 +61786,8 @@
         <v>2268</v>
       </c>
       <c r="Q456" s="16"/>
-      <c r="R456" s="71"/>
-      <c r="S456" s="2">
+      <c r="R456" s="49"/>
+      <c r="S456" s="93">
         <f t="shared" si="7"/>
         <v>7.0600000000000005</v>
       </c>
@@ -61826,8 +61838,8 @@
         <v>6.59</v>
       </c>
       <c r="Q457" s="16"/>
-      <c r="R457" s="71"/>
-      <c r="S457" s="2">
+      <c r="R457" s="49"/>
+      <c r="S457" s="93">
         <f t="shared" si="7"/>
         <v>7.27</v>
       </c>
@@ -61845,7 +61857,7 @@
       <c r="D458" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="E458" s="1" t="s">
+      <c r="E458" s="91" t="s">
         <v>1292</v>
       </c>
       <c r="F458" s="26"/>
@@ -61866,8 +61878,8 @@
       <c r="O458" s="2"/>
       <c r="P458" s="2"/>
       <c r="Q458" s="16"/>
-      <c r="R458" s="71"/>
-      <c r="S458" s="2" t="e">
+      <c r="R458" s="49"/>
+      <c r="S458" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -61918,8 +61930,8 @@
         <v>6.95</v>
       </c>
       <c r="Q459" s="16"/>
-      <c r="R459" s="71"/>
-      <c r="S459" s="2">
+      <c r="R459" s="49"/>
+      <c r="S459" s="93">
         <f t="shared" si="7"/>
         <v>7.62</v>
       </c>
@@ -61970,8 +61982,8 @@
         <v>2281</v>
       </c>
       <c r="Q460" s="16"/>
-      <c r="R460" s="71"/>
-      <c r="S460" s="2">
+      <c r="R460" s="49"/>
+      <c r="S460" s="93">
         <f t="shared" si="7"/>
         <v>6.9749999999999996</v>
       </c>
@@ -62008,8 +62020,8 @@
       <c r="O461" s="2"/>
       <c r="P461" s="2"/>
       <c r="Q461" s="16"/>
-      <c r="R461" s="71"/>
-      <c r="S461" s="2" t="e">
+      <c r="R461" s="49"/>
+      <c r="S461" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -62060,8 +62072,8 @@
         <v>8.77</v>
       </c>
       <c r="Q462" s="16"/>
-      <c r="R462" s="71"/>
-      <c r="S462" s="2">
+      <c r="R462" s="49"/>
+      <c r="S462" s="93">
         <f t="shared" si="7"/>
         <v>8.8849999999999998</v>
       </c>
@@ -62112,8 +62124,8 @@
         <v>6.55</v>
       </c>
       <c r="Q463" s="16"/>
-      <c r="R463" s="71"/>
-      <c r="S463" s="2">
+      <c r="R463" s="49"/>
+      <c r="S463" s="93">
         <f t="shared" si="7"/>
         <v>6.72</v>
       </c>
@@ -62164,8 +62176,8 @@
         <v>6.73</v>
       </c>
       <c r="Q464" s="16"/>
-      <c r="R464" s="71"/>
-      <c r="S464" s="2">
+      <c r="R464" s="49"/>
+      <c r="S464" s="93">
         <f t="shared" si="7"/>
         <v>7.3850000000000007</v>
       </c>
@@ -62216,8 +62228,8 @@
         <v>2281</v>
       </c>
       <c r="Q465" s="16"/>
-      <c r="R465" s="71"/>
-      <c r="S465" s="2">
+      <c r="R465" s="49"/>
+      <c r="S465" s="93">
         <f t="shared" si="7"/>
         <v>7.41</v>
       </c>
@@ -62268,8 +62280,8 @@
         <v>2288</v>
       </c>
       <c r="Q466" s="16"/>
-      <c r="R466" s="71"/>
-      <c r="S466" s="2">
+      <c r="R466" s="49"/>
+      <c r="S466" s="93">
         <f t="shared" si="7"/>
         <v>6.25</v>
       </c>
@@ -62320,8 +62332,8 @@
         <v>7.2</v>
       </c>
       <c r="Q467" s="16"/>
-      <c r="R467" s="71"/>
-      <c r="S467" s="2">
+      <c r="R467" s="49"/>
+      <c r="S467" s="93">
         <f t="shared" si="7"/>
         <v>8.1274999999999995</v>
       </c>
@@ -62372,8 +62384,8 @@
         <v>6.82</v>
       </c>
       <c r="Q468" s="16"/>
-      <c r="R468" s="71"/>
-      <c r="S468" s="2">
+      <c r="R468" s="49"/>
+      <c r="S468" s="93">
         <f t="shared" si="7"/>
         <v>7.53</v>
       </c>
@@ -62424,8 +62436,8 @@
         <v>2289</v>
       </c>
       <c r="Q469" s="16"/>
-      <c r="R469" s="71"/>
-      <c r="S469" s="2">
+      <c r="R469" s="49"/>
+      <c r="S469" s="93">
         <f t="shared" si="7"/>
         <v>7.45</v>
       </c>
@@ -62476,8 +62488,8 @@
         <v>8.18</v>
       </c>
       <c r="Q470" s="16"/>
-      <c r="R470" s="71"/>
-      <c r="S470" s="2">
+      <c r="R470" s="49"/>
+      <c r="S470" s="93">
         <f t="shared" si="7"/>
         <v>8.51</v>
       </c>
@@ -62528,8 +62540,8 @@
         <v>2250</v>
       </c>
       <c r="Q471" s="16"/>
-      <c r="R471" s="71"/>
-      <c r="S471" s="2">
+      <c r="R471" s="49"/>
+      <c r="S471" s="93">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
@@ -62580,8 +62592,8 @@
         <v>2290</v>
       </c>
       <c r="Q472" s="16"/>
-      <c r="R472" s="71"/>
-      <c r="S472" s="2">
+      <c r="R472" s="49"/>
+      <c r="S472" s="93">
         <f t="shared" si="7"/>
         <v>6.8849999999999998</v>
       </c>
@@ -62599,7 +62611,7 @@
       <c r="D473" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="E473" s="1" t="s">
+      <c r="E473" s="91" t="s">
         <v>891</v>
       </c>
       <c r="F473" s="26">
@@ -62632,8 +62644,8 @@
         <v>2290</v>
       </c>
       <c r="Q473" s="16"/>
-      <c r="R473" s="71"/>
-      <c r="S473" s="2">
+      <c r="R473" s="49"/>
+      <c r="S473" s="93">
         <f t="shared" si="7"/>
         <v>7.3666666666666671</v>
       </c>
@@ -62684,8 +62696,8 @@
         <v>6.36</v>
       </c>
       <c r="Q474" s="16"/>
-      <c r="R474" s="71"/>
-      <c r="S474" s="2">
+      <c r="R474" s="49"/>
+      <c r="S474" s="93">
         <f t="shared" si="7"/>
         <v>7.18</v>
       </c>
@@ -62734,8 +62746,8 @@
         <v>7.64</v>
       </c>
       <c r="Q475" s="16"/>
-      <c r="R475" s="71"/>
-      <c r="S475" s="2">
+      <c r="R475" s="49"/>
+      <c r="S475" s="93">
         <f t="shared" si="7"/>
         <v>7.8650000000000002</v>
       </c>
@@ -62786,8 +62798,8 @@
         <v>6.95</v>
       </c>
       <c r="Q476" s="16"/>
-      <c r="R476" s="71"/>
-      <c r="S476" s="2">
+      <c r="R476" s="49"/>
+      <c r="S476" s="93">
         <f t="shared" si="7"/>
         <v>7.3624999999999998</v>
       </c>
@@ -62822,8 +62834,8 @@
       <c r="O477" s="2"/>
       <c r="P477" s="2"/>
       <c r="Q477" s="16"/>
-      <c r="R477" s="71"/>
-      <c r="S477" s="2" t="e">
+      <c r="R477" s="49"/>
+      <c r="S477" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -62874,8 +62886,8 @@
         <v>6.57</v>
       </c>
       <c r="Q478" s="16"/>
-      <c r="R478" s="71"/>
-      <c r="S478" s="2">
+      <c r="R478" s="49"/>
+      <c r="S478" s="93">
         <f t="shared" si="7"/>
         <v>7.585</v>
       </c>
@@ -62926,8 +62938,8 @@
         <v>2291</v>
       </c>
       <c r="Q479" s="16"/>
-      <c r="R479" s="71"/>
-      <c r="S479" s="2">
+      <c r="R479" s="49"/>
+      <c r="S479" s="93">
         <f t="shared" si="7"/>
         <v>7.49</v>
       </c>
@@ -62978,8 +62990,8 @@
         <v>6.18</v>
       </c>
       <c r="Q480" s="16"/>
-      <c r="R480" s="71"/>
-      <c r="S480" s="2">
+      <c r="R480" s="49"/>
+      <c r="S480" s="93">
         <f t="shared" si="7"/>
         <v>7.2275</v>
       </c>
@@ -63030,8 +63042,8 @@
         <v>6.77</v>
       </c>
       <c r="Q481" s="16"/>
-      <c r="R481" s="71"/>
-      <c r="S481" s="2">
+      <c r="R481" s="49"/>
+      <c r="S481" s="93">
         <f t="shared" si="7"/>
         <v>7.7424999999999997</v>
       </c>
@@ -63082,8 +63094,8 @@
         <v>7.64</v>
       </c>
       <c r="Q482" s="16"/>
-      <c r="R482" s="71"/>
-      <c r="S482" s="2">
+      <c r="R482" s="49"/>
+      <c r="S482" s="93">
         <f t="shared" si="7"/>
         <v>7.9625000000000004</v>
       </c>
@@ -63134,8 +63146,8 @@
         <v>2250</v>
       </c>
       <c r="Q483" s="16"/>
-      <c r="R483" s="71"/>
-      <c r="S483" s="2">
+      <c r="R483" s="49"/>
+      <c r="S483" s="93">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -63186,8 +63198,8 @@
         <v>6.25</v>
       </c>
       <c r="Q484" s="16"/>
-      <c r="R484" s="71"/>
-      <c r="S484" s="2">
+      <c r="R484" s="49"/>
+      <c r="S484" s="93">
         <f t="shared" si="7"/>
         <v>7.3250000000000002</v>
       </c>
@@ -63238,8 +63250,8 @@
         <v>8</v>
       </c>
       <c r="Q485" s="16"/>
-      <c r="R485" s="71"/>
-      <c r="S485" s="2">
+      <c r="R485" s="49"/>
+      <c r="S485" s="93">
         <f t="shared" si="7"/>
         <v>8.0150000000000006</v>
       </c>
@@ -63268,8 +63280,8 @@
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
       <c r="Q486" s="16"/>
-      <c r="R486" s="71"/>
-      <c r="S486" s="2" t="e">
+      <c r="R486" s="49"/>
+      <c r="S486" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -63298,8 +63310,8 @@
       <c r="O487" s="2"/>
       <c r="P487" s="2"/>
       <c r="Q487" s="16"/>
-      <c r="R487" s="71"/>
-      <c r="S487" s="2" t="e">
+      <c r="R487" s="49"/>
+      <c r="S487" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -63350,8 +63362,8 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="Q488" s="16"/>
-      <c r="R488" s="71"/>
-      <c r="S488" s="2">
+      <c r="R488" s="49"/>
+      <c r="S488" s="93">
         <f t="shared" si="7"/>
         <v>8.2850000000000001</v>
       </c>
@@ -63402,8 +63414,8 @@
         <v>8.18</v>
       </c>
       <c r="Q489" s="16"/>
-      <c r="R489" s="71"/>
-      <c r="S489" s="2">
+      <c r="R489" s="49"/>
+      <c r="S489" s="93">
         <f t="shared" si="7"/>
         <v>7.8449999999999998</v>
       </c>
@@ -63454,8 +63466,8 @@
         <v>6.27</v>
       </c>
       <c r="Q490" s="16"/>
-      <c r="R490" s="71"/>
-      <c r="S490" s="2">
+      <c r="R490" s="49"/>
+      <c r="S490" s="93">
         <f t="shared" si="7"/>
         <v>6.8933333333333335</v>
       </c>
@@ -63506,8 +63518,8 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="Q491" s="16"/>
-      <c r="R491" s="71"/>
-      <c r="S491" s="2">
+      <c r="R491" s="49"/>
+      <c r="S491" s="93">
         <f t="shared" si="7"/>
         <v>7.9450000000000003</v>
       </c>
@@ -63558,8 +63570,8 @@
         <v>6.98</v>
       </c>
       <c r="Q492" s="16"/>
-      <c r="R492" s="71"/>
-      <c r="S492" s="2">
+      <c r="R492" s="49"/>
+      <c r="S492" s="93">
         <f t="shared" si="7"/>
         <v>7.1550000000000002</v>
       </c>
@@ -63610,8 +63622,8 @@
         <v>8.27</v>
       </c>
       <c r="Q493" s="16"/>
-      <c r="R493" s="71"/>
-      <c r="S493" s="2">
+      <c r="R493" s="49"/>
+      <c r="S493" s="93">
         <f t="shared" si="7"/>
         <v>7.51</v>
       </c>
@@ -63660,8 +63672,8 @@
         <v>2292</v>
       </c>
       <c r="Q494" s="16"/>
-      <c r="R494" s="71"/>
-      <c r="S494" s="2">
+      <c r="R494" s="49"/>
+      <c r="S494" s="93">
         <f t="shared" si="7"/>
         <v>6.05</v>
       </c>
@@ -63712,8 +63724,8 @@
         <v>7.05</v>
       </c>
       <c r="Q495" s="16"/>
-      <c r="R495" s="71"/>
-      <c r="S495" s="2">
+      <c r="R495" s="49"/>
+      <c r="S495" s="93">
         <f t="shared" si="7"/>
         <v>7.3</v>
       </c>
@@ -63764,8 +63776,8 @@
         <v>6.16</v>
       </c>
       <c r="Q496" s="16"/>
-      <c r="R496" s="71"/>
-      <c r="S496" s="2">
+      <c r="R496" s="49"/>
+      <c r="S496" s="93">
         <f t="shared" si="7"/>
         <v>6.1050000000000004</v>
       </c>
@@ -63794,8 +63806,8 @@
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
       <c r="Q497" s="16"/>
-      <c r="R497" s="71"/>
-      <c r="S497" s="2" t="e">
+      <c r="R497" s="49"/>
+      <c r="S497" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -63830,8 +63842,8 @@
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
       <c r="Q498" s="16"/>
-      <c r="R498" s="71"/>
-      <c r="S498" s="2" t="e">
+      <c r="R498" s="49"/>
+      <c r="S498" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -63882,8 +63894,8 @@
         <v>7.23</v>
       </c>
       <c r="Q499" s="16"/>
-      <c r="R499" s="71"/>
-      <c r="S499" s="2">
+      <c r="R499" s="49"/>
+      <c r="S499" s="93">
         <f t="shared" si="7"/>
         <v>6.9625000000000004</v>
       </c>
@@ -63934,8 +63946,8 @@
         <v>7.41</v>
       </c>
       <c r="Q500" s="16"/>
-      <c r="R500" s="71"/>
-      <c r="S500" s="2">
+      <c r="R500" s="49"/>
+      <c r="S500" s="93">
         <f t="shared" si="7"/>
         <v>6.9649999999999999</v>
       </c>
@@ -63986,8 +63998,8 @@
         <v>6.09</v>
       </c>
       <c r="Q501" s="16"/>
-      <c r="R501" s="71"/>
-      <c r="S501" s="2">
+      <c r="R501" s="49"/>
+      <c r="S501" s="93">
         <f t="shared" si="7"/>
         <v>6.2666666666666666</v>
       </c>
@@ -64016,8 +64028,8 @@
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
       <c r="Q502" s="16"/>
-      <c r="R502" s="71"/>
-      <c r="S502" s="2" t="e">
+      <c r="R502" s="49"/>
+      <c r="S502" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -64068,8 +64080,8 @@
         <v>7.86</v>
       </c>
       <c r="Q503" s="16"/>
-      <c r="R503" s="71"/>
-      <c r="S503" s="2">
+      <c r="R503" s="49"/>
+      <c r="S503" s="93">
         <f t="shared" si="7"/>
         <v>7.34</v>
       </c>
@@ -64120,8 +64132,8 @@
         <v>2286</v>
       </c>
       <c r="Q504" s="16"/>
-      <c r="R504" s="71"/>
-      <c r="S504" s="2">
+      <c r="R504" s="49"/>
+      <c r="S504" s="93">
         <f t="shared" si="7"/>
         <v>6.32</v>
       </c>
@@ -64172,8 +64184,8 @@
         <v>6.7</v>
       </c>
       <c r="Q505" s="16"/>
-      <c r="R505" s="71"/>
-      <c r="S505" s="2">
+      <c r="R505" s="49"/>
+      <c r="S505" s="93">
         <f t="shared" si="7"/>
         <v>7.04</v>
       </c>
@@ -64224,8 +64236,8 @@
         <v>2272</v>
       </c>
       <c r="Q506" s="16"/>
-      <c r="R506" s="71"/>
-      <c r="S506" s="2">
+      <c r="R506" s="49"/>
+      <c r="S506" s="93">
         <f t="shared" si="7"/>
         <v>6.14</v>
       </c>
@@ -64276,8 +64288,8 @@
         <v>6.41</v>
       </c>
       <c r="Q507" s="16"/>
-      <c r="R507" s="71"/>
-      <c r="S507" s="2">
+      <c r="R507" s="49"/>
+      <c r="S507" s="93">
         <f t="shared" si="7"/>
         <v>6.4866666666666672</v>
       </c>
@@ -64328,8 +64340,8 @@
         <v>8.41</v>
       </c>
       <c r="Q508" s="16"/>
-      <c r="R508" s="71"/>
-      <c r="S508" s="2">
+      <c r="R508" s="49"/>
+      <c r="S508" s="93">
         <f t="shared" si="7"/>
         <v>7.68</v>
       </c>
@@ -64378,8 +64390,8 @@
         <v>6.59</v>
       </c>
       <c r="Q509" s="16"/>
-      <c r="R509" s="71"/>
-      <c r="S509" s="2">
+      <c r="R509" s="49"/>
+      <c r="S509" s="93">
         <f t="shared" si="7"/>
         <v>6.5249999999999995</v>
       </c>
@@ -64430,8 +64442,8 @@
         <v>7.32</v>
       </c>
       <c r="Q510" s="16"/>
-      <c r="R510" s="71"/>
-      <c r="S510" s="2">
+      <c r="R510" s="49"/>
+      <c r="S510" s="93">
         <f t="shared" si="7"/>
         <v>7.03</v>
       </c>
@@ -64482,8 +64494,8 @@
         <v>2279</v>
       </c>
       <c r="Q511" s="16"/>
-      <c r="R511" s="71"/>
-      <c r="S511" s="2">
+      <c r="R511" s="49"/>
+      <c r="S511" s="93">
         <f t="shared" si="7"/>
         <v>6.7249999999999996</v>
       </c>
@@ -64534,8 +64546,8 @@
         <v>2293</v>
       </c>
       <c r="Q512" s="16"/>
-      <c r="R512" s="71"/>
-      <c r="S512" s="2">
+      <c r="R512" s="49"/>
+      <c r="S512" s="93">
         <f t="shared" si="7"/>
         <v>6.8933333333333335</v>
       </c>
@@ -64564,8 +64576,8 @@
       <c r="O513" s="2"/>
       <c r="P513" s="2"/>
       <c r="Q513" s="16"/>
-      <c r="R513" s="71"/>
-      <c r="S513" s="2" t="e">
+      <c r="R513" s="49"/>
+      <c r="S513" s="93" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
@@ -64606,8 +64618,8 @@
       <c r="O514" s="2"/>
       <c r="P514" s="2"/>
       <c r="Q514" s="16"/>
-      <c r="R514" s="71"/>
-      <c r="S514" s="2" t="e">
+      <c r="R514" s="49"/>
+      <c r="S514" s="93" t="e">
         <f t="shared" ref="S514:S577" si="8">AVERAGE(M514:P514)</f>
         <v>#DIV/0!</v>
       </c>
@@ -64658,8 +64670,8 @@
         <v>6.2</v>
       </c>
       <c r="Q515" s="16"/>
-      <c r="R515" s="71"/>
-      <c r="S515" s="2">
+      <c r="R515" s="49"/>
+      <c r="S515" s="93">
         <f t="shared" si="8"/>
         <v>6.416666666666667</v>
       </c>
@@ -64708,8 +64720,8 @@
         <v>2272</v>
       </c>
       <c r="Q516" s="16"/>
-      <c r="R516" s="71"/>
-      <c r="S516" s="2">
+      <c r="R516" s="49"/>
+      <c r="S516" s="93">
         <f t="shared" si="8"/>
         <v>6.65</v>
       </c>
@@ -64760,8 +64772,8 @@
         <v>7.02</v>
       </c>
       <c r="Q517" s="16"/>
-      <c r="R517" s="71"/>
-      <c r="S517" s="2">
+      <c r="R517" s="49"/>
+      <c r="S517" s="93">
         <f t="shared" si="8"/>
         <v>7.47</v>
       </c>
@@ -64812,8 +64824,8 @@
         <v>8.18</v>
       </c>
       <c r="Q518" s="16"/>
-      <c r="R518" s="71"/>
-      <c r="S518" s="2">
+      <c r="R518" s="49"/>
+      <c r="S518" s="93">
         <f t="shared" si="8"/>
         <v>8.25</v>
       </c>
@@ -64864,8 +64876,8 @@
         <v>2279</v>
       </c>
       <c r="Q519" s="16"/>
-      <c r="R519" s="71"/>
-      <c r="S519" s="2">
+      <c r="R519" s="49"/>
+      <c r="S519" s="93">
         <f t="shared" si="8"/>
         <v>8.06</v>
       </c>
@@ -64916,8 +64928,8 @@
         <v>2279</v>
       </c>
       <c r="Q520" s="16"/>
-      <c r="R520" s="71"/>
-      <c r="S520" s="2">
+      <c r="R520" s="49"/>
+      <c r="S520" s="93">
         <f t="shared" si="8"/>
         <v>6.28</v>
       </c>
@@ -64968,8 +64980,8 @@
         <v>2283</v>
       </c>
       <c r="Q521" s="16"/>
-      <c r="R521" s="71"/>
-      <c r="S521" s="2">
+      <c r="R521" s="49"/>
+      <c r="S521" s="93">
         <f t="shared" si="8"/>
         <v>6.8</v>
       </c>
@@ -65020,8 +65032,8 @@
         <v>2279</v>
       </c>
       <c r="Q522" s="16"/>
-      <c r="R522" s="71"/>
-      <c r="S522" s="2">
+      <c r="R522" s="49"/>
+      <c r="S522" s="93">
         <f t="shared" si="8"/>
         <v>6.2433333333333332</v>
       </c>
@@ -65072,8 +65084,8 @@
         <v>2283</v>
       </c>
       <c r="Q523" s="16"/>
-      <c r="R523" s="71"/>
-      <c r="S523" s="2">
+      <c r="R523" s="49"/>
+      <c r="S523" s="93">
         <f t="shared" si="8"/>
         <v>6.2149999999999999</v>
       </c>
@@ -65124,8 +65136,8 @@
         <v>7.43</v>
       </c>
       <c r="Q524" s="16"/>
-      <c r="R524" s="71"/>
-      <c r="S524" s="2">
+      <c r="R524" s="49"/>
+      <c r="S524" s="93">
         <f t="shared" si="8"/>
         <v>7.5066666666666668</v>
       </c>
@@ -65176,8 +65188,8 @@
         <v>2294</v>
       </c>
       <c r="Q525" s="16"/>
-      <c r="R525" s="71"/>
-      <c r="S525" s="2">
+      <c r="R525" s="49"/>
+      <c r="S525" s="93">
         <f t="shared" si="8"/>
         <v>7.18</v>
       </c>
@@ -65228,8 +65240,8 @@
         <v>2279</v>
       </c>
       <c r="Q526" s="16"/>
-      <c r="R526" s="71"/>
-      <c r="S526" s="2">
+      <c r="R526" s="49"/>
+      <c r="S526" s="93">
         <f t="shared" si="8"/>
         <v>6.84</v>
       </c>
@@ -65278,8 +65290,8 @@
         <v>7.07</v>
       </c>
       <c r="Q527" s="16"/>
-      <c r="R527" s="71"/>
-      <c r="S527" s="2">
+      <c r="R527" s="49"/>
+      <c r="S527" s="93">
         <f t="shared" si="8"/>
         <v>7.8475000000000001</v>
       </c>
@@ -65330,8 +65342,8 @@
         <v>6.66</v>
       </c>
       <c r="Q528" s="16"/>
-      <c r="R528" s="71"/>
-      <c r="S528" s="2">
+      <c r="R528" s="49"/>
+      <c r="S528" s="93">
         <f t="shared" si="8"/>
         <v>7.4725000000000001</v>
       </c>
@@ -65382,8 +65394,8 @@
         <v>7.34</v>
       </c>
       <c r="Q529" s="16"/>
-      <c r="R529" s="71"/>
-      <c r="S529" s="2">
+      <c r="R529" s="49"/>
+      <c r="S529" s="93">
         <f t="shared" si="8"/>
         <v>7.6074999999999999</v>
       </c>
@@ -65422,8 +65434,8 @@
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
       <c r="Q530" s="16"/>
-      <c r="R530" s="71"/>
-      <c r="S530" s="2" t="e">
+      <c r="R530" s="49"/>
+      <c r="S530" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -65458,8 +65470,8 @@
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
       <c r="Q531" s="16"/>
-      <c r="R531" s="71"/>
-      <c r="S531" s="2" t="e">
+      <c r="R531" s="49"/>
+      <c r="S531" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -65510,8 +65522,8 @@
         <v>7.41</v>
       </c>
       <c r="Q532" s="16"/>
-      <c r="R532" s="71"/>
-      <c r="S532" s="2">
+      <c r="R532" s="49"/>
+      <c r="S532" s="93">
         <f t="shared" si="8"/>
         <v>7.45</v>
       </c>
@@ -65562,8 +65574,8 @@
         <v>6.77</v>
       </c>
       <c r="Q533" s="16"/>
-      <c r="R533" s="71"/>
-      <c r="S533" s="2">
+      <c r="R533" s="49"/>
+      <c r="S533" s="93">
         <f t="shared" si="8"/>
         <v>6.8033333333333337</v>
       </c>
@@ -65614,8 +65626,8 @@
         <v>2279</v>
       </c>
       <c r="Q534" s="16"/>
-      <c r="R534" s="71"/>
-      <c r="S534" s="2">
+      <c r="R534" s="49"/>
+      <c r="S534" s="93">
         <f t="shared" si="8"/>
         <v>6.5250000000000004</v>
       </c>
@@ -65666,8 +65678,8 @@
         <v>6.7</v>
       </c>
       <c r="Q535" s="16"/>
-      <c r="R535" s="71"/>
-      <c r="S535" s="2">
+      <c r="R535" s="49"/>
+      <c r="S535" s="93">
         <f t="shared" si="8"/>
         <v>6.6449999999999996</v>
       </c>
@@ -65718,8 +65730,8 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="Q536" s="16"/>
-      <c r="R536" s="71"/>
-      <c r="S536" s="2">
+      <c r="R536" s="49"/>
+      <c r="S536" s="93">
         <f t="shared" si="8"/>
         <v>8.2800000000000011</v>
       </c>
@@ -65770,8 +65782,8 @@
         <v>7</v>
       </c>
       <c r="Q537" s="16"/>
-      <c r="R537" s="71"/>
-      <c r="S537" s="2">
+      <c r="R537" s="49"/>
+      <c r="S537" s="93">
         <f t="shared" si="8"/>
         <v>6.9550000000000001</v>
       </c>
@@ -65822,8 +65834,8 @@
         <v>7</v>
       </c>
       <c r="Q538" s="16"/>
-      <c r="R538" s="71"/>
-      <c r="S538" s="2">
+      <c r="R538" s="49"/>
+      <c r="S538" s="93">
         <f t="shared" si="8"/>
         <v>6.875</v>
       </c>
@@ -65874,8 +65886,8 @@
         <v>2250</v>
       </c>
       <c r="Q539" s="16"/>
-      <c r="R539" s="71"/>
-      <c r="S539" s="2">
+      <c r="R539" s="49"/>
+      <c r="S539" s="93">
         <f t="shared" si="8"/>
         <v>6.17</v>
       </c>
@@ -65926,8 +65938,8 @@
         <v>7.57</v>
       </c>
       <c r="Q540" s="16"/>
-      <c r="R540" s="71"/>
-      <c r="S540" s="2">
+      <c r="R540" s="49"/>
+      <c r="S540" s="93">
         <f t="shared" si="8"/>
         <v>6.9375</v>
       </c>
@@ -65976,8 +65988,8 @@
         <v>2283</v>
       </c>
       <c r="Q541" s="16"/>
-      <c r="R541" s="71"/>
-      <c r="S541" s="2" t="e">
+      <c r="R541" s="49"/>
+      <c r="S541" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66028,8 +66040,8 @@
         <v>2279</v>
       </c>
       <c r="Q542" s="16"/>
-      <c r="R542" s="71"/>
-      <c r="S542" s="2">
+      <c r="R542" s="49"/>
+      <c r="S542" s="93">
         <f t="shared" si="8"/>
         <v>7.17</v>
       </c>
@@ -66047,7 +66059,7 @@
       <c r="D543" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="E543" s="1" t="s">
+      <c r="E543" s="91" t="s">
         <v>1415</v>
       </c>
       <c r="F543" s="26"/>
@@ -66068,8 +66080,8 @@
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
       <c r="Q543" s="16"/>
-      <c r="R543" s="71"/>
-      <c r="S543" s="2" t="e">
+      <c r="R543" s="49"/>
+      <c r="S543" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66120,8 +66132,8 @@
         <v>7.02</v>
       </c>
       <c r="Q544" s="16"/>
-      <c r="R544" s="71"/>
-      <c r="S544" s="2">
+      <c r="R544" s="49"/>
+      <c r="S544" s="93">
         <f t="shared" si="8"/>
         <v>7.1924999999999999</v>
       </c>
@@ -66172,8 +66184,8 @@
         <v>8.09</v>
       </c>
       <c r="Q545" s="16"/>
-      <c r="R545" s="71"/>
-      <c r="S545" s="2">
+      <c r="R545" s="49"/>
+      <c r="S545" s="93">
         <f t="shared" si="8"/>
         <v>7.8850000000000007</v>
       </c>
@@ -66222,8 +66234,8 @@
         <v>2279</v>
       </c>
       <c r="Q546" s="16"/>
-      <c r="R546" s="71"/>
-      <c r="S546" s="2" t="e">
+      <c r="R546" s="49"/>
+      <c r="S546" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66266,8 +66278,8 @@
       </c>
       <c r="P547" s="2"/>
       <c r="Q547" s="16"/>
-      <c r="R547" s="71"/>
-      <c r="S547" s="2" t="e">
+      <c r="R547" s="49"/>
+      <c r="S547" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66296,8 +66308,8 @@
       <c r="O548" s="2"/>
       <c r="P548" s="2"/>
       <c r="Q548" s="16"/>
-      <c r="R548" s="71"/>
-      <c r="S548" s="2" t="e">
+      <c r="R548" s="49"/>
+      <c r="S548" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66328,8 +66340,8 @@
       <c r="O549" s="2"/>
       <c r="P549" s="2"/>
       <c r="Q549" s="16"/>
-      <c r="R549" s="71"/>
-      <c r="S549" s="2" t="e">
+      <c r="R549" s="49"/>
+      <c r="S549" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66380,8 +66392,8 @@
         <v>2295</v>
       </c>
       <c r="Q550" s="16"/>
-      <c r="R550" s="71"/>
-      <c r="S550" s="2" t="e">
+      <c r="R550" s="49"/>
+      <c r="S550" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66428,8 +66440,8 @@
         <v>2279</v>
       </c>
       <c r="Q551" s="16"/>
-      <c r="R551" s="71"/>
-      <c r="S551" s="2">
+      <c r="R551" s="49"/>
+      <c r="S551" s="93">
         <f t="shared" si="8"/>
         <v>7.01</v>
       </c>
@@ -66468,8 +66480,8 @@
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
       <c r="Q552" s="16"/>
-      <c r="R552" s="71"/>
-      <c r="S552" s="2" t="e">
+      <c r="R552" s="49"/>
+      <c r="S552" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66520,8 +66532,8 @@
         <v>6.18</v>
       </c>
       <c r="Q553" s="16"/>
-      <c r="R553" s="71"/>
-      <c r="S553" s="2">
+      <c r="R553" s="49"/>
+      <c r="S553" s="93">
         <f t="shared" si="8"/>
         <v>6.18</v>
       </c>
@@ -66568,8 +66580,8 @@
         <v>2296</v>
       </c>
       <c r="Q554" s="16"/>
-      <c r="R554" s="71"/>
-      <c r="S554" s="2">
+      <c r="R554" s="49"/>
+      <c r="S554" s="93">
         <f t="shared" si="8"/>
         <v>6.32</v>
       </c>
@@ -66606,8 +66618,8 @@
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
       <c r="Q555" s="16"/>
-      <c r="R555" s="71"/>
-      <c r="S555" s="2" t="e">
+      <c r="R555" s="49"/>
+      <c r="S555" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66658,8 +66670,8 @@
         <v>7.36</v>
       </c>
       <c r="Q556" s="16"/>
-      <c r="R556" s="71"/>
-      <c r="S556" s="2">
+      <c r="R556" s="49"/>
+      <c r="S556" s="93">
         <f t="shared" si="8"/>
         <v>7.1733333333333329</v>
       </c>
@@ -66708,8 +66720,8 @@
         <v>6.73</v>
       </c>
       <c r="Q557" s="16"/>
-      <c r="R557" s="71"/>
-      <c r="S557" s="2">
+      <c r="R557" s="49"/>
+      <c r="S557" s="93">
         <f t="shared" si="8"/>
         <v>6.8500000000000005</v>
       </c>
@@ -66738,8 +66750,8 @@
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
       <c r="Q558" s="16"/>
-      <c r="R558" s="71"/>
-      <c r="S558" s="2" t="e">
+      <c r="R558" s="49"/>
+      <c r="S558" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66768,8 +66780,8 @@
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
       <c r="Q559" s="16"/>
-      <c r="R559" s="71"/>
-      <c r="S559" s="2" t="e">
+      <c r="R559" s="49"/>
+      <c r="S559" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66820,8 +66832,8 @@
         <v>6.91</v>
       </c>
       <c r="Q560" s="16"/>
-      <c r="R560" s="71"/>
-      <c r="S560" s="2">
+      <c r="R560" s="49"/>
+      <c r="S560" s="93">
         <f t="shared" si="8"/>
         <v>6.74</v>
       </c>
@@ -66858,8 +66870,8 @@
       <c r="O561" s="2"/>
       <c r="P561" s="2"/>
       <c r="Q561" s="16"/>
-      <c r="R561" s="71"/>
-      <c r="S561" s="2" t="e">
+      <c r="R561" s="49"/>
+      <c r="S561" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -66910,8 +66922,8 @@
         <v>7.73</v>
       </c>
       <c r="Q562" s="16"/>
-      <c r="R562" s="71"/>
-      <c r="S562" s="2">
+      <c r="R562" s="49"/>
+      <c r="S562" s="93">
         <f t="shared" si="8"/>
         <v>7.4249999999999998</v>
       </c>
@@ -66962,8 +66974,8 @@
         <v>6.36</v>
       </c>
       <c r="Q563" s="16"/>
-      <c r="R563" s="71"/>
-      <c r="S563" s="2">
+      <c r="R563" s="49"/>
+      <c r="S563" s="93">
         <f t="shared" si="8"/>
         <v>6.47</v>
       </c>
@@ -67014,8 +67026,8 @@
         <v>2297</v>
       </c>
       <c r="Q564" s="16"/>
-      <c r="R564" s="71"/>
-      <c r="S564" s="2" t="e">
+      <c r="R564" s="49"/>
+      <c r="S564" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -67051,10 +67063,11 @@
       <c r="N565" s="16" t="s">
         <v>958</v>
       </c>
+      <c r="O565" s="91"/>
       <c r="P565" s="2"/>
       <c r="Q565" s="16"/>
-      <c r="R565" s="71"/>
-      <c r="S565" s="2" t="e">
+      <c r="R565" s="49"/>
+      <c r="S565" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -67105,8 +67118,8 @@
         <v>2268</v>
       </c>
       <c r="Q566" s="16"/>
-      <c r="R566" s="71"/>
-      <c r="S566" s="2">
+      <c r="R566" s="49"/>
+      <c r="S566" s="93">
         <f t="shared" si="8"/>
         <v>6.49</v>
       </c>
@@ -67157,8 +67170,8 @@
         <v>9</v>
       </c>
       <c r="Q567" s="16"/>
-      <c r="R567" s="71"/>
-      <c r="S567" s="2">
+      <c r="R567" s="49"/>
+      <c r="S567" s="93">
         <f t="shared" si="8"/>
         <v>8.65</v>
       </c>
@@ -67209,8 +67222,8 @@
         <v>6.36</v>
       </c>
       <c r="Q568" s="16"/>
-      <c r="R568" s="71"/>
-      <c r="S568" s="2">
+      <c r="R568" s="49"/>
+      <c r="S568" s="93">
         <f t="shared" si="8"/>
         <v>6.3566666666666665</v>
       </c>
@@ -67245,8 +67258,8 @@
       <c r="O569" s="2"/>
       <c r="P569" s="2"/>
       <c r="Q569" s="16"/>
-      <c r="R569" s="71"/>
-      <c r="S569" s="2" t="e">
+      <c r="R569" s="49"/>
+      <c r="S569" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -67285,8 +67298,8 @@
       <c r="O570" s="2"/>
       <c r="P570" s="2"/>
       <c r="Q570" s="16"/>
-      <c r="R570" s="71"/>
-      <c r="S570" s="2" t="e">
+      <c r="R570" s="49"/>
+      <c r="S570" s="93" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
@@ -67337,8 +67350,8 @@
         <v>6.57</v>
       </c>
       <c r="Q571" s="16"/>
-      <c r="R571" s="71"/>
-      <c r="S571" s="2">
+      <c r="R571" s="49"/>
+      <c r="S571" s="93">
         <f t="shared" si="8"/>
         <v>6.45</v>
       </c>
@@ -67389,8 +67402,8 @@
         <v>6.77</v>
       </c>
       <c r="Q572" s="16"/>
-      <c r="R572" s="71"/>
-      <c r="S572" s="2">
+      <c r="R572" s="49"/>
+      <c r="S572" s="93">
         <f t="shared" si="8"/>
         <v>6.5133333333333328</v>
       </c>
@@ -67441,8 +67454,8 @@
         <v>7.11</v>
       </c>
       <c r="Q573" s="16"/>
-      <c r="R573" s="71"/>
-      <c r="S573" s="2">
+      <c r="R573" s="49"/>
+      <c r="S573" s="93">
         <f t="shared" si="8"/>
         <v>7.08</v>
       </c>
@@ -67493,8 +67506,8 @@
         <v>7.48</v>
       </c>
       <c r="Q574" s="16"/>
-      <c r="R574" s="71"/>
-      <c r="S574" s="2">
+      <c r="R574" s="49"/>
+      <c r="S574" s="93">
         <f t="shared" si="8"/>
         <v>6.66</v>
       </c>
@@ -67545,8 +67558,8 @@
         <v>7.3</v>
       </c>
       <c r="Q575" s="16"/>
-      <c r="R575" s="71"/>
-      <c r="S575" s="2">
+      <c r="R575" s="49"/>
+      <c r="S575" s="93">
         <f t="shared" si="8"/>
         <v>7.37</v>
       </c>
@@ -67597,8 +67610,8 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="Q576" s="16"/>
-      <c r="R576" s="71"/>
-      <c r="S576" s="2">
+      <c r="R576" s="49"/>
+      <c r="S576" s="93">
         <f t="shared" si="8"/>
         <v>8.8524999999999991</v>
       </c>
@@ -67649,8 +67662,8 @@
         <v>2281</v>
       </c>
       <c r="Q577" s="16"/>
-      <c r="R577" s="71"/>
-      <c r="S577" s="2">
+      <c r="R577" s="49"/>
+      <c r="S577" s="93">
         <f t="shared" si="8"/>
         <v>6.24</v>
       </c>
@@ -67701,9 +67714,9 @@
         <v>7.02</v>
       </c>
       <c r="Q578" s="16"/>
-      <c r="R578" s="71"/>
-      <c r="S578" s="2">
-        <f t="shared" ref="S578:S641" si="9">AVERAGE(M578:P578)</f>
+      <c r="R578" s="49"/>
+      <c r="S578" s="93">
+        <f t="shared" ref="S578:S631" si="9">AVERAGE(M578:P578)</f>
         <v>6.6499999999999995</v>
       </c>
     </row>
@@ -67753,8 +67766,8 @@
         <v>7.64</v>
       </c>
       <c r="Q579" s="16"/>
-      <c r="R579" s="71"/>
-      <c r="S579" s="2">
+      <c r="R579" s="49"/>
+      <c r="S579" s="93">
         <f t="shared" si="9"/>
         <v>6.98</v>
       </c>
@@ -67783,8 +67796,8 @@
       <c r="O580" s="2"/>
       <c r="P580" s="2"/>
       <c r="Q580" s="16"/>
-      <c r="R580" s="71"/>
-      <c r="S580" s="2" t="e">
+      <c r="R580" s="49"/>
+      <c r="S580" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -67835,8 +67848,8 @@
         <v>8.27</v>
       </c>
       <c r="Q581" s="16"/>
-      <c r="R581" s="71"/>
-      <c r="S581" s="2">
+      <c r="R581" s="49"/>
+      <c r="S581" s="93">
         <f t="shared" si="9"/>
         <v>8.0949999999999989</v>
       </c>
@@ -67887,8 +67900,8 @@
         <v>7.59</v>
       </c>
       <c r="Q582" s="16"/>
-      <c r="R582" s="71"/>
-      <c r="S582" s="2">
+      <c r="R582" s="49"/>
+      <c r="S582" s="93">
         <f t="shared" si="9"/>
         <v>6.9950000000000001</v>
       </c>
@@ -67939,8 +67952,8 @@
         <v>6.95</v>
       </c>
       <c r="Q583" s="16"/>
-      <c r="R583" s="71"/>
-      <c r="S583" s="2">
+      <c r="R583" s="49"/>
+      <c r="S583" s="93">
         <f t="shared" si="9"/>
         <v>6.6633333333333331</v>
       </c>
@@ -67991,8 +68004,8 @@
         <v>8.36</v>
       </c>
       <c r="Q584" s="16"/>
-      <c r="R584" s="71"/>
-      <c r="S584" s="2">
+      <c r="R584" s="49"/>
+      <c r="S584" s="93">
         <f t="shared" si="9"/>
         <v>7.7949999999999999</v>
       </c>
@@ -68043,8 +68056,8 @@
         <v>9.41</v>
       </c>
       <c r="Q585" s="16"/>
-      <c r="R585" s="71"/>
-      <c r="S585" s="2">
+      <c r="R585" s="49"/>
+      <c r="S585" s="93">
         <f t="shared" si="9"/>
         <v>9.2149999999999999</v>
       </c>
@@ -68077,8 +68090,8 @@
       <c r="O586" s="2"/>
       <c r="P586" s="2"/>
       <c r="Q586" s="16"/>
-      <c r="R586" s="71"/>
-      <c r="S586" s="2" t="e">
+      <c r="R586" s="49"/>
+      <c r="S586" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68129,8 +68142,8 @@
         <v>2256</v>
       </c>
       <c r="Q587" s="16"/>
-      <c r="R587" s="71"/>
-      <c r="S587" s="2">
+      <c r="R587" s="49"/>
+      <c r="S587" s="93">
         <f t="shared" si="9"/>
         <v>6.59</v>
       </c>
@@ -68181,8 +68194,8 @@
         <v>8.09</v>
       </c>
       <c r="Q588" s="16"/>
-      <c r="R588" s="71"/>
-      <c r="S588" s="2">
+      <c r="R588" s="49"/>
+      <c r="S588" s="93">
         <f t="shared" si="9"/>
         <v>8.1125000000000007</v>
       </c>
@@ -68229,8 +68242,8 @@
         <v>8.59</v>
       </c>
       <c r="Q589" s="16"/>
-      <c r="R589" s="71"/>
-      <c r="S589" s="2">
+      <c r="R589" s="49"/>
+      <c r="S589" s="93">
         <f t="shared" si="9"/>
         <v>7.9375</v>
       </c>
@@ -68265,8 +68278,8 @@
       <c r="O590" s="2"/>
       <c r="P590" s="2"/>
       <c r="Q590" s="16"/>
-      <c r="R590" s="71"/>
-      <c r="S590" s="2" t="e">
+      <c r="R590" s="49"/>
+      <c r="S590" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68317,8 +68330,8 @@
         <v>7.32</v>
       </c>
       <c r="Q591" s="16"/>
-      <c r="R591" s="71"/>
-      <c r="S591" s="2">
+      <c r="R591" s="49"/>
+      <c r="S591" s="93">
         <f t="shared" si="9"/>
         <v>7.6074999999999999</v>
       </c>
@@ -68355,8 +68368,8 @@
       <c r="O592" s="2"/>
       <c r="P592" s="2"/>
       <c r="Q592" s="16"/>
-      <c r="R592" s="71"/>
-      <c r="S592" s="2" t="e">
+      <c r="R592" s="49"/>
+      <c r="S592" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68391,8 +68404,8 @@
       <c r="O593" s="2"/>
       <c r="P593" s="2"/>
       <c r="Q593" s="16"/>
-      <c r="R593" s="71"/>
-      <c r="S593" s="2" t="e">
+      <c r="R593" s="49"/>
+      <c r="S593" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68421,8 +68434,8 @@
       <c r="O594" s="2"/>
       <c r="P594" s="2"/>
       <c r="Q594" s="16"/>
-      <c r="R594" s="71"/>
-      <c r="S594" s="2" t="e">
+      <c r="R594" s="49"/>
+      <c r="S594" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68457,8 +68470,8 @@
       <c r="O595" s="2"/>
       <c r="P595" s="2"/>
       <c r="Q595" s="16"/>
-      <c r="R595" s="71"/>
-      <c r="S595" s="2" t="e">
+      <c r="R595" s="49"/>
+      <c r="S595" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68487,8 +68500,8 @@
       <c r="O596" s="2"/>
       <c r="P596" s="2"/>
       <c r="Q596" s="16"/>
-      <c r="R596" s="71"/>
-      <c r="S596" s="2" t="e">
+      <c r="R596" s="49"/>
+      <c r="S596" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68523,8 +68536,8 @@
       <c r="O597" s="2"/>
       <c r="P597" s="2"/>
       <c r="Q597" s="16"/>
-      <c r="R597" s="71"/>
-      <c r="S597" s="2" t="e">
+      <c r="R597" s="49"/>
+      <c r="S597" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -68575,8 +68588,8 @@
         <v>2279</v>
       </c>
       <c r="Q598" s="16"/>
-      <c r="R598" s="71"/>
-      <c r="S598" s="2">
+      <c r="R598" s="49"/>
+      <c r="S598" s="93">
         <f t="shared" si="9"/>
         <v>6.39</v>
       </c>
@@ -68627,8 +68640,8 @@
         <v>7.41</v>
       </c>
       <c r="Q599" s="16"/>
-      <c r="R599" s="71"/>
-      <c r="S599" s="2">
+      <c r="R599" s="49"/>
+      <c r="S599" s="93">
         <f t="shared" si="9"/>
         <v>6.9550000000000001</v>
       </c>
@@ -68679,8 +68692,8 @@
         <v>6.8</v>
       </c>
       <c r="Q600" s="16"/>
-      <c r="R600" s="71"/>
-      <c r="S600" s="2">
+      <c r="R600" s="49"/>
+      <c r="S600" s="93">
         <f t="shared" si="9"/>
         <v>6.9050000000000002</v>
       </c>
@@ -68731,8 +68744,8 @@
         <v>7.23</v>
       </c>
       <c r="Q601" s="16"/>
-      <c r="R601" s="71"/>
-      <c r="S601" s="2">
+      <c r="R601" s="49"/>
+      <c r="S601" s="93">
         <f t="shared" si="9"/>
         <v>6.7566666666666668</v>
       </c>
@@ -68783,8 +68796,8 @@
         <v>6.86</v>
       </c>
       <c r="Q602" s="16"/>
-      <c r="R602" s="71"/>
-      <c r="S602" s="2">
+      <c r="R602" s="49"/>
+      <c r="S602" s="93">
         <f t="shared" si="9"/>
         <v>6.375</v>
       </c>
@@ -68835,8 +68848,8 @@
         <v>6.05</v>
       </c>
       <c r="Q603" s="16"/>
-      <c r="R603" s="71"/>
-      <c r="S603" s="2">
+      <c r="R603" s="49"/>
+      <c r="S603" s="93">
         <f t="shared" si="9"/>
         <v>6.6166666666666671</v>
       </c>
@@ -68887,8 +68900,8 @@
         <v>7.93</v>
       </c>
       <c r="Q604" s="16"/>
-      <c r="R604" s="71"/>
-      <c r="S604" s="2">
+      <c r="R604" s="49"/>
+      <c r="S604" s="93">
         <f t="shared" si="9"/>
         <v>8.02</v>
       </c>
@@ -68939,8 +68952,8 @@
         <v>7.64</v>
       </c>
       <c r="Q605" s="16"/>
-      <c r="R605" s="71"/>
-      <c r="S605" s="2">
+      <c r="R605" s="49"/>
+      <c r="S605" s="93">
         <f t="shared" si="9"/>
         <v>7.6150000000000002</v>
       </c>
@@ -68991,8 +69004,8 @@
         <v>8.14</v>
       </c>
       <c r="Q606" s="16"/>
-      <c r="R606" s="71"/>
-      <c r="S606" s="2">
+      <c r="R606" s="49"/>
+      <c r="S606" s="93">
         <f t="shared" si="9"/>
         <v>8.2733333333333334</v>
       </c>
@@ -69043,8 +69056,8 @@
         <v>2253</v>
       </c>
       <c r="Q607" s="16"/>
-      <c r="R607" s="71"/>
-      <c r="S607" s="2">
+      <c r="R607" s="49"/>
+      <c r="S607" s="93">
         <f t="shared" si="9"/>
         <v>6.5350000000000001</v>
       </c>
@@ -69095,8 +69108,8 @@
         <v>7.36</v>
       </c>
       <c r="Q608" s="16"/>
-      <c r="R608" s="71"/>
-      <c r="S608" s="2">
+      <c r="R608" s="49"/>
+      <c r="S608" s="93">
         <f t="shared" si="9"/>
         <v>7.8650000000000002</v>
       </c>
@@ -69147,8 +69160,8 @@
         <v>7.05</v>
       </c>
       <c r="Q609" s="16"/>
-      <c r="R609" s="71"/>
-      <c r="S609" s="2">
+      <c r="R609" s="49"/>
+      <c r="S609" s="93">
         <f t="shared" si="9"/>
         <v>6.625</v>
       </c>
@@ -69199,8 +69212,8 @@
         <v>2253</v>
       </c>
       <c r="Q610" s="16"/>
-      <c r="R610" s="71"/>
-      <c r="S610" s="2">
+      <c r="R610" s="49"/>
+      <c r="S610" s="93">
         <f t="shared" si="9"/>
         <v>6.8166666666666664</v>
       </c>
@@ -69251,8 +69264,8 @@
         <v>7.55</v>
       </c>
       <c r="Q611" s="16"/>
-      <c r="R611" s="71"/>
-      <c r="S611" s="2">
+      <c r="R611" s="49"/>
+      <c r="S611" s="93">
         <f t="shared" si="9"/>
         <v>7.8366666666666669</v>
       </c>
@@ -69303,8 +69316,8 @@
         <v>6.14</v>
       </c>
       <c r="Q612" s="16"/>
-      <c r="R612" s="71"/>
-      <c r="S612" s="2">
+      <c r="R612" s="49"/>
+      <c r="S612" s="93">
         <f t="shared" si="9"/>
         <v>6.5075000000000003</v>
       </c>
@@ -69355,8 +69368,8 @@
         <v>6.05</v>
       </c>
       <c r="Q613" s="16"/>
-      <c r="R613" s="71"/>
-      <c r="S613" s="2">
+      <c r="R613" s="49"/>
+      <c r="S613" s="93">
         <f t="shared" si="9"/>
         <v>6.3</v>
       </c>
@@ -69407,8 +69420,8 @@
         <v>2294</v>
       </c>
       <c r="Q614" s="16"/>
-      <c r="R614" s="71"/>
-      <c r="S614" s="2">
+      <c r="R614" s="49"/>
+      <c r="S614" s="93">
         <f t="shared" si="9"/>
         <v>6.05</v>
       </c>
@@ -69437,8 +69450,8 @@
       <c r="O615" s="2"/>
       <c r="P615" s="2"/>
       <c r="Q615" s="16"/>
-      <c r="R615" s="71"/>
-      <c r="S615" s="2" t="e">
+      <c r="R615" s="49"/>
+      <c r="S615" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -69489,8 +69502,8 @@
         <v>5.64</v>
       </c>
       <c r="Q616" s="16"/>
-      <c r="R616" s="71"/>
-      <c r="S616" s="2">
+      <c r="R616" s="49"/>
+      <c r="S616" s="93">
         <f t="shared" si="9"/>
         <v>6.123333333333334</v>
       </c>
@@ -69539,8 +69552,8 @@
         <v>6.25</v>
       </c>
       <c r="Q617" s="16"/>
-      <c r="R617" s="71"/>
-      <c r="S617" s="2">
+      <c r="R617" s="49"/>
+      <c r="S617" s="93">
         <f t="shared" si="9"/>
         <v>6.62</v>
       </c>
@@ -69591,8 +69604,8 @@
         <v>7.45</v>
       </c>
       <c r="Q618" s="16"/>
-      <c r="R618" s="71"/>
-      <c r="S618" s="2">
+      <c r="R618" s="49"/>
+      <c r="S618" s="93">
         <f t="shared" si="9"/>
         <v>6.9466666666666663</v>
       </c>
@@ -69643,8 +69656,8 @@
         <v>6.14</v>
       </c>
       <c r="Q619" s="16"/>
-      <c r="R619" s="71"/>
-      <c r="S619" s="2">
+      <c r="R619" s="49"/>
+      <c r="S619" s="93">
         <f t="shared" si="9"/>
         <v>6.69</v>
       </c>
@@ -69695,8 +69708,8 @@
         <v>6.64</v>
       </c>
       <c r="Q620" s="16"/>
-      <c r="R620" s="71"/>
-      <c r="S620" s="2">
+      <c r="R620" s="49"/>
+      <c r="S620" s="93">
         <f t="shared" si="9"/>
         <v>6.7975000000000003</v>
       </c>
@@ -69747,8 +69760,8 @@
         <v>7.14</v>
       </c>
       <c r="Q621" s="16"/>
-      <c r="R621" s="71"/>
-      <c r="S621" s="2">
+      <c r="R621" s="49"/>
+      <c r="S621" s="93">
         <f t="shared" si="9"/>
         <v>7.0166666666666666</v>
       </c>
@@ -69799,8 +69812,8 @@
         <v>2298</v>
       </c>
       <c r="Q622" s="16"/>
-      <c r="R622" s="71"/>
-      <c r="S622" s="2" t="e">
+      <c r="R622" s="49"/>
+      <c r="S622" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -69851,8 +69864,8 @@
         <v>6.36</v>
       </c>
       <c r="Q623" s="16"/>
-      <c r="R623" s="71"/>
-      <c r="S623" s="2">
+      <c r="R623" s="49"/>
+      <c r="S623" s="93">
         <f t="shared" si="9"/>
         <v>6.6633333333333331</v>
       </c>
@@ -69903,8 +69916,8 @@
         <v>6.84</v>
       </c>
       <c r="Q624" s="16"/>
-      <c r="R624" s="71"/>
-      <c r="S624" s="2">
+      <c r="R624" s="49"/>
+      <c r="S624" s="93">
         <f t="shared" si="9"/>
         <v>7.25</v>
       </c>
@@ -69953,8 +69966,8 @@
         <v>2250</v>
       </c>
       <c r="Q625" s="16"/>
-      <c r="R625" s="71"/>
-      <c r="S625" s="2" t="e">
+      <c r="R625" s="49"/>
+      <c r="S625" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -70005,8 +70018,8 @@
         <v>6.95</v>
       </c>
       <c r="Q626" s="16"/>
-      <c r="R626" s="71"/>
-      <c r="S626" s="2">
+      <c r="R626" s="49"/>
+      <c r="S626" s="93">
         <f t="shared" si="9"/>
         <v>6.9849999999999994</v>
       </c>
@@ -70057,8 +70070,8 @@
         <v>2299</v>
       </c>
       <c r="Q627" s="16"/>
-      <c r="R627" s="71"/>
-      <c r="S627" s="2" t="e">
+      <c r="R627" s="49"/>
+      <c r="S627" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -70109,8 +70122,8 @@
         <v>6.64</v>
       </c>
       <c r="Q628" s="16"/>
-      <c r="R628" s="71"/>
-      <c r="S628" s="2">
+      <c r="R628" s="49"/>
+      <c r="S628" s="93">
         <f t="shared" si="9"/>
         <v>7.38</v>
       </c>
@@ -70161,8 +70174,8 @@
         <v>5.86</v>
       </c>
       <c r="Q629" s="16"/>
-      <c r="R629" s="71"/>
-      <c r="S629" s="2">
+      <c r="R629" s="49"/>
+      <c r="S629" s="93">
         <f t="shared" si="9"/>
         <v>5.86</v>
       </c>
@@ -70213,8 +70226,8 @@
         <v>5.82</v>
       </c>
       <c r="Q630" s="16"/>
-      <c r="R630" s="71"/>
-      <c r="S630" s="2">
+      <c r="R630" s="49"/>
+      <c r="S630" s="93">
         <f t="shared" si="9"/>
         <v>6.15</v>
       </c>
@@ -70247,112 +70260,16 @@
       <c r="O631" s="7"/>
       <c r="P631" s="7"/>
       <c r="Q631" s="22"/>
-      <c r="R631" s="72"/>
-      <c r="S631" s="2" t="e">
+      <c r="R631" s="50"/>
+      <c r="S631" s="94" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B632"/>
-      <c r="E632"/>
-      <c r="F632" s="42"/>
-      <c r="G632" s="42"/>
-      <c r="S632" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="633" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B633"/>
-      <c r="E633"/>
-      <c r="F633" s="42"/>
-      <c r="G633" s="42"/>
-      <c r="S633" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B634"/>
-      <c r="E634"/>
-      <c r="F634" s="42"/>
-      <c r="G634" s="42"/>
-      <c r="S634" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="635" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B635"/>
-      <c r="E635"/>
-      <c r="F635" s="42"/>
-      <c r="G635" s="42"/>
-      <c r="S635" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B636"/>
-      <c r="E636"/>
-      <c r="F636" s="42"/>
-      <c r="G636" s="42"/>
-      <c r="S636" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B637"/>
-      <c r="E637"/>
-      <c r="F637" s="42"/>
-      <c r="G637" s="42"/>
-      <c r="S637" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="638" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B638"/>
-      <c r="E638"/>
-      <c r="F638" s="42"/>
-      <c r="G638" s="42"/>
-      <c r="S638" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B639"/>
-      <c r="E639"/>
-      <c r="F639" s="42"/>
-      <c r="G639" s="42"/>
-      <c r="S639" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B640"/>
-      <c r="E640"/>
-      <c r="F640" s="42"/>
-      <c r="G640" s="42"/>
-      <c r="S640" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="641" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S641" s="2" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="P1:P641" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R641">
-      <sortCondition ref="P1:P641"/>
+  <autoFilter ref="P1:P631" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R631">
+      <sortCondition ref="P1:P631"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
